--- a/data/proteomics/membrane_size_ratio_across_compartment_cell_system_2018.xlsx
+++ b/data/proteomics/membrane_size_ratio_across_compartment_cell_system_2018.xlsx
@@ -675,142 +675,142 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.02842927155946023</v>
+        <v>0.02511520181973679</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03317641434109971</v>
+        <v>0.03000341216649309</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0045582890610242</v>
+        <v>0.003702045292069249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03802767431881509</v>
+        <v>0.03488844041365578</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02328238310449684</v>
+        <v>0.01951517110992164</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001417590693869521</v>
+        <v>0.001187598375903376</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007961167536998768</v>
+        <v>0.007340441237873826</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02812149168137265</v>
+        <v>0.02610709374497482</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02519400073203616</v>
+        <v>0.02356839435911318</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01966744170377339</v>
+        <v>0.01815014422997259</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02586409034486817</v>
+        <v>0.02426062249443635</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02259933346910684</v>
+        <v>0.02100155371957382</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03272147370626892</v>
+        <v>0.03070505397151046</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02350821182376006</v>
+        <v>0.02104595317801336</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03644396299415342</v>
+        <v>0.03522607155688043</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0193009334998136</v>
+        <v>0.008767265452101422</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0234667014717409</v>
+        <v>0.02223068738853374</v>
       </c>
       <c r="T2" t="n">
-        <v>0.02104496375315105</v>
+        <v>0.01881819639134931</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02244775001939967</v>
+        <v>0.02119583773454431</v>
       </c>
       <c r="V2" t="n">
-        <v>0.02215052347149957</v>
+        <v>0.01978001408311683</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02028905265210317</v>
+        <v>0.0127032635462696</v>
       </c>
       <c r="X2" t="n">
-        <v>0.02053420951633405</v>
+        <v>0.01621921711936075</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.02203542391942723</v>
+        <v>0.01977910637750847</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03644396299415342</v>
+        <v>0.03522607155688043</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.02929465960091819</v>
+        <v>0.02799072126915804</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.03377755559221318</v>
+        <v>0.03228872619884952</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.03150298078404016</v>
+        <v>0.02990535559142441</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.02104496375315105</v>
+        <v>0.01881819639134931</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.02349494677367305</v>
+        <v>0.02067864439237451</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.01761794784382041</v>
+        <v>0.01468996123749254</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.02053420951633405</v>
+        <v>0.01621921711936075</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.02251129574603813</v>
+        <v>0.01488343238678852</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.02746280112861291</v>
+        <v>0.008110975656194624</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.02870120554836343</v>
+        <v>0.01163966883120805</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.02028905265210317</v>
+        <v>0.0127032635462696</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.01938700007188437</v>
+        <v>0.01418868743908389</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.02077199622425967</v>
+        <v>0.01648013733760059</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0185003169389756</v>
+        <v>0.01300676237568732</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.02350821182376006</v>
+        <v>0.02104595317801336</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.02329017536555601</v>
+        <v>0.02023825679949192</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.02684199964129998</v>
+        <v>0.023294325515702</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.02106742031092643</v>
+        <v>0.01899681388009873</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.02328238418546813</v>
+        <v>0.01951517190430115</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0135174676139822</v>
+        <v>0.01210963592228034</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.008954375277667351</v>
+        <v>0.008252827282967385</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.008774921583990273</v>
+        <v>0.008015482318599259</v>
       </c>
     </row>
     <row r="3">
@@ -823,142 +823,142 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.08907099701578305</v>
+        <v>0.07887370759644524</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09703088681125907</v>
+        <v>0.08800443629922101</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1235237928490553</v>
+        <v>0.1004949900392503</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07831025359966572</v>
+        <v>0.07218749048890638</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1077534708611257</v>
+        <v>0.09034791271500815</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1103736507294026</v>
+        <v>0.09246644247569383</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05988791933277583</v>
+        <v>0.05521850289894695</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1001457884555325</v>
+        <v>0.09322016018048279</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1134043877366823</v>
+        <v>0.106087134022874</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09634488869853103</v>
+        <v>0.08918774356158633</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08688384867780662</v>
+        <v>0.0817604740153481</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09955231840996914</v>
+        <v>0.09251393922095685</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1016059657315763</v>
+        <v>0.09572447059740836</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0936740528859179</v>
+        <v>0.08418582309307256</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1003855335015951</v>
+        <v>0.09742050381254624</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1450726593959705</v>
+        <v>0.06589787560166725</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1855705140964648</v>
+        <v>0.1762291280800927</v>
       </c>
       <c r="T3" t="n">
-        <v>0.09814531864348933</v>
+        <v>0.08806999810962311</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09300042920877195</v>
+        <v>0.0878137900256617</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09222997697796778</v>
+        <v>0.08235968986724085</v>
       </c>
       <c r="W3" t="n">
-        <v>0.09427043192048754</v>
+        <v>0.05902405409660568</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1350081693904605</v>
+        <v>0.1069938715621271</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09214306306758299</v>
+        <v>0.08288188216441197</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1003855335015951</v>
+        <v>0.09742050381254624</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1108673249367251</v>
+        <v>0.1063186737611517</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.09880504660121948</v>
+        <v>0.09490791201928499</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1075523453257638</v>
+        <v>0.1025806033273688</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.09814531864348933</v>
+        <v>0.08806999810962311</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.08524806461783302</v>
+        <v>0.07538907809898207</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.08441703731270303</v>
+        <v>0.07067868667820262</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.1350081693904605</v>
+        <v>0.1069938715621271</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.1434108806823956</v>
+        <v>0.0948166720497145</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1372491726783913</v>
+        <v>0.04053573024885065</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1456518942231602</v>
+        <v>0.05906859245124633</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.09427043192048754</v>
+        <v>0.05902405409660568</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.09460555043816217</v>
+        <v>0.06940004349720799</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1479129774779076</v>
+        <v>0.117635504603033</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.1277163096106507</v>
+        <v>0.09005662810555166</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0936740528859179</v>
+        <v>0.08418582309307256</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1072993477932194</v>
+        <v>0.093603863986954</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.1065629613332156</v>
+        <v>0.09294610532538071</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.08801971252841698</v>
+        <v>0.07953570127862787</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1077534694951086</v>
+        <v>0.09034791105351689</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1164486665482558</v>
+        <v>0.1043979188753149</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.07691648745355242</v>
+        <v>0.07095021623455798</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.07220730128069888</v>
+        <v>0.06602165822355537</v>
       </c>
     </row>
     <row r="4">
@@ -971,142 +971,142 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1608828609108774</v>
+        <v>0.1428287595334072</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1438602029272342</v>
+        <v>0.1309242100286049</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08335770607771249</v>
+        <v>0.06769952480226209</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1167469800648234</v>
+        <v>0.1078763763470893</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1503377897171035</v>
+        <v>0.126219053510812</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05337350621176096</v>
+        <v>0.04471409805910471</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04129264354542201</v>
+        <v>0.03807308690502782</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1414078641923061</v>
+        <v>0.1324409375017697</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1405345753430541</v>
+        <v>0.1319401743146003</v>
       </c>
       <c r="L4" t="n">
-        <v>0.14526558046567</v>
+        <v>0.1344605902944148</v>
       </c>
       <c r="M4" t="n">
-        <v>0.125326963754474</v>
+        <v>0.1195811711044992</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1418121001842789</v>
+        <v>0.1317859415711089</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09608938668923306</v>
+        <v>0.09198077092205778</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1527375194478331</v>
+        <v>0.1372797919893179</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1260038995294527</v>
+        <v>0.1223853700836404</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07825383170656529</v>
+        <v>0.03554605870343806</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1339836020923175</v>
+        <v>0.1275150821080244</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2412487588789539</v>
+        <v>0.2164993717502487</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1429970156987557</v>
+        <v>0.135691716336592</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2243652636414759</v>
+        <v>0.2003540945793355</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1908842263879116</v>
+        <v>0.1200506709682665</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1174620245027878</v>
+        <v>0.09277893444960385</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.296783695514696</v>
+        <v>0.267276247624928</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1260038995294527</v>
+        <v>0.1223853700836404</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.09948396005956366</v>
+        <v>0.09629825122545309</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1094271805162439</v>
+        <v>0.1059524690725917</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1322112051503542</v>
+        <v>0.1266294971082676</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2412487588789539</v>
+        <v>0.2164993717502487</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1977158167005515</v>
+        <v>0.1750161691066271</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2873824444034118</v>
+        <v>0.2400548781222447</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.1174620245027878</v>
+        <v>0.09277893444960385</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.1007733291191053</v>
+        <v>0.06662668587612317</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.07761962513369176</v>
+        <v>0.02292449655641244</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.08212643212017899</v>
+        <v>0.03330607387054785</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.1908842263879116</v>
+        <v>0.1200506709682665</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1859387968704498</v>
+        <v>0.1364247227163576</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.1153922398003982</v>
+        <v>0.09193629379111026</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.09597149769425339</v>
+        <v>0.06779348019996712</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1527375194478331</v>
+        <v>0.1372797919893179</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.1381158751743666</v>
+        <v>0.1210451810678976</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.1440811492910651</v>
+        <v>0.1259532444883827</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.283078221639547</v>
+        <v>0.2561028220149204</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.1503377598268428</v>
+        <v>0.1262190277426657</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.07380931735561301</v>
+        <v>0.06633602233980131</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.04739139440993434</v>
+        <v>0.04382924267972185</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.05258695973589612</v>
+        <v>0.04818721370499118</v>
       </c>
     </row>
     <row r="5">
@@ -1119,142 +1119,142 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0621408866176475</v>
+        <v>0.06145705818614611</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06082328821695546</v>
+        <v>0.0609586370260697</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01831648595207737</v>
+        <v>0.01487585795423529</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1009889382717829</v>
+        <v>0.1022956510734337</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1090903616882438</v>
+        <v>0.1021142538917223</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09124582739816299</v>
+        <v>0.07644194963655154</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1271610055132124</v>
+        <v>0.13630811796995</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07259767138134253</v>
+        <v>0.07374174149300732</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07606306595439795</v>
+        <v>0.07716974291553412</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0794444543118667</v>
+        <v>0.08040266057000886</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07585561567237858</v>
+        <v>0.07605621063629092</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07430588249916859</v>
+        <v>0.07887844453603042</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08525053183144578</v>
+        <v>0.08456454676751991</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03500931286546679</v>
+        <v>0.0351483673888362</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02652261664932844</v>
+        <v>0.03548378263851888</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03092480391302697</v>
+        <v>0.01616728373555455</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03886738007255545</v>
+        <v>0.04312257026611115</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02902094962300062</v>
+        <v>0.02879388498976778</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03526202622064661</v>
+        <v>0.04343615816141662</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03048114342098428</v>
+        <v>0.03110232056627165</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04128182214896473</v>
+        <v>0.03085671220746983</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03989915161471552</v>
+        <v>0.03831577320777386</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04144809096557472</v>
+        <v>0.05372022582205089</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02652261664932844</v>
+        <v>0.03548378263851888</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02509366291068153</v>
+        <v>0.04148003035171896</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03130583152716384</v>
+        <v>0.04398607313382118</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.02921479478227395</v>
+        <v>0.05101921641512238</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.02902094962300062</v>
+        <v>0.02879388498976778</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.03487340780690572</v>
+        <v>0.03472738365820869</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02811043942226731</v>
+        <v>0.02713725629779178</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.03989915161471552</v>
+        <v>0.03831577320777386</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.03560165744712124</v>
+        <v>0.02743759569607277</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.03082548885344944</v>
+        <v>0.01076738430900853</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.02870716119242532</v>
+        <v>0.01364204623450146</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.04128182214896473</v>
+        <v>0.03085671220746983</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.04146610557551029</v>
+        <v>0.03561668204931327</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.03141313459845525</v>
+        <v>0.02905743182946033</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.03448233606370753</v>
+        <v>0.02794904429365182</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.03500931286546679</v>
+        <v>0.0351483673888362</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.03592387408822594</v>
+        <v>0.03560703337348028</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.03945278165027074</v>
+        <v>0.03921777024606543</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.03963417135149879</v>
+        <v>0.05160990264043091</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.1090903689931502</v>
+        <v>0.1021142596727985</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.1284029761814702</v>
+        <v>0.135048687656857</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1730098041691603</v>
+        <v>0.1758739954032645</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1592064779417577</v>
+        <v>0.1749171466883628</v>
       </c>
     </row>
     <row r="6">
@@ -1267,142 +1267,142 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0203905747331714</v>
+        <v>0.01801359554967606</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01619226248700595</v>
+        <v>0.01464362966747239</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003065844863637121</v>
+        <v>0.002489946642631805</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03475716856867678</v>
+        <v>0.03188791916090685</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03709264252534172</v>
+        <v>0.03109085794835961</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0487643238642673</v>
+        <v>0.04085271727140761</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06520521798645247</v>
+        <v>0.06012121573976388</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0219810869684635</v>
+        <v>0.02040653833744675</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02273036147100398</v>
+        <v>0.02126371784980564</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02696671122181043</v>
+        <v>0.02488629204834375</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02155166203586262</v>
+        <v>0.02021554710828952</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02293954342107093</v>
+        <v>0.02131771072446403</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02196789513120248</v>
+        <v>0.02061415117482393</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008237638158806857</v>
+        <v>0.007374824945742531</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01146217249853219</v>
+        <v>0.01107912739060176</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009770027123755432</v>
+        <v>0.004437941888614976</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008668541812347847</v>
+        <v>0.008211961249722345</v>
       </c>
       <c r="T6" t="n">
-        <v>0.007337210765330019</v>
+        <v>0.006560860582429331</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001856537697780592</v>
+        <v>0.001752998485648419</v>
       </c>
       <c r="V6" t="n">
-        <v>0.005822144343298689</v>
+        <v>0.005199068873138043</v>
       </c>
       <c r="W6" t="n">
-        <v>0.006305790355494651</v>
+        <v>0.003948144752094672</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004149728806781876</v>
+        <v>0.003277718212143625</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01022081065084377</v>
+        <v>0.009174250600605883</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01146217249853219</v>
+        <v>0.01107912739060176</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01036347301487459</v>
+        <v>0.009902183145036558</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0133719942220327</v>
+        <v>0.01278259046866457</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01293680303353352</v>
+        <v>0.01228073297527567</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.007337210765330019</v>
+        <v>0.006560860582429331</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.01041142453972393</v>
+        <v>0.009163423426702018</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.008152493329026209</v>
+        <v>0.006797602765881605</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.004149728806781876</v>
+        <v>0.003277718212143625</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.008519899627411422</v>
+        <v>0.005632965400009</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.008120625742143457</v>
+        <v>0.002398378715963113</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.007916928870654731</v>
+        <v>0.003210681518564488</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.006305790355494651</v>
+        <v>0.003948144752094672</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.007378144341700295</v>
+        <v>0.005399813460394523</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.007194998971333174</v>
+        <v>0.005708385939959978</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.006995803977847432</v>
+        <v>0.004918443303803645</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.008237638158806857</v>
+        <v>0.007374824945742531</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.009491227110405358</v>
+        <v>0.008247507311033837</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.01117537560371812</v>
+        <v>0.009698339935624741</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.009769103760324176</v>
+        <v>0.008808949703917983</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.03709264965603879</v>
+        <v>0.03109086374734005</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.05316441987472581</v>
+        <v>0.04762739494461515</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1233884100116502</v>
+        <v>0.1137213043868968</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1188602515164675</v>
+        <v>0.1085733057891634</v>
       </c>
     </row>
     <row r="7">
@@ -1415,142 +1415,142 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0300838399642728</v>
+        <v>0.02668527424463491</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03384895170058553</v>
+        <v>0.03075827077977365</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01155083818305306</v>
+        <v>0.009381091357426374</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03827780324967657</v>
+        <v>0.0351179208764085</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01798685151428063</v>
+        <v>0.01507648437251868</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001110390883689106</v>
+        <v>0.0009302391838419285</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01359660797984889</v>
+        <v>0.01253649058968454</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02250830223559297</v>
+        <v>0.02089598813472931</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01569039308911192</v>
+        <v>0.01467799322175407</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01575608446409233</v>
+        <v>0.0146936619102909</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02514142572493212</v>
+        <v>0.02358276012616511</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02377784364093118</v>
+        <v>0.02209674286382302</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0309831719306646</v>
+        <v>0.02907387286035907</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02310278693841269</v>
+        <v>0.02068299264242732</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02505141984441925</v>
+        <v>0.02442613305290647</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01931320622178885</v>
+        <v>0.00877284021932073</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03275285779243557</v>
+        <v>0.03102773278730939</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01873091141257594</v>
+        <v>0.0167489939011201</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03420230611575081</v>
+        <v>0.0322948415743296</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02445036046759303</v>
+        <v>0.02183372663894574</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03617396041216296</v>
+        <v>0.02264902952875893</v>
       </c>
       <c r="X7" t="n">
-        <v>0.02006580841387156</v>
+        <v>0.0158492443101448</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01398582789551439</v>
+        <v>0.01255374885159436</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.02505141984441925</v>
+        <v>0.02442613305290647</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02361952223670551</v>
+        <v>0.02256819066836272</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02280542715956014</v>
+        <v>0.02180022149301409</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03699185877316734</v>
+        <v>0.03511587357980316</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.01873091141257594</v>
+        <v>0.0167489939011201</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.02294948861092974</v>
+        <v>0.02019856944319753</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01669052576433736</v>
+        <v>0.01391667058416713</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.02006580841387156</v>
+        <v>0.0158492443101448</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.03241828226338777</v>
+        <v>0.02143347578061445</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.02067112534201723</v>
+        <v>0.006105094438475357</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0203254677065423</v>
+        <v>0.008242919014147691</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.03617396041216296</v>
+        <v>0.02264902952875893</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01901853737686741</v>
+        <v>0.01391902209668056</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.02715366061707987</v>
+        <v>0.02154323789378704</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.02723193392530947</v>
+        <v>0.01914557976305303</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.02310278693841269</v>
+        <v>0.02068299264242732</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.02446061500106782</v>
+        <v>0.02125532333248263</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.02465782685953666</v>
+        <v>0.02139883216793191</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.01336834595865361</v>
+        <v>0.01205444123263639</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.01798685118318374</v>
+        <v>0.0150764840087126</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.01494730316721515</v>
+        <v>0.01339055543123284</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.008985752994578046</v>
+        <v>0.008281746651451266</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.008906586033927017</v>
+        <v>0.008135751663499334</v>
       </c>
     </row>
     <row r="8">
@@ -1563,142 +1563,142 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01603552853437165</v>
+        <v>0.01610562731002609</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01898751239764094</v>
+        <v>0.01995641059801948</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008253103068134628</v>
+        <v>0.006702813478767194</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01531789282176903</v>
+        <v>0.01661440359082067</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0134977204425345</v>
+        <v>0.01207595891798584</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001210178638964338</v>
+        <v>0.001013837204492321</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01079704698115102</v>
+        <v>0.01022930078921933</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02753056225521878</v>
+        <v>0.0289803416961788</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02039273469941592</v>
+        <v>0.02188029255717675</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02456564907428945</v>
+        <v>0.02482609268714449</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02260142334986394</v>
+        <v>0.02544511299167182</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0273233038041487</v>
+        <v>0.02539153791519958</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0246131951863286</v>
+        <v>0.02723883043933851</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009687263077655694</v>
+        <v>0.01085045245244728</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003922543140760803</v>
+        <v>0.003791458831838833</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01188322181307187</v>
+        <v>0.005397840475560894</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01108516935612246</v>
+        <v>0.01420143144934516</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01010189637517664</v>
+        <v>0.01172004636591742</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01699039455919884</v>
+        <v>0.01883374592421826</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01084889773591307</v>
+        <v>0.009687868111955151</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01494149560441452</v>
+        <v>0.009873188679726844</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01653750959875895</v>
+        <v>0.01554498286099823</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.005845058202202614</v>
+        <v>0.006543507055078391</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003922543140760803</v>
+        <v>0.003791458831838833</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01053053345074163</v>
+        <v>0.01241187945286332</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.009780247463989087</v>
+        <v>0.01069919198640815</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.009403018168632288</v>
+        <v>0.009512175640705925</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.01010189637517664</v>
+        <v>0.01172004636591742</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01217575211738652</v>
+        <v>0.0133943346191838</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.008698077376391285</v>
+        <v>0.009321032930323729</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.01653750959875895</v>
+        <v>0.01554498286099823</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0192650706632601</v>
+        <v>0.01660885438179522</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.01178373812020699</v>
+        <v>0.00348025726088047</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.008870730560971722</v>
+        <v>0.003597492302077701</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01494149560441452</v>
+        <v>0.009873188679726844</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0134757843498531</v>
+        <v>0.0119963389318053</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.009041541213597366</v>
+        <v>0.009600946070610614</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.008472274475672491</v>
+        <v>0.007289064389602124</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.009687263077655694</v>
+        <v>0.01085045245244728</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.01194944209928902</v>
+        <v>0.01302273476179075</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.01194403678925313</v>
+        <v>0.0130103109344143</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.005585004860961087</v>
+        <v>0.006281900852482534</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.01349772051708884</v>
+        <v>0.01207595891433864</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.01360579860296705</v>
+        <v>0.01266723381126817</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.01011004663049394</v>
+        <v>0.009642679759006935</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.009016814126264148</v>
+        <v>0.008578843999649277</v>
       </c>
     </row>
     <row r="9">
@@ -1711,142 +1711,142 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03400157772892229</v>
+        <v>0.03003793062602001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0270796546886015</v>
+        <v>0.02448974842775269</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2434604776669986</v>
+        <v>0.1977280736447042</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04158187848232753</v>
+        <v>0.03814924040728879</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1099113730274903</v>
+        <v>0.0921271350072243</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1295785969728368</v>
+        <v>0.1085555456749797</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07666318276851815</v>
+        <v>0.07068581154779126</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01941178477760121</v>
+        <v>0.01802128033207422</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01900135013263511</v>
+        <v>0.01777531556201309</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02767721556174003</v>
+        <v>0.0255419826277275</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01453406095306181</v>
+        <v>0.0136330085996364</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02695080788473941</v>
+        <v>0.02504537757058188</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0143091067373832</v>
+        <v>0.01342732600002916</v>
       </c>
       <c r="P9" t="n">
-        <v>0.05406555570475424</v>
+        <v>0.04840270976099847</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05966366159790328</v>
+        <v>0.05766980976054693</v>
       </c>
       <c r="R9" t="n">
-        <v>0.07614032359459508</v>
+        <v>0.03458601774723295</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002515213216591397</v>
+        <v>0.002382734480211703</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03827467576982355</v>
+        <v>0.03422483278660506</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002301409920413397</v>
+        <v>0.002173060159329834</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02303254351629569</v>
+        <v>0.02056764192090162</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0375459392552239</v>
+        <v>0.02350804493584362</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02333936885900026</v>
+        <v>0.0184349093473433</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0148055541403223</v>
+        <v>0.01328953921604462</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05966366159790328</v>
+        <v>0.05766980976054693</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.07275215183191787</v>
+        <v>0.06951387151789437</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.08241915831101727</v>
+        <v>0.07878632984494488</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.07204795628678022</v>
+        <v>0.06839415505351558</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.03827467576982355</v>
+        <v>0.03422483278660506</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0520284485681473</v>
+        <v>0.04579188012603737</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.03030716570752316</v>
+        <v>0.02527031487483591</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.02333936885900026</v>
+        <v>0.0184349093473433</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.02314367102911365</v>
+        <v>0.01530152981107327</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.06608910590467183</v>
+        <v>0.01951902599527494</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.08279239134829017</v>
+        <v>0.03357615119734306</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0375459392552239</v>
+        <v>0.02350804493584362</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.04921891836283194</v>
+        <v>0.03602165606595216</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.06571201355850557</v>
+        <v>0.05213475857027509</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.1235189827520651</v>
+        <v>0.08684078563854546</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.05406555570475424</v>
+        <v>0.04840270976099847</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.05275952710891102</v>
+        <v>0.04584597760603448</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.04658419094086807</v>
+        <v>0.04042721563830712</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01415318825922552</v>
+        <v>0.01276214549301327</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.1099113723436142</v>
+        <v>0.09212713390676122</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.1394190445771818</v>
+        <v>0.1248986806312365</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.06713753604929928</v>
+        <v>0.0618775148502824</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.07994265998364299</v>
+        <v>0.0730238978738882</v>
       </c>
     </row>
     <row r="10">
@@ -1859,142 +1859,142 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.009021039329655875</v>
+        <v>0.007969434704446287</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01021629850579691</v>
+        <v>0.009239208665947459</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002478629186308102</v>
+        <v>0.0002013035458505036</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01281878279923788</v>
+        <v>0.01176057563019389</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01226192039230191</v>
+        <v>0.01027787720518142</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00598774069952125</v>
+        <v>0.005016279495085693</v>
       </c>
       <c r="I10" t="n">
-        <v>0.009642827198802571</v>
+        <v>0.008890983149246176</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01045564841619934</v>
+        <v>0.009706689689829774</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01014682835006305</v>
+        <v>0.009492118960861369</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009960513795861672</v>
+        <v>0.009192083277655571</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01145215828019318</v>
+        <v>0.01074217129145727</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01101291547049173</v>
+        <v>0.01023429899730572</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0130749667923578</v>
+        <v>0.01226923837963137</v>
       </c>
       <c r="P10" t="n">
-        <v>0.009022272293128783</v>
+        <v>0.008077276215818295</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.005729147826597796</v>
+        <v>0.00553769005121799</v>
       </c>
       <c r="R10" t="n">
-        <v>0.006419017995957697</v>
+        <v>0.002915777867061234</v>
       </c>
       <c r="S10" t="n">
-        <v>0.009371904935860705</v>
+        <v>0.008878277550642038</v>
       </c>
       <c r="T10" t="n">
-        <v>0.007773026181380123</v>
+        <v>0.006950562374544822</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01329873543914581</v>
+        <v>0.01255706421352544</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0100301307553166</v>
+        <v>0.008956724108616938</v>
       </c>
       <c r="W10" t="n">
-        <v>0.007776804671848878</v>
+        <v>0.004869167673243544</v>
       </c>
       <c r="X10" t="n">
-        <v>0.006776603447164502</v>
+        <v>0.005352589908753981</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.009472088036376876</v>
+        <v>0.008502193448769979</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.005729147826597796</v>
+        <v>0.00553769005121799</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.005388024630299737</v>
+        <v>0.005148197578419759</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.006344871020050075</v>
+        <v>0.006065205120427381</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.005224530910891324</v>
+        <v>0.004959576865429432</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.007773026181380123</v>
+        <v>0.006950562374544822</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.009314210077959476</v>
+        <v>0.00819773033977741</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.00831952151077864</v>
+        <v>0.006936871966657036</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.006776603447164502</v>
+        <v>0.005352589908753981</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.005739577181063238</v>
+        <v>0.003794744197172357</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.007572808155382515</v>
+        <v>0.002236584036336501</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.007641954396124869</v>
+        <v>0.003099166627137024</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.007776804671848878</v>
+        <v>0.004869167673243544</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.007313797220342689</v>
+        <v>0.005352719985944503</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.007341701763745845</v>
+        <v>0.005824777361403945</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.00644063607424619</v>
+        <v>0.00452812907164381</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.009022272293128783</v>
+        <v>0.008077276215818295</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.008145125219311308</v>
+        <v>0.007077797108227351</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.009367165461796305</v>
+        <v>0.008129118707340703</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.009057886316137862</v>
+        <v>0.008167634098301112</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.01226192160977859</v>
+        <v>0.01027787816684388</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0131572277260529</v>
+        <v>0.01178691468394762</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.01066838862181892</v>
+        <v>0.00983255290885931</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.009946470027015444</v>
+        <v>0.009085637275605785</v>
       </c>
     </row>
     <row r="11">
@@ -2007,142 +2007,142 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02228540629034714</v>
+        <v>0.01968754195640482</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02615855724094217</v>
+        <v>0.02365674501504237</v>
       </c>
       <c r="E11" t="n">
-        <v>0.009919723579662504</v>
+        <v>0.00805637059982031</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02500120330442084</v>
+        <v>0.02293732150021104</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02681841456917523</v>
+        <v>0.02247905409275673</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01444377289147583</v>
+        <v>0.01210039068541793</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02009492375573477</v>
+        <v>0.01852813752794519</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0252534683618503</v>
+        <v>0.02344451259480272</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0265763436669728</v>
+        <v>0.02486154362018679</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02255466116317739</v>
+        <v>0.02081462141012928</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02525794798346976</v>
+        <v>0.02369205848109996</v>
       </c>
       <c r="N11" t="n">
-        <v>0.03433264511540417</v>
+        <v>0.03190531666395741</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0252646878420156</v>
+        <v>0.02370778317401489</v>
       </c>
       <c r="P11" t="n">
-        <v>0.02729244046846891</v>
+        <v>0.02443382033985947</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.02624134166646511</v>
+        <v>0.02536440341133436</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01324200528066229</v>
+        <v>0.00601505494098595</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02049470749353479</v>
+        <v>0.01941523123549633</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02524313980439465</v>
+        <v>0.02257216348506468</v>
       </c>
       <c r="U11" t="n">
-        <v>0.03187314224472157</v>
+        <v>0.03009557530377538</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0290806382756939</v>
+        <v>0.02596848040089728</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0181816537207703</v>
+        <v>0.01138379119431268</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02134147355874893</v>
+        <v>0.01685684530593229</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02108345702660399</v>
+        <v>0.01892461614805494</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.02624134166646511</v>
+        <v>0.02536440341133436</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02896672703586639</v>
+        <v>0.02767738535235642</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.02843147029973687</v>
+        <v>0.02717828285213625</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02078427136569875</v>
+        <v>0.01973022902692345</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.02524313980439465</v>
+        <v>0.02257216348506468</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.02588831020275667</v>
+        <v>0.02278511910493659</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02018413271009196</v>
+        <v>0.01682966312263528</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02134147355874893</v>
+        <v>0.01685684530593229</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.01856486115132812</v>
+        <v>0.01227423151617284</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.01401557069327754</v>
+        <v>0.004139415792601293</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.01416414275389999</v>
+        <v>0.005744216237033705</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0181816537207703</v>
+        <v>0.01138379119431268</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.02785585587389</v>
+        <v>0.02038675560310028</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.01641705577250414</v>
+        <v>0.01302500399523154</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.01630862307618536</v>
+        <v>0.01146587843474748</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.02729244046846891</v>
+        <v>0.02443382033985947</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.02593743083362185</v>
+        <v>0.02253861886786043</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.03083189386015849</v>
+        <v>0.02675688031598984</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.02017132118707532</v>
+        <v>0.01818878764704873</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.02681841467332463</v>
+        <v>0.02247905405140705</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.02276009880931979</v>
+        <v>0.02038965566678309</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.01514242000466536</v>
+        <v>0.01395605757738667</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.01401118047020718</v>
+        <v>0.01279856101808936</v>
       </c>
     </row>
     <row r="12">
@@ -2155,142 +2155,142 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.05310428953584975</v>
+        <v>0.04691379258160368</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06044338435626871</v>
+        <v>0.05466256102704491</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02175430878854139</v>
+        <v>0.01766790902346699</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04349132159690576</v>
+        <v>0.03990105651278403</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05552054586596309</v>
+        <v>0.04653702964286559</v>
       </c>
       <c r="H12" t="n">
-        <v>0.06646702539127451</v>
+        <v>0.05568330248439931</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04192880320898806</v>
+        <v>0.0386596456737775</v>
       </c>
       <c r="J12" t="n">
-        <v>0.07387846220246691</v>
+        <v>0.06858640218335094</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0829407068154818</v>
+        <v>0.07758907794922799</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08303689020115648</v>
+        <v>0.07663078687403616</v>
       </c>
       <c r="M12" t="n">
-        <v>0.08964377743594583</v>
+        <v>0.0840862297629682</v>
       </c>
       <c r="N12" t="n">
-        <v>0.03858712025363387</v>
+        <v>0.03585899911597592</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06544453601283337</v>
+        <v>0.06141159864781777</v>
       </c>
       <c r="P12" t="n">
-        <v>0.06717217410021026</v>
+        <v>0.06013653618475307</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07763392576943404</v>
+        <v>0.07503954015194099</v>
       </c>
       <c r="R12" t="n">
-        <v>0.07404671687047988</v>
+        <v>0.03363501680715925</v>
       </c>
       <c r="S12" t="n">
-        <v>0.08935527667137125</v>
+        <v>0.08464884698811617</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0668180499991209</v>
+        <v>0.05974803293173584</v>
       </c>
       <c r="U12" t="n">
-        <v>0.06048924998328452</v>
+        <v>0.05711576109952931</v>
       </c>
       <c r="V12" t="n">
-        <v>0.07070995228083179</v>
+        <v>0.06314269970779542</v>
       </c>
       <c r="W12" t="n">
-        <v>0.06620439260751403</v>
+        <v>0.0414515089311858</v>
       </c>
       <c r="X12" t="n">
-        <v>0.06379545496073366</v>
+        <v>0.05038968431745432</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.03649393048041612</v>
+        <v>0.03275713395598297</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.07763392576943404</v>
+        <v>0.07503954015194099</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.05131832693384045</v>
+        <v>0.04903409033500532</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.06464326504799545</v>
+        <v>0.06179395308923904</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.05226446938493048</v>
+        <v>0.04961395724639781</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0668180499991209</v>
+        <v>0.05974803293173584</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.06525070607893296</v>
+        <v>0.05742920638873461</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.05790916971938391</v>
+        <v>0.04828504806656626</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.06379545496073366</v>
+        <v>0.05038968431745432</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.05175993284729936</v>
+        <v>0.03422128470828135</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.07145374344274349</v>
+        <v>0.02110343991837881</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.05701618669234981</v>
+        <v>0.02312270576923989</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.06620439260751403</v>
+        <v>0.0414515089311858</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.05908570174412018</v>
+        <v>0.04324281998544241</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.07209382826575177</v>
+        <v>0.0571979783832897</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.05729900884105115</v>
+        <v>0.04028442295428192</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.06717217410021026</v>
+        <v>0.06013653618475307</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.06097394000938987</v>
+        <v>0.05298398301507968</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.05652603260007307</v>
+        <v>0.04905505629585478</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.03488879426493688</v>
+        <v>0.03145975735853711</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.05552054837799494</v>
+        <v>0.04653703148210696</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.05520674953066301</v>
+        <v>0.04945701786459859</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.04353592149358603</v>
+        <v>0.04012501481677797</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.04056921826579754</v>
+        <v>0.03705809203835898</v>
       </c>
     </row>
     <row r="13">
@@ -2303,142 +2303,142 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02910246887685529</v>
+        <v>0.02570992287882265</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03006943273924848</v>
+        <v>0.02719358321283881</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03033359629483329</v>
+        <v>0.0246356353999158</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03186765303988413</v>
+        <v>0.02923693689190343</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02429500076331995</v>
+        <v>0.0203639419076603</v>
       </c>
       <c r="H13" t="n">
-        <v>0.06014682646107694</v>
+        <v>0.05038850334572796</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02035175968976378</v>
+        <v>0.01876494815562671</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03291041050633827</v>
+        <v>0.0305529728653654</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02040079062128435</v>
+        <v>0.01908445918193271</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02482281227711652</v>
+        <v>0.02290778993064254</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03440282440950681</v>
+        <v>0.03226998995953589</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03285500806917804</v>
+        <v>0.03053214900630186</v>
       </c>
       <c r="O13" t="n">
-        <v>0.03947166762126814</v>
+        <v>0.03703927566148601</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01663059760009739</v>
+        <v>0.01488870276642116</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02180791284220412</v>
+        <v>0.02107913177304386</v>
       </c>
       <c r="R13" t="n">
-        <v>0.009109485673411299</v>
+        <v>0.004137897217856486</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01507191155314547</v>
+        <v>0.01427805925298415</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01710980049185285</v>
+        <v>0.01529941270743615</v>
       </c>
       <c r="U13" t="n">
-        <v>0.001548742673483651</v>
+        <v>0.00146236920721918</v>
       </c>
       <c r="V13" t="n">
-        <v>0.008230849605569562</v>
+        <v>0.007349998808094112</v>
       </c>
       <c r="W13" t="n">
-        <v>0.009419508124722413</v>
+        <v>0.005897687597166973</v>
       </c>
       <c r="X13" t="n">
-        <v>0.008301430806169557</v>
+        <v>0.00655699497657856</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.02250482913261247</v>
+        <v>0.02020044683729252</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.02180791284220412</v>
+        <v>0.02107913177304386</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.02153731733171638</v>
+        <v>0.02057866705160773</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.02148512611637346</v>
+        <v>0.02053811598726998</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.02391960273037479</v>
+        <v>0.02270655688619336</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01710980049185285</v>
+        <v>0.01529941270743615</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.02229849905179213</v>
+        <v>0.01962561298042148</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01449108014120164</v>
+        <v>0.01208275830140549</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.008301430806169557</v>
+        <v>0.00655699497657856</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01875012356223663</v>
+        <v>0.01239671849327435</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.01143456983908426</v>
+        <v>0.003377132477110651</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.01145572745811263</v>
+        <v>0.004645828329695755</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.009419508124722413</v>
+        <v>0.005897687597166973</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01024094446546784</v>
+        <v>0.007494999719542261</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.01269813532162527</v>
+        <v>0.01007447776191187</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.01182270975690819</v>
+        <v>0.00831202929939317</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.01663059760009739</v>
+        <v>0.01488870276642116</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.01891671498210241</v>
+        <v>0.01643788977977261</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.01757665930445123</v>
+        <v>0.01525357383160482</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.02150623614004112</v>
+        <v>0.01939250079906193</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.02429500107437093</v>
+        <v>0.02036394205183918</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.03348011106390113</v>
+        <v>0.02999318860597689</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.05199611530102399</v>
+        <v>0.04792237824059509</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.04941351478113554</v>
+        <v>0.04513694512674223</v>
       </c>
     </row>
     <row r="14">
@@ -2451,142 +2451,142 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.01784284045986879</v>
+        <v>0.01596740251737053</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02070856113624542</v>
+        <v>0.01899487939553832</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01437346660013009</v>
+        <v>0.01167350811792752</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01968306093766948</v>
+        <v>0.01860180547733113</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01382464302077743</v>
+        <v>0.01163738268700695</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00416202208912137</v>
+        <v>0.003486768567887808</v>
       </c>
       <c r="I14" t="n">
-        <v>0.005928799047677642</v>
+        <v>0.005466535004870198</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02947136024554572</v>
+        <v>0.02770434591344084</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0196608032878576</v>
+        <v>0.01911657037372011</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02454992614965159</v>
+        <v>0.02265595633446633</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02692924671923824</v>
+        <v>0.02551903024389265</v>
       </c>
       <c r="N14" t="n">
-        <v>0.03172869302284028</v>
+        <v>0.02948546477629293</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02558818910975762</v>
+        <v>0.0240489914323811</v>
       </c>
       <c r="P14" t="n">
-        <v>0.014935145923615</v>
+        <v>0.01337083331440406</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01593905197792123</v>
+        <v>0.01584074372882486</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01814786573329269</v>
+        <v>0.008243495387122535</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01011271996783408</v>
+        <v>0.009580073131429513</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01340097290421955</v>
+        <v>0.01228949868310249</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01806145135773646</v>
+        <v>0.01705416319667236</v>
       </c>
       <c r="V14" t="n">
-        <v>0.007545000572334083</v>
+        <v>0.006737548111218034</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01338528335165158</v>
+        <v>0.008380715697925836</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01471464303138976</v>
+        <v>0.01162255551985849</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.01114989727958077</v>
+        <v>0.01002657957110216</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.01593905197792123</v>
+        <v>0.01584074372882486</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01755864173841379</v>
+        <v>0.01733421718434069</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.02029767301922814</v>
+        <v>0.02001253595189928</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.01485576013713478</v>
+        <v>0.01459227131093671</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.01340097290421955</v>
+        <v>0.01228949868310249</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.01467012208608817</v>
+        <v>0.01328052963155595</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.006959718536973039</v>
+        <v>0.005803059268781564</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.01471464303138976</v>
+        <v>0.01162255551985849</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.01277625779196844</v>
+        <v>0.008447073466946408</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.01771632333267224</v>
+        <v>0.005232411165766437</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01840917164751333</v>
+        <v>0.007465772163223231</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.01338528335165158</v>
+        <v>0.008380715697925836</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01314992616472355</v>
+        <v>0.009623984706580671</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.009075084192289693</v>
+        <v>0.007528493149464917</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.008798736283257337</v>
+        <v>0.006186006024662376</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.014935145923615</v>
+        <v>0.01337083331440406</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.01482992054605435</v>
+        <v>0.01288662432190082</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.01666381178647386</v>
+        <v>0.01446137624893113</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.01065558164757416</v>
+        <v>0.009625926052572285</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.01382464490014955</v>
+        <v>0.01163738420548913</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.0104178016771196</v>
+        <v>0.009381443922646136</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.007292648711685528</v>
+        <v>0.006755180260962427</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.007336846351368329</v>
+        <v>0.006732321300935751</v>
       </c>
     </row>
     <row r="15">
@@ -2599,142 +2599,142 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.05167687975113278</v>
+        <v>0.04565277944774081</v>
       </c>
       <c r="D15" t="n">
-        <v>0.04032364945447692</v>
+        <v>0.03646708357934478</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02765658121670773</v>
+        <v>0.02246147949753732</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0355429122714565</v>
+        <v>0.03260879870050237</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08334496753351728</v>
+        <v>0.06985931359635199</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0509167141023696</v>
+        <v>0.04265590006749601</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01664141612952561</v>
+        <v>0.0153438973173323</v>
       </c>
       <c r="J15" t="n">
-        <v>0.04712758202679419</v>
+        <v>0.04375174033753283</v>
       </c>
       <c r="K15" t="n">
-        <v>0.06246911533508041</v>
+        <v>0.05843838623097117</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05507349205584143</v>
+        <v>0.05082469998474639</v>
       </c>
       <c r="M15" t="n">
-        <v>0.03619690896569128</v>
+        <v>0.03395284860874122</v>
       </c>
       <c r="N15" t="n">
-        <v>0.04573051934713483</v>
+        <v>0.04249735772100271</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02957356766557349</v>
+        <v>0.02775113368832104</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0410350972949937</v>
+        <v>0.0367370662983726</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.03667569105190465</v>
+        <v>0.03545005568136742</v>
       </c>
       <c r="R15" t="n">
-        <v>0.05994078585903774</v>
+        <v>0.02722753182061511</v>
       </c>
       <c r="S15" t="n">
-        <v>0.05652337642968561</v>
+        <v>0.05354623499454857</v>
       </c>
       <c r="T15" t="n">
-        <v>0.04297644687004838</v>
+        <v>0.03842910954322114</v>
       </c>
       <c r="U15" t="n">
-        <v>0.02646522375508951</v>
+        <v>0.02498925673336978</v>
       </c>
       <c r="V15" t="n">
-        <v>0.07770883059323964</v>
+        <v>0.06939257058617772</v>
       </c>
       <c r="W15" t="n">
-        <v>0.04672556207253192</v>
+        <v>0.02925553694067734</v>
       </c>
       <c r="X15" t="n">
-        <v>0.05678525001590317</v>
+        <v>0.04485258117447827</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2462547418350313</v>
+        <v>0.2210394840839337</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.03667569105190465</v>
+        <v>0.03545005568136742</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.03676172872531899</v>
+        <v>0.03512542272689704</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.03947389635757399</v>
+        <v>0.03773398664127424</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.05722413671191072</v>
+        <v>0.05432210267699323</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.04297644687004838</v>
+        <v>0.03842910954322114</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.05403507509350481</v>
+        <v>0.04755797548032309</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.03062419789391522</v>
+        <v>0.02553465840510527</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.05678525001590317</v>
+        <v>0.04485258117447827</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.04153647625038677</v>
+        <v>0.0274620058672935</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.05624291192469601</v>
+        <v>0.01661101092049267</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.06209605916317356</v>
+        <v>0.02518282945169372</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.04672556207253192</v>
+        <v>0.02925553694067734</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.05848371784461352</v>
+        <v>0.04280224839820403</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.04797234074286425</v>
+        <v>0.03806041341973873</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.04793846671096264</v>
+        <v>0.03370343585037058</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0410350972949937</v>
+        <v>0.0367370662983726</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.04990714076955263</v>
+        <v>0.04336736478662775</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.04996999570497321</v>
+        <v>0.04336552274514158</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.2346681022961739</v>
+        <v>0.2116038032717424</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.08334494938380498</v>
+        <v>0.06985929798355527</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.05461106381134338</v>
+        <v>0.04892337225944093</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.03106735080445185</v>
+        <v>0.02863331861553277</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.02492663626526308</v>
+        <v>0.0227693216781449</v>
       </c>
     </row>
     <row r="16">
@@ -2747,130 +2747,132 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002766093476537901</v>
+        <v>0.002648188816115491</v>
       </c>
       <c r="D16" t="n">
-        <v>0.003187971757578111</v>
+        <v>0.003149964416983359</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0009162641637808602</v>
+        <v>0.0007441501380025561</v>
       </c>
       <c r="F16" t="n">
-        <v>0.002021165936400868</v>
+        <v>0.002397922847592523</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0008377329754391284</v>
+        <v>0.0007518229663189841</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0004629459398344093</v>
+        <v>0.0003878368055433996</v>
       </c>
       <c r="I16" t="n">
-        <v>2.964201437151747e-05</v>
+        <v>2.733084860419375e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00139573177247945</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+        <v>0.001639830104667513</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0007243519153011242</v>
+      </c>
       <c r="L16" t="n">
-        <v>0.002610588027345836</v>
+        <v>0.002409187220942709</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0008001798594078881</v>
+        <v>0.001009858695007763</v>
       </c>
       <c r="N16" t="n">
-        <v>0.002599324892452216</v>
+        <v>0.002415551832007998</v>
       </c>
       <c r="O16" t="n">
-        <v>0.00123601828516013</v>
+        <v>0.001197492560267215</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0007816178731331894</v>
+        <v>0.0006997509331795862</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.001295261588435024</v>
+        <v>0.001686322372213509</v>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>0.0004994132776753184</v>
+        <v>0.000473108692632095</v>
       </c>
       <c r="T16" t="n">
-        <v>0.001530829802151654</v>
+        <v>0.001675335280008557</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0009556986249872683</v>
+        <v>0.0009023992587609453</v>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
-        <v>0.0009256943658943437</v>
+        <v>0.0005795903680122683</v>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>0.0007364969572466207</v>
+        <v>0.0006794595211248414</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.001295261588435024</v>
+        <v>0.001686322372213509</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.001631087901997962</v>
+        <v>0.002115616729237587</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.001361621037498913</v>
+        <v>0.001911137345477046</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.002246772909427477</v>
+        <v>0.002622729467348767</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.001530829802151654</v>
+        <v>0.001675335280008557</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.001999062622989027</v>
+        <v>0.002128330171982691</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0006514117163988249</v>
+        <v>0.0005431513901832597</v>
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>0.002850782673469449</v>
+        <v>0.001884806261206804</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.00132539606558899</v>
+        <v>0.0003914478778935616</v>
       </c>
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="n">
-        <v>0.0009256943658943437</v>
+        <v>0.0005795903680122683</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0009499632582299198</v>
+        <v>0.0006952458709269487</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.000391227116220235</v>
+        <v>0.0006388733128033177</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.0002514941490646941</v>
+        <v>0.0001768145187214988</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.0007816178731331894</v>
+        <v>0.0006997509331795862</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.001203511422777538</v>
+        <v>0.001045804630192497</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.001154197922858779</v>
+        <v>0.001001649000965316</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.0007041131936364559</v>
+        <v>0.000652535325892692</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0008377329195907229</v>
+        <v>0.0007518229250073262</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.002104146289185442</v>
+        <v>0.001933648018400699</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.001308025647298633</v>
+        <v>0.001239434162267051</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.001328323704285455</v>
+        <v>0.00124381561144156</v>
       </c>
     </row>
     <row r="17">
@@ -2883,142 +2885,142 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01708019186164754</v>
+        <v>0.01508911210854986</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02006351926620491</v>
+        <v>0.01814463829228772</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01218567723610228</v>
+        <v>0.009896680188257229</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02218543858422328</v>
+        <v>0.02035400181476603</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02452019936972641</v>
+        <v>0.02055270219555751</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0064119575698901</v>
+        <v>0.005371670701066077</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01085297091600611</v>
+        <v>0.01000677286278153</v>
       </c>
       <c r="J17" t="n">
-        <v>0.03051228727163257</v>
+        <v>0.02832663192976222</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02164498819908814</v>
+        <v>0.02024837671477004</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02188241146885939</v>
+        <v>0.02019423421924793</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0270884165327319</v>
+        <v>0.02540904546457602</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01651783628503248</v>
+        <v>0.01535002023601476</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02797127344449361</v>
+        <v>0.0262475788369064</v>
       </c>
       <c r="P17" t="n">
-        <v>0.01871998117882229</v>
+        <v>0.01675924355014466</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01234010092294492</v>
+        <v>0.01192771703232495</v>
       </c>
       <c r="R17" t="n">
-        <v>0.01319561207315437</v>
+        <v>0.00599398126776697</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01805217456649569</v>
+        <v>0.0171013489030094</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01555780202942182</v>
+        <v>0.01391163118366296</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0218849588716594</v>
+        <v>0.02066443348086046</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01602998082981364</v>
+        <v>0.01431448096356618</v>
       </c>
       <c r="W17" t="n">
-        <v>0.01416701528285755</v>
+        <v>0.008870169144319963</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01684770517129578</v>
+        <v>0.01330738287825786</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.01771681378228207</v>
+        <v>0.01590270038605066</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.01234010092294492</v>
+        <v>0.01192771703232495</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.01445383240278169</v>
+        <v>0.01381047602426165</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.01566879479052719</v>
+        <v>0.01497815386540063</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.010838490578209</v>
+        <v>0.01028883320716912</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.01555780202942182</v>
+        <v>0.01391163118366296</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.01658303723688773</v>
+        <v>0.01459525459965522</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.01184344196586876</v>
+        <v>0.009875140109358926</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.01684770517129578</v>
+        <v>0.01330738287825786</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.02268043438582708</v>
+        <v>0.01499525906872153</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.01602346006807406</v>
+        <v>0.004732434027086429</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.01644910577775183</v>
+        <v>0.006670874625803288</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.01416701528285755</v>
+        <v>0.008870169144319963</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01745328198941562</v>
+        <v>0.01277346479681219</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.01414159477302865</v>
+        <v>0.01121969316362675</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.01340120447502596</v>
+        <v>0.009421799784815577</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.01871998117882229</v>
+        <v>0.01675924355014466</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.01871345265472716</v>
+        <v>0.01626126272074382</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.01887629851256433</v>
+        <v>0.01638144132178146</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.01693471329919984</v>
+        <v>0.0152702890012064</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.02452020057160836</v>
+        <v>0.02055270308534596</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.01694058239976491</v>
+        <v>0.01517623648384747</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.01157074203491896</v>
+        <v>0.01066420968396497</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.01093942385804952</v>
+        <v>0.009992654369679886</v>
       </c>
     </row>
     <row r="18">
@@ -3031,124 +3033,124 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002137926881016008</v>
+        <v>0.001888703513920666</v>
       </c>
       <c r="D18" t="n">
-        <v>0.002567531231960712</v>
+        <v>0.002321971778228869</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00506479216496936</v>
+        <v>0.004113405213802103</v>
       </c>
       <c r="F18" t="n">
-        <v>0.002642352916122209</v>
+        <v>0.002424223251022408</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0007392890421509485</v>
+        <v>0.0006196681882826364</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>0.003591127537242576</v>
+        <v>0.003333887986000897</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00103443460933299</v>
+        <v>0.0009676892158089861</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0006034067719176221</v>
+        <v>0.0005568553401404404</v>
       </c>
       <c r="M18" t="n">
-        <v>0.003123760061646569</v>
+        <v>0.002930099709995847</v>
       </c>
       <c r="N18" t="n">
-        <v>0.003768359755982225</v>
+        <v>0.003501935575141041</v>
       </c>
       <c r="O18" t="n">
-        <v>0.001844320105943037</v>
+        <v>0.001730666194990889</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0007536401223400451</v>
+        <v>0.0006747035821673959</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.001783739622861434</v>
+        <v>0.001724130265521345</v>
       </c>
       <c r="R18" t="n">
-        <v>0.001171969580652614</v>
+        <v>0.000532356034254441</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="n">
-        <v>0.001147932203298847</v>
+        <v>0.001026469510663689</v>
       </c>
       <c r="U18" t="n">
-        <v>0.001128955015910266</v>
+        <v>0.001065993130988806</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
-        <v>0.0006325902176734368</v>
+        <v>0.0003960737048540662</v>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="n">
-        <v>0.0004641037147875194</v>
+        <v>0.0004165818083892711</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.001783739622861434</v>
+        <v>0.001724130265521345</v>
       </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="n">
-        <v>0.002747610689185618</v>
+        <v>0.002626502945186442</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.002086098047743649</v>
+        <v>0.0019803047954102</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.001147932203298847</v>
+        <v>0.001026469510663689</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0006338027551833143</v>
+        <v>0.0005578298140274535</v>
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="n">
-        <v>0.001127130731083267</v>
+        <v>0.000745206949275753</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.002542456258525957</v>
+        <v>0.0007508993974528795</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.003815251083103393</v>
+        <v>0.001547261108610941</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.0006325902176734368</v>
+        <v>0.0003960737048540662</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.0009180770081907508</v>
+        <v>0.0006719094066089666</v>
       </c>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="n">
-        <v>0.0009517604229568378</v>
+        <v>0.0006691410585460338</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.0007536401223400451</v>
+        <v>0.0006747035821673959</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.0008370757582724518</v>
+        <v>0.000727386285875777</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.0015463267633083</v>
+        <v>0.001341950654180133</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.0004436604993802621</v>
+        <v>0.0004000554319556307</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.0007392890739311543</v>
+        <v>0.0006196682113742896</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.0006620343761490959</v>
+        <v>0.0005930841110288237</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.0004887602807827548</v>
+        <v>0.0004504674033636771</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.0004798035354233563</v>
+        <v>0.0004382781906113028</v>
       </c>
     </row>
     <row r="19">
@@ -3161,138 +3163,138 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.003879403795387576</v>
+        <v>0.003427172203748919</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0036775938220703</v>
+        <v>0.003325867650737401</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0.004365460147291132</v>
+        <v>0.00400508574229583</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001976199992150507</v>
+        <v>0.001656440443452466</v>
       </c>
       <c r="H19" t="n">
-        <v>0.002599616627405156</v>
+        <v>0.002177850417633975</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>0.003135344980242272</v>
+        <v>0.002910754032875178</v>
       </c>
       <c r="K19" t="n">
-        <v>0.002063647298058606</v>
+        <v>0.001930493447867452</v>
       </c>
       <c r="L19" t="n">
-        <v>0.003397398876847661</v>
+        <v>0.003135297439814007</v>
       </c>
       <c r="M19" t="n">
-        <v>0.003206918024085582</v>
+        <v>0.003008102218773029</v>
       </c>
       <c r="N19" t="n">
-        <v>0.003393542188845868</v>
+        <v>0.003153617723996679</v>
       </c>
       <c r="O19" t="n">
-        <v>0.001614875362903176</v>
+        <v>0.001515360696168917</v>
       </c>
       <c r="P19" t="n">
-        <v>0.007382994594420699</v>
+        <v>0.006609697058738297</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.006344163311165156</v>
+        <v>0.006132152828809847</v>
       </c>
       <c r="R19" t="n">
-        <v>0.003069891879597746</v>
+        <v>0.001394469185541929</v>
       </c>
       <c r="S19" t="n">
-        <v>0.01073890269024084</v>
+        <v>0.01017327419834081</v>
       </c>
       <c r="T19" t="n">
-        <v>0.004252380121645282</v>
+        <v>0.003802435832079264</v>
       </c>
       <c r="U19" t="n">
-        <v>0.01022425848364841</v>
+        <v>0.009654051011266809</v>
       </c>
       <c r="V19" t="n">
-        <v>0.006424086352896741</v>
+        <v>0.005736592125913028</v>
       </c>
       <c r="W19" t="n">
-        <v>0.01573866657255278</v>
+        <v>0.009854202301420737</v>
       </c>
       <c r="X19" t="n">
-        <v>0.005238515988142442</v>
+        <v>0.004137711175457683</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.0001854954938824282</v>
+        <v>0.0001665016801793567</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.006344163311165156</v>
+        <v>0.006132152828809847</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.009097586243988657</v>
+        <v>0.008692642421748137</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.008244342958848759</v>
+        <v>0.007880953130576688</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.01656560540294354</v>
+        <v>0.01572550621664425</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.004252380121645282</v>
+        <v>0.003802435832079264</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.006194388604205636</v>
+        <v>0.005451876967777461</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.00701681482043674</v>
+        <v>0.00585066652692093</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.005238515988142442</v>
+        <v>0.004137711175457683</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.01342821475003212</v>
+        <v>0.008878117393244822</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.002791531926620293</v>
+        <v>0.0008244624207949783</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.004239623081242507</v>
+        <v>0.001719363618773933</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.01573866657255278</v>
+        <v>0.009854202301420737</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.002141416557363255</v>
+        <v>0.001567230107631244</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.008412571548816642</v>
+        <v>0.006674386659331813</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.01107447319635561</v>
+        <v>0.007785976952505757</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.007382994594420699</v>
+        <v>0.006609697058738297</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.007401450850703376</v>
+        <v>0.006431572998238645</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.005946146685857213</v>
+        <v>0.005160251781366997</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.0001775311928232001</v>
+        <v>0.0001600825814551733</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.001976200119542009</v>
+        <v>0.001656440540751577</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.001521609528958794</v>
+        <v>0.001363135310381943</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.0009456769587330454</v>
+        <v>0.0008715860530628554</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.001228678641037252</v>
+        <v>0.001122340732986495</v>
       </c>
     </row>
     <row r="20">
@@ -3305,140 +3307,140 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.008056343736784313</v>
+        <v>0.007117196037025438</v>
       </c>
       <c r="D20" t="n">
-        <v>0.008363947368883878</v>
+        <v>0.007564016944911361</v>
       </c>
       <c r="E20" t="n">
-        <v>0.006447209205659003</v>
+        <v>0.005236144563730797</v>
       </c>
       <c r="F20" t="n">
-        <v>0.002999172886723576</v>
+        <v>0.002751587269614753</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003835404305280821</v>
+        <v>0.003214815723860707</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01363117330818369</v>
+        <v>0.01141962863643517</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01149913324326278</v>
+        <v>0.01060255439498923</v>
       </c>
       <c r="J20" t="n">
-        <v>0.00482523138409845</v>
+        <v>0.004479590539263454</v>
       </c>
       <c r="K20" t="n">
-        <v>0.003090628942825121</v>
+        <v>0.002891210590843884</v>
       </c>
       <c r="L20" t="n">
-        <v>0.008788623236197295</v>
+        <v>0.008110601354382808</v>
       </c>
       <c r="M20" t="n">
-        <v>0.006398348043353358</v>
+        <v>0.006001676625700885</v>
       </c>
       <c r="N20" t="n">
-        <v>0.005288798709248561</v>
+        <v>0.004914879031991477</v>
       </c>
       <c r="O20" t="n">
-        <v>0.004374849619186126</v>
+        <v>0.004105255004105041</v>
       </c>
       <c r="P20" t="n">
-        <v>0.009477948377982151</v>
+        <v>0.008485224622020402</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.002725611800445554</v>
+        <v>0.002634526775646649</v>
       </c>
       <c r="R20" t="n">
-        <v>0.002902439715079749</v>
+        <v>0.001318405632612097</v>
       </c>
       <c r="S20" t="n">
-        <v>0.006569127784123521</v>
+        <v>0.006223125408572706</v>
       </c>
       <c r="T20" t="n">
-        <v>0.01368182311216861</v>
+        <v>0.01223414957309873</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.01118756003046802</v>
+        <v>0.009990287373709241</v>
       </c>
       <c r="W20" t="n">
-        <v>0.01536326688793639</v>
+        <v>0.009619159236047548</v>
       </c>
       <c r="X20" t="n">
-        <v>0.004658397437094052</v>
+        <v>0.003679496861099086</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.002854497044075698</v>
+        <v>0.002562210779130057</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.002725611800445554</v>
+        <v>0.002634526775646649</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.002778260455020217</v>
+        <v>0.002654596949375634</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.002648350821220976</v>
+        <v>0.002531618201662161</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.004016468470198725</v>
+        <v>0.003812779452409425</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.01368182311216861</v>
+        <v>0.01223414957309873</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.0128349655853831</v>
+        <v>0.01129645841232138</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.02370360439395193</v>
+        <v>0.01976422185051175</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.004658397437094052</v>
+        <v>0.003679496861099086</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.004714782546747925</v>
+        <v>0.003117197163796458</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.003373347257161458</v>
+        <v>0.0009962981326846697</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.003034106669638594</v>
+        <v>0.001230470851603881</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.01536326688793639</v>
+        <v>0.009619159236047548</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.01566454726110713</v>
+        <v>0.011464350551323</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.005146080478732718</v>
+        <v>0.004082809958381031</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.007130872084003235</v>
+        <v>0.005013403772161974</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.009477948377982151</v>
+        <v>0.008485224622020402</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.00844522369195921</v>
+        <v>0.007338571012212878</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.008188833447557768</v>
+        <v>0.007106525388212119</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.002729556280768385</v>
+        <v>0.002461282486214912</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.003835404630979903</v>
+        <v>0.00321481597846164</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.005851669140901771</v>
+        <v>0.005242223237188721</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.02306528563034117</v>
+        <v>0.02125819084378414</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.02319563529619161</v>
+        <v>0.02118813288594133</v>
       </c>
     </row>
     <row r="21">
@@ -3451,142 +3453,142 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01125626327118107</v>
+        <v>0.009944093122489086</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01353785503292563</v>
+        <v>0.0122430905349501</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01182054143421883</v>
+        <v>0.009600132677067845</v>
       </c>
       <c r="F21" t="n">
-        <v>0.008723372222021283</v>
+        <v>0.008003246515223985</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01418790380845791</v>
+        <v>0.0118922263786514</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01136579683049371</v>
+        <v>0.009521790679859291</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01073292126480279</v>
+        <v>0.009896083393405348</v>
       </c>
       <c r="J21" t="n">
-        <v>0.01582832960068879</v>
+        <v>0.0146945151200945</v>
       </c>
       <c r="K21" t="n">
-        <v>0.02288046053994979</v>
+        <v>0.02140413199392973</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01945496887303707</v>
+        <v>0.01795406318491858</v>
       </c>
       <c r="M21" t="n">
-        <v>0.02047484687160692</v>
+        <v>0.01920549008142503</v>
       </c>
       <c r="N21" t="n">
-        <v>0.008299209016887917</v>
+        <v>0.007712452415307077</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01206260834191457</v>
+        <v>0.01131926524766272</v>
       </c>
       <c r="P21" t="n">
-        <v>0.01399655568995452</v>
+        <v>0.0125305513627588</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.0160220138500597</v>
+        <v>0.01548658707775759</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0224561695215011</v>
+        <v>0.01020050140239543</v>
       </c>
       <c r="S21" t="n">
-        <v>0.03529635362799895</v>
+        <v>0.03343726021333207</v>
       </c>
       <c r="T21" t="n">
-        <v>0.01600111435589156</v>
+        <v>0.01430803663819668</v>
       </c>
       <c r="U21" t="n">
-        <v>0.01189579452334254</v>
+        <v>0.01123236539173616</v>
       </c>
       <c r="V21" t="n">
-        <v>0.01789907520234517</v>
+        <v>0.01598354820068666</v>
       </c>
       <c r="W21" t="n">
-        <v>0.01579688508944475</v>
+        <v>0.009890653740333785</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0214740743571604</v>
+        <v>0.01696158180128777</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.0007388548806890671</v>
+        <v>0.0006631998247969375</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.0160220138500597</v>
+        <v>0.01548658707775759</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.01303271148499549</v>
+        <v>0.01245261080099493</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.002825458597603543</v>
+        <v>0.002700919514295396</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.007623616635369856</v>
+        <v>0.007236996649184875</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.01600111435589156</v>
+        <v>0.01430803663819668</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.01397596808631593</v>
+        <v>0.01230069073490908</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.01149684668678232</v>
+        <v>0.009586146677205953</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.0214740743571604</v>
+        <v>0.01696158180128777</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.01728816921965882</v>
+        <v>0.01143014158647154</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.02047301889849552</v>
+        <v>0.006046584873729402</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.01702221629506257</v>
+        <v>0.006903297497864835</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.01579688508944475</v>
+        <v>0.009890653740333785</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.01400803191555628</v>
+        <v>0.01025200318510243</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.02765022729721892</v>
+        <v>0.02193720518501976</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.02141064533672481</v>
+        <v>0.0150528867761288</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.01399655568995452</v>
+        <v>0.0125305513627588</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.0133781723285729</v>
+        <v>0.01162511156931564</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.01314303137665067</v>
+        <v>0.01140593306169787</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.0007068255600903351</v>
+        <v>0.0006373553768122537</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.01418790506475364</v>
+        <v>0.0118922273636129</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.01851945968462022</v>
+        <v>0.01659067516656193</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.01297447497277368</v>
+        <v>0.01195796442712615</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.01074671972226234</v>
+        <v>0.009816628113679929</v>
       </c>
     </row>
     <row r="22">
@@ -3599,140 +3601,140 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001383072071831437</v>
+        <v>0.001221843976643471</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00183391256871047</v>
+        <v>0.001658516623002498</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.001575721585671336</v>
+        <v>0.001445643722235353</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0005749377088865205</v>
+        <v>0.0004819097648255641</v>
       </c>
       <c r="H22" t="n">
-        <v>9.021720104806079e-05</v>
+        <v>7.558020936972019e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>0.001186552074565863</v>
+        <v>0.001094037493690462</v>
       </c>
       <c r="J22" t="n">
-        <v>0.001744871371326534</v>
+        <v>0.001619882792146431</v>
       </c>
       <c r="K22" t="n">
-        <v>0.000833196857723575</v>
+        <v>0.0007794360383832566</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0005429140428561609</v>
+        <v>0.0005010294847054898</v>
       </c>
       <c r="M22" t="n">
-        <v>0.001449646681204657</v>
+        <v>0.001359774514165229</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0006678437955871442</v>
+        <v>0.0006206270361239028</v>
       </c>
       <c r="O22" t="n">
-        <v>0.002032587625545444</v>
+        <v>0.001907331965071007</v>
       </c>
       <c r="P22" t="n">
-        <v>0.001926853145358021</v>
+        <v>0.001725033846986429</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.002380604675160835</v>
+        <v>0.002301049165517837</v>
       </c>
       <c r="R22" t="n">
-        <v>0.003409205394641369</v>
+        <v>0.001548599122205448</v>
       </c>
       <c r="S22" t="n">
-        <v>0.001227406553278655</v>
+        <v>0.001162757851478784</v>
       </c>
       <c r="T22" t="n">
-        <v>0.002359694134764634</v>
+        <v>0.002110014926724083</v>
       </c>
       <c r="U22" t="n">
-        <v>0.003114195925842812</v>
+        <v>0.002940517043387342</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0007789442780396764</v>
+        <v>0.0006955830551549938</v>
       </c>
       <c r="W22" t="n">
-        <v>0.001998067697749633</v>
+        <v>0.001251018516390445</v>
       </c>
       <c r="X22" t="n">
-        <v>0.001927958496491537</v>
+        <v>0.001522823531475058</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.00100254077180941</v>
+        <v>0.0008998855953901335</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.002380604675160835</v>
+        <v>0.002301049165517837</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.002118047982302518</v>
+        <v>0.002023771278280159</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.002589662209429457</v>
+        <v>0.002475516435743855</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.003006396706657252</v>
+        <v>0.002853931924023541</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.002359694134764634</v>
+        <v>0.002110014926724083</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.003033306217706257</v>
+        <v>0.002669708563860698</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.002002928173096108</v>
+        <v>0.001670054735380762</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.001927958496491537</v>
+        <v>0.001522823531475058</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.002762026217640005</v>
+        <v>0.001826124578724754</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.003235282028398517</v>
+        <v>0.000955521385104598</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.003031535429362117</v>
+        <v>0.001229428094523409</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.001998067697749633</v>
+        <v>0.001251018516390445</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.002262916239817632</v>
+        <v>0.001656151602029605</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.001203522045681682</v>
+        <v>0.0009548532739717959</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.001022165183895355</v>
+        <v>0.0007186395616616819</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.001926853145358021</v>
+        <v>0.001725033846986429</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.002571662792650723</v>
+        <v>0.002234674972706947</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.002798720344090554</v>
+        <v>0.0024288169135638</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.0009578894906273228</v>
+        <v>0.0008637435482175386</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.0005749376986867521</v>
+        <v>0.0004819097535182122</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.000575618130322174</v>
+        <v>0.0005156680369076729</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.0003812443769568283</v>
+        <v>0.0003513750427094952</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.0004203709556632192</v>
+        <v>0.0003839892961002374</v>
       </c>
     </row>
     <row r="23">
@@ -3745,142 +3747,142 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01208358591413844</v>
+        <v>0.01067497274085898</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01327512624034333</v>
+        <v>0.01200548920254552</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02859445747449738</v>
+        <v>0.02322318204386806</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01172566130356329</v>
+        <v>0.01075769273372761</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01480838785992197</v>
+        <v>0.01241231284836333</v>
       </c>
       <c r="H23" t="n">
-        <v>0.03235686289626336</v>
+        <v>0.02710723059280148</v>
       </c>
       <c r="I23" t="n">
-        <v>0.007433419154159938</v>
+        <v>0.006853841003095725</v>
       </c>
       <c r="J23" t="n">
-        <v>0.01812047317537873</v>
+        <v>0.01682246792784011</v>
       </c>
       <c r="K23" t="n">
-        <v>0.01705728454910712</v>
+        <v>0.01595668799190649</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01921730454456843</v>
+        <v>0.01773473410770577</v>
       </c>
       <c r="M23" t="n">
-        <v>0.01782941180181963</v>
+        <v>0.01672406116952879</v>
       </c>
       <c r="N23" t="n">
-        <v>0.02531841959593521</v>
+        <v>0.0235283996302639</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01662010918811907</v>
+        <v>0.01559591582624298</v>
       </c>
       <c r="P23" t="n">
-        <v>0.01152824647698777</v>
+        <v>0.01032077375336816</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.01327455599065796</v>
+        <v>0.01283094429899817</v>
       </c>
       <c r="R23" t="n">
-        <v>0.007869498700416238</v>
+        <v>0.003574644930110901</v>
       </c>
       <c r="S23" t="n">
-        <v>0.01347479010260977</v>
+        <v>0.01276505974893639</v>
       </c>
       <c r="T23" t="n">
-        <v>0.01195087275432011</v>
+        <v>0.01068635105181155</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01308237172485744</v>
+        <v>0.01235276711578797</v>
       </c>
       <c r="V23" t="n">
-        <v>0.007968026824216086</v>
+        <v>0.007115302850536963</v>
       </c>
       <c r="W23" t="n">
-        <v>0.01154209819463142</v>
+        <v>0.007226671336383297</v>
       </c>
       <c r="X23" t="n">
-        <v>0.01930166986647543</v>
+        <v>0.01524567936650126</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.01717003247646494</v>
+        <v>0.01541190675972721</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.01327455599065796</v>
+        <v>0.01283094429899817</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.01031449284445911</v>
+        <v>0.009855383137236761</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.01305081131343504</v>
+        <v>0.0124755644919876</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.01646344781962548</v>
+        <v>0.01562852939796065</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.01195087275432011</v>
+        <v>0.01068635105181155</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.01468886756888588</v>
+        <v>0.01292813607579789</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.005501953058272897</v>
+        <v>0.004587564787511936</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.01930166986647543</v>
+        <v>0.01524567936650126</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.01779672521003338</v>
+        <v>0.01176637539473503</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.006160128976342167</v>
+        <v>0.001819357607846976</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.01110436046517043</v>
+        <v>0.004503332732109336</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.01154209819463142</v>
+        <v>0.007226671336383297</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.009295697546595314</v>
+        <v>0.0068032055773382</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.01094896324771516</v>
+        <v>0.008686715329552694</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.00966463543503865</v>
+        <v>0.006794781784865777</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.01152824647698777</v>
+        <v>0.01032077375336816</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.01422488495101509</v>
+        <v>0.01236087191544419</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.01498315756190565</v>
+        <v>0.01300285202906658</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.01635666011785069</v>
+        <v>0.01474904964029645</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.01480838809338459</v>
+        <v>0.01241231297301506</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.02049124310666098</v>
+        <v>0.01835709917735838</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.01249842451639354</v>
+        <v>0.01151921107218452</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.01151715861940336</v>
+        <v>0.01052038817563444</v>
       </c>
     </row>
     <row r="24">
@@ -3893,142 +3895,142 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01859370083113564</v>
+        <v>0.01642618763456791</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01113075328202834</v>
+        <v>0.01006620471430887</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01016380515564736</v>
+        <v>0.008254603102664819</v>
       </c>
       <c r="F24" t="n">
-        <v>0.005644997032401062</v>
+        <v>0.005178995195684236</v>
       </c>
       <c r="G24" t="n">
-        <v>0.002153248773330561</v>
+        <v>0.001804841800994962</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00179055453702461</v>
+        <v>0.001500051932714347</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0003010534245597021</v>
+        <v>0.0002775805134323624</v>
       </c>
       <c r="J24" t="n">
-        <v>0.006833201778981423</v>
+        <v>0.006343726052781313</v>
       </c>
       <c r="K24" t="n">
-        <v>0.007674689194615614</v>
+        <v>0.007179491000503233</v>
       </c>
       <c r="L24" t="n">
-        <v>0.002802529383673721</v>
+        <v>0.002586320747179591</v>
       </c>
       <c r="M24" t="n">
-        <v>0.007722670781288865</v>
+        <v>0.007243896768665496</v>
       </c>
       <c r="N24" t="n">
-        <v>0.001908901599442328</v>
+        <v>0.001773941675796374</v>
       </c>
       <c r="O24" t="n">
-        <v>0.004752752304825116</v>
+        <v>0.00445986991120505</v>
       </c>
       <c r="P24" t="n">
-        <v>0.01118957521570497</v>
+        <v>0.010017575043014</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0328686031559134</v>
+        <v>0.03177019378849272</v>
       </c>
       <c r="R24" t="n">
-        <v>0.002587121523812885</v>
+        <v>0.001175175343531013</v>
       </c>
       <c r="S24" t="n">
-        <v>0.01039195054671332</v>
+        <v>0.009844596363033186</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0376116513195391</v>
+        <v>0.03363196294543695</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0401043906301419</v>
+        <v>0.03786776650241763</v>
       </c>
       <c r="V24" t="n">
-        <v>0.008676614438399847</v>
+        <v>0.007748058686113975</v>
       </c>
       <c r="W24" t="n">
-        <v>0.02108630917278743</v>
+        <v>0.013202437158261</v>
       </c>
       <c r="X24" t="n">
-        <v>0.009087156306108865</v>
+        <v>0.007177610660352347</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.04662493885713938</v>
+        <v>0.04185077758758901</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.0328686031559134</v>
+        <v>0.03177019378849272</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.03785853514800466</v>
+        <v>0.03617340905894013</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.0108154155197076</v>
+        <v>0.01033869930253722</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.007037843097656656</v>
+        <v>0.006680929715028769</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.0376116513195391</v>
+        <v>0.03363196294543695</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.009941025008795472</v>
+        <v>0.008749409948990757</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.09191681334817831</v>
+        <v>0.07664084586515475</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.009087156306108865</v>
+        <v>0.007177610660352347</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.01089868296089431</v>
+        <v>0.007205707427217404</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.004828939363354474</v>
+        <v>0.001426198640043327</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.003067528008121826</v>
+        <v>0.001244024753065791</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.02108630917278743</v>
+        <v>0.013202437158261</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.007507094153059765</v>
+        <v>0.005494187451312373</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.008140778441491721</v>
+        <v>0.006458750776878846</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.005370462829814888</v>
+        <v>0.003775737145762187</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.01118957521570497</v>
+        <v>0.010017575043014</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.009510359473626651</v>
+        <v>0.008264132590748399</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.009336945386510767</v>
+        <v>0.008102892782289754</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.04453913489228665</v>
+        <v>0.04016161653596278</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.00215324879544093</v>
+        <v>0.001804841809198685</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.003401397786193914</v>
+        <v>0.003047145367306289</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.0008052938704125741</v>
+        <v>0.0007422015515836844</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.0008167988585551322</v>
+        <v>0.0007461077282497543</v>
       </c>
     </row>
     <row r="25">
@@ -4041,134 +4043,134 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001878080377007395</v>
+        <v>0.001659147952615484</v>
       </c>
       <c r="D25" t="n">
-        <v>0.002301359231688975</v>
+        <v>0.002081256547546465</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0002466606202308127</v>
+        <v>0.0002003270910728917</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00197184574199075</v>
+        <v>0.001809067314966652</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0002502078543281083</v>
+        <v>0.0002097229080177917</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>0.0009827922099048061</v>
+        <v>0.0009123928647359485</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0003763117117791517</v>
+        <v>0.0003520307441241863</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001512394163592412</v>
+        <v>0.001395716464562062</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0007858410880791503</v>
+        <v>0.0007371221537001842</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>0.0021088472608199</v>
+        <v>0.001978892196066998</v>
       </c>
       <c r="P25" t="n">
-        <v>0.001923161027720892</v>
+        <v>0.00172172844309177</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.001139156268516356</v>
+        <v>0.001101087722969745</v>
       </c>
       <c r="R25" t="n">
-        <v>0.002482877163714123</v>
+        <v>0.001127823334526934</v>
       </c>
       <c r="S25" t="n">
-        <v>0.002005293267655082</v>
+        <v>0.001899672512954344</v>
       </c>
       <c r="T25" t="n">
-        <v>0.001949580817068128</v>
+        <v>0.001743295694244287</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.002348297598587236</v>
+        <v>0.0020969869913535</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001137267581853989</v>
+        <v>0.0007120593584453229</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001744336503063278</v>
+        <v>0.001377787270062914</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.0007011144087802005</v>
+        <v>0.0006293237890395893</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.001139156268516356</v>
+        <v>0.001101087722969745</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.0004851922767257644</v>
+        <v>0.0004635958213814985</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.0009170872603063702</v>
+        <v>0.0008766643686706524</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.0012139107556093</v>
+        <v>0.001152349139645291</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.001949580817068128</v>
+        <v>0.001743295694244287</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.002261183223753395</v>
+        <v>0.001990138740914014</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.001204974550308352</v>
+        <v>0.001004715736084065</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.001744336503063278</v>
+        <v>0.001377787270062914</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.0007124979300897092</v>
+        <v>0.0004710708298558637</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.002217874492278515</v>
+        <v>0.0006550360952300511</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.002228391860724255</v>
+        <v>0.0009037161606777459</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.001137267581853989</v>
+        <v>0.0007120593584453229</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.001005748163204182</v>
+        <v>0.0007360729497717406</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.001570893561205219</v>
+        <v>0.001246319388464897</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.001331801770663989</v>
+        <v>0.0009363314812219269</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.001923161027720892</v>
+        <v>0.00172172844309177</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.001527456048947484</v>
+        <v>0.001327299914377372</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.002410549044930064</v>
+        <v>0.002091949738266443</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.0006699337975012502</v>
+        <v>0.0006040895123983674</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.0002502078604464256</v>
+        <v>0.0002097229119458932</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.0006351624610441742</v>
+        <v>0.0005690108809129674</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.0003423381616313666</v>
+        <v>0.0003155170107018599</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.0003708192067269801</v>
+        <v>0.0003387260805088019</v>
       </c>
     </row>
     <row r="26">
@@ -4181,136 +4183,136 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.002073782288260933</v>
+        <v>0.001832036413276914</v>
       </c>
       <c r="D26" t="n">
-        <v>0.002311511383927547</v>
+        <v>0.00209043774491334</v>
       </c>
       <c r="E26" t="n">
-        <v>0.004856444660619234</v>
+        <v>0.003944194378932308</v>
       </c>
       <c r="F26" t="n">
-        <v>0.002291018326293849</v>
+        <v>0.002101891787895876</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0006500565019601491</v>
+        <v>0.0005448739422391516</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>6.988637702707315e-05</v>
+        <v>6.443738829901789e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.001454921438629594</v>
+        <v>0.001350702545236476</v>
       </c>
       <c r="K26" t="n">
-        <v>0.002094367776547314</v>
+        <v>0.001959231732017848</v>
       </c>
       <c r="L26" t="n">
-        <v>0.001029864199803808</v>
+        <v>0.0009504125673924405</v>
       </c>
       <c r="M26" t="n">
-        <v>0.00110896004789724</v>
+        <v>0.001040209059151588</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>0.001683780077461782</v>
+        <v>0.001580019244203939</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0004495451854719394</v>
+        <v>0.0004024596594489294</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.001834092120193023</v>
+        <v>0.001772800073312411</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0009621001379519158</v>
+        <v>0.0004370248361826283</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0003642534042820813</v>
+        <v>0.0003450678217624855</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0007423398919320139</v>
+        <v>0.0006637929168881569</v>
       </c>
       <c r="U26" t="n">
-        <v>0.004006576140019905</v>
+        <v>0.003783129162680775</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>0.0006811848835074268</v>
+        <v>0.0004264995141620274</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001362980964883178</v>
+        <v>0.001076568551685</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.001018030968358997</v>
+        <v>0.0009137896730463245</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.001834092120193023</v>
+        <v>0.001772800073312411</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.001081892383685004</v>
+        <v>0.001033736133735541</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.001145273162813302</v>
+        <v>0.001094792412553799</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.001517690227320315</v>
+        <v>0.001440722902914554</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.0007423398919320139</v>
+        <v>0.0006637929168881569</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.001331236557628999</v>
+        <v>0.00117166332158646</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.0003976922087465891</v>
+        <v>0.000331598389479245</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.001362980964883178</v>
+        <v>0.001076568551685</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.002274994759661772</v>
+        <v>0.0015041218003492</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.000946306764997988</v>
+        <v>0.0002794860982405052</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.001646301924702443</v>
+        <v>0.0006676517182327729</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.0006811848835074268</v>
+        <v>0.0004264995141620274</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.0003277945167230549</v>
+        <v>0.0002399016828175478</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.0006181427972856779</v>
+        <v>0.0004904236493948065</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.0004266703118702098</v>
+        <v>0.0002999732046516773</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.0004495451854719394</v>
+        <v>0.0004024596594489294</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.0004813865235393374</v>
+        <v>0.0004183061711768778</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.0004903411873896166</v>
+        <v>0.0004255333948829594</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.0009733979954459648</v>
+        <v>0.0008777278033019429</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.0006500565317259195</v>
+        <v>0.0005448739640703615</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.000335985545214505</v>
+        <v>0.0003009929628747897</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.0003115977397218343</v>
+        <v>0.0002871850070993702</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.0003098435369478229</v>
+        <v>0.0002830276451095272</v>
       </c>
     </row>
     <row r="27">
@@ -4323,142 +4325,142 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.004365046712470185</v>
+        <v>0.004055898526163918</v>
       </c>
       <c r="D27" t="n">
-        <v>0.004659920595820958</v>
+        <v>0.004480087135708896</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001638359725600583</v>
+        <v>0.001544912556482825</v>
       </c>
       <c r="F27" t="n">
-        <v>0.008773918761593521</v>
+        <v>0.008258379295735082</v>
       </c>
       <c r="G27" t="n">
-        <v>0.004469888627134909</v>
+        <v>0.003794682145137206</v>
       </c>
       <c r="H27" t="n">
-        <v>0.000361262398206857</v>
+        <v>0.0003026505741331506</v>
       </c>
       <c r="I27" t="n">
-        <v>0.001302511775192852</v>
+        <v>0.001200955902888359</v>
       </c>
       <c r="J27" t="n">
-        <v>0.005300177910834202</v>
+        <v>0.005510627554440097</v>
       </c>
       <c r="K27" t="n">
-        <v>0.004608550352167695</v>
+        <v>0.004311190321813565</v>
       </c>
       <c r="L27" t="n">
-        <v>0.006280192884622633</v>
+        <v>0.005795690581662129</v>
       </c>
       <c r="M27" t="n">
-        <v>0.004945215695316761</v>
+        <v>0.004859770986686503</v>
       </c>
       <c r="N27" t="n">
-        <v>0.004805958325162077</v>
+        <v>0.00446617560990897</v>
       </c>
       <c r="O27" t="n">
-        <v>0.004770841566655997</v>
+        <v>0.004675595336520992</v>
       </c>
       <c r="P27" t="n">
-        <v>0.003880957505682659</v>
+        <v>0.003474464606784904</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.002988315186868167</v>
+        <v>0.003361521371866789</v>
       </c>
       <c r="R27" t="n">
-        <v>0.00172755638454129</v>
+        <v>0.000784726055187557</v>
       </c>
       <c r="S27" t="n">
-        <v>0.004984621434497172</v>
+        <v>0.004722076555749979</v>
       </c>
       <c r="T27" t="n">
-        <v>0.003775554667684874</v>
+        <v>0.003678655094601526</v>
       </c>
       <c r="U27" t="n">
-        <v>0.007388355907969908</v>
+        <v>0.00827450445977972</v>
       </c>
       <c r="V27" t="n">
-        <v>0.001823681664374007</v>
+        <v>0.001628514515733823</v>
       </c>
       <c r="W27" t="n">
-        <v>0.003250769405304527</v>
+        <v>0.002035352817690717</v>
       </c>
       <c r="X27" t="n">
-        <v>0.004078898425989398</v>
+        <v>0.00322177189856353</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.004313424979595667</v>
+        <v>0.004104586847203949</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.002988315186868167</v>
+        <v>0.003361521371866789</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.002696679534958231</v>
+        <v>0.002933113376166471</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.003847148276253059</v>
+        <v>0.004160693151096135</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.00399852354149716</v>
+        <v>0.0037957445731527</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.003775554667684874</v>
+        <v>0.003678655094601526</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.005523747791072132</v>
+        <v>0.004861624815968368</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.003596619404500595</v>
+        <v>0.002998885006726769</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.004078898425989398</v>
+        <v>0.00322177189856353</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.009866742482409345</v>
+        <v>0.00652343589065229</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.00426527632191259</v>
+        <v>0.001259724099226425</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.004683424283843753</v>
+        <v>0.00189934557167364</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.003250769405304527</v>
+        <v>0.002035352817690717</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.004010118134439366</v>
+        <v>0.003159107426375853</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.003904820228940183</v>
+        <v>0.003098015855424541</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.002580871088348082</v>
+        <v>0.00202768585855352</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.003880957505682659</v>
+        <v>0.003474464606784904</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.004864131832767249</v>
+        <v>0.004226741430367791</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.004523827614740703</v>
+        <v>0.004371322610924969</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.004123494201292616</v>
+        <v>0.003941994773293977</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.004469888686077933</v>
+        <v>0.003794682164342853</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.00292920846723689</v>
+        <v>0.00262834900781964</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.004177051801981858</v>
+        <v>0.003852471154072289</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.004938591546647784</v>
+        <v>0.004516192974024121</v>
       </c>
     </row>
     <row r="28">
@@ -4471,136 +4473,136 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.00154812380065209</v>
+        <v>0.001367655221625854</v>
       </c>
       <c r="D28" t="n">
-        <v>0.001815751378882242</v>
+        <v>0.001642092374792672</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0002552072119033591</v>
+        <v>0.0002072682633068175</v>
       </c>
       <c r="F28" t="n">
-        <v>0.001258648682046566</v>
+        <v>0.001154745598617408</v>
       </c>
       <c r="G28" t="n">
-        <v>0.000366146934778362</v>
+        <v>0.0003069024356958097</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0008603545162169087</v>
+        <v>0.0007207691406123045</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0007320734522866661</v>
+        <v>0.0006749942308516616</v>
       </c>
       <c r="J28" t="n">
-        <v>0.001259025052389611</v>
+        <v>0.001168838603671218</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0008616364137517509</v>
+        <v>0.0008060405732881811</v>
       </c>
       <c r="L28" t="n">
-        <v>0.001911672450592503</v>
+        <v>0.001764191358556924</v>
       </c>
       <c r="M28" t="n">
-        <v>0.001803467828364874</v>
+        <v>0.001691660196876108</v>
       </c>
       <c r="N28" t="n">
-        <v>0.002821233851952408</v>
+        <v>0.002621771760581059</v>
       </c>
       <c r="O28" t="n">
-        <v>0.001855548463527457</v>
+        <v>0.001741202619136571</v>
       </c>
       <c r="P28" t="n">
-        <v>0.001220508460762212</v>
+        <v>0.001092671961233934</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.002158593498030278</v>
+        <v>0.002086457201046715</v>
       </c>
       <c r="R28" t="n">
-        <v>0.00196264534723693</v>
+        <v>0.000891512980329377</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0009498473909505072</v>
+        <v>0.0008998180012842094</v>
       </c>
       <c r="T28" t="n">
-        <v>0.001557132149663248</v>
+        <v>0.001392372015621054</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.0007805820544150404</v>
+        <v>0.0006970455596331104</v>
       </c>
       <c r="W28" t="n">
-        <v>0.00171594246448526</v>
+        <v>0.001074375907557814</v>
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="n">
-        <v>0.002058695832753159</v>
+        <v>0.001847895644025193</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.002158593498030278</v>
+        <v>0.002086457201046715</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.001920698938589711</v>
+        <v>0.001835206463035577</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.002516220421852634</v>
+        <v>0.002405311776790713</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.002709497138059288</v>
+        <v>0.002572089160167976</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.001557132149663248</v>
+        <v>0.001392372015621054</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.001410423074537014</v>
+        <v>0.001241357875040245</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.001355953425099791</v>
+        <v>0.001130602918747307</v>
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="n">
-        <v>0.001892569517723084</v>
+        <v>0.001251279836225593</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.002010188668935172</v>
+        <v>0.0005936973173906881</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.002893121247822008</v>
+        <v>0.001173294729952545</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.00171594246448526</v>
+        <v>0.001074375907557814</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.002579228641513078</v>
+        <v>0.001887649914513307</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0007440852540818353</v>
+        <v>0.000590344184822762</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.0004711869746401279</v>
+        <v>0.0003312709200538975</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.001220508460762212</v>
+        <v>0.001092671961233934</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.001293406257716992</v>
+        <v>0.001123919746369046</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.001220163986901509</v>
+        <v>0.001058896411342175</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.001972152777092766</v>
+        <v>0.001778320207060209</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.0003661469521869486</v>
+        <v>0.0003069024485311992</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.001353069729354086</v>
+        <v>0.001212148774300586</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.001535772068007824</v>
+        <v>0.001415449010148696</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.001430823751779578</v>
+        <v>0.001306990880049074</v>
       </c>
     </row>
     <row r="29">
@@ -4613,140 +4615,140 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.00550256066646305</v>
+        <v>0.004861113707205682</v>
       </c>
       <c r="D29" t="n">
-        <v>0.006085394132100525</v>
+        <v>0.005503385220107498</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001128798008899201</v>
+        <v>0.000916760937842648</v>
       </c>
       <c r="F29" t="n">
-        <v>0.006862465927144133</v>
+        <v>0.00629596045192414</v>
       </c>
       <c r="G29" t="n">
-        <v>0.00451797834057749</v>
+        <v>0.003786945691580009</v>
       </c>
       <c r="H29" t="n">
-        <v>0.005347759258743446</v>
+        <v>0.004480129728469084</v>
       </c>
       <c r="I29" t="n">
-        <v>0.001293104436853067</v>
+        <v>0.001192282047707311</v>
       </c>
       <c r="J29" t="n">
-        <v>0.006588162227169635</v>
+        <v>0.006116239167559843</v>
       </c>
       <c r="K29" t="n">
-        <v>0.00295874634833091</v>
+        <v>0.002767837529566237</v>
       </c>
       <c r="L29" t="n">
-        <v>0.005841811925733431</v>
+        <v>0.00539112969614614</v>
       </c>
       <c r="M29" t="n">
-        <v>0.007271017283477273</v>
+        <v>0.006820243941034816</v>
       </c>
       <c r="N29" t="n">
-        <v>0.009879305601587162</v>
+        <v>0.009180835690904094</v>
       </c>
       <c r="O29" t="n">
-        <v>0.007504245305720215</v>
+        <v>0.00704180561046823</v>
       </c>
       <c r="P29" t="n">
-        <v>0.003890155474469493</v>
+        <v>0.003482699176979855</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.007452657075549909</v>
+        <v>0.00720360273316952</v>
       </c>
       <c r="R29" t="n">
-        <v>0.005680370595088364</v>
+        <v>0.002580254311219297</v>
       </c>
       <c r="S29" t="n">
-        <v>0.002421677221439383</v>
+        <v>0.00229412511726805</v>
       </c>
       <c r="T29" t="n">
-        <v>0.003860700896418352</v>
+        <v>0.003452200180966378</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0.002790284102574786</v>
+        <v>0.002491672890522881</v>
       </c>
       <c r="W29" t="n">
-        <v>0.005081209125531724</v>
+        <v>0.003181417080538184</v>
       </c>
       <c r="X29" t="n">
-        <v>0.003429267358230857</v>
+        <v>0.002708652203009795</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.007767927467917437</v>
+        <v>0.006972530425668463</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.007452657075549909</v>
+        <v>0.00720360273316952</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.007265701052131188</v>
+        <v>0.006942296505430568</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.01056854557289067</v>
+        <v>0.0101027107598573</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.006711331995110198</v>
+        <v>0.006370977120601684</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.003860700896418352</v>
+        <v>0.003452200180966378</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.005012844840149723</v>
+        <v>0.004411962999625055</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.003530812656731308</v>
+        <v>0.002944014905937172</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.003429267358230857</v>
+        <v>0.002708652203009795</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.007780695304931132</v>
+        <v>0.005144237532996126</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.005528716790477945</v>
+        <v>0.00163287375849071</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.008698785869879615</v>
+        <v>0.003527760762117678</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.005081209125531724</v>
+        <v>0.003181417080538184</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.004938294545202002</v>
+        <v>0.003614170192613698</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.002620939131068277</v>
+        <v>0.002079407119429909</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.003334538510984017</v>
+        <v>0.002344367947209282</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.003890155474469493</v>
+        <v>0.003482699176979855</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.00404291772180309</v>
+        <v>0.00351313829925361</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.008586706442428213</v>
+        <v>0.007451811998012941</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.007427693626460762</v>
+        <v>0.006697664512208416</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.004517978629867784</v>
+        <v>0.003786945912389</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.003950001311392492</v>
+        <v>0.003538612345112291</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.002552382986733648</v>
+        <v>0.002352411563767358</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.003375966231511136</v>
+        <v>0.003083787972104079</v>
       </c>
     </row>
     <row r="30">
@@ -4759,140 +4761,140 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.00425613672041895</v>
+        <v>0.003759988450008111</v>
       </c>
       <c r="D30" t="n">
-        <v>0.004866757983200373</v>
+        <v>0.004401299796392985</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>0.006840783029754017</v>
+        <v>0.006276067505875211</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00338751650296962</v>
+        <v>0.002839398522755481</v>
       </c>
       <c r="H30" t="n">
-        <v>0.009325687910411593</v>
+        <v>0.007812672490361272</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0007069204999457436</v>
+        <v>0.0006518024354573913</v>
       </c>
       <c r="J30" t="n">
-        <v>0.006540255280784232</v>
+        <v>0.006071763890270493</v>
       </c>
       <c r="K30" t="n">
-        <v>0.005020372362330614</v>
+        <v>0.004696440113798386</v>
       </c>
       <c r="L30" t="n">
-        <v>0.004626022043293225</v>
+        <v>0.00426913518094707</v>
       </c>
       <c r="M30" t="n">
-        <v>0.006939986699422526</v>
+        <v>0.006509735899701032</v>
       </c>
       <c r="N30" t="n">
-        <v>0.004566920804175438</v>
+        <v>0.004244038114355963</v>
       </c>
       <c r="O30" t="n">
-        <v>0.007927511815371473</v>
+        <v>0.007438988852880839</v>
       </c>
       <c r="P30" t="n">
-        <v>0.005267539722682204</v>
+        <v>0.004715815698701806</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.006316680425323714</v>
+        <v>0.006105588371388039</v>
       </c>
       <c r="R30" t="n">
-        <v>0.006547366763139729</v>
+        <v>0.00297407907370213</v>
       </c>
       <c r="S30" t="n">
-        <v>0.003936401443175242</v>
+        <v>0.00372906733502286</v>
       </c>
       <c r="T30" t="n">
-        <v>0.004789049976593427</v>
+        <v>0.004282320656125064</v>
       </c>
       <c r="U30" t="n">
-        <v>0.003424175554694221</v>
+        <v>0.003233209090851814</v>
       </c>
       <c r="V30" t="n">
-        <v>0.002743892284061123</v>
+        <v>0.002450245841418495</v>
       </c>
       <c r="W30" t="n">
-        <v>0.004553647761408047</v>
+        <v>0.002851103430107696</v>
       </c>
       <c r="X30" t="n">
-        <v>0.004535052705821809</v>
+        <v>0.003582071392860713</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.001921964480449664</v>
+        <v>0.001725164900462456</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.006316680425323714</v>
+        <v>0.006105588371388039</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.007577727174848067</v>
+        <v>0.007240433993581838</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.007033806566656865</v>
+        <v>0.00672377412706591</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.005897137092223517</v>
+        <v>0.005598072859304389</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.004789049976593427</v>
+        <v>0.004282320656125064</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.005735777551581092</v>
+        <v>0.005048238901984435</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.005555163635311401</v>
+        <v>0.004631932117977976</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.004535052705821809</v>
+        <v>0.003582071392860713</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.006935794700240785</v>
+        <v>0.004585628150163124</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.006581749309114796</v>
+        <v>0.001943880675951361</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.007518798551698192</v>
+        <v>0.003049221225319712</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.004553647761408047</v>
+        <v>0.002851103430107696</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.005392516858114526</v>
+        <v>0.003946600089032796</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.003083672488779591</v>
+        <v>0.002446531646290028</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.003163496260832978</v>
+        <v>0.002224115634167524</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.005267539722682204</v>
+        <v>0.004715815698701806</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.005937455708014103</v>
+        <v>0.005159418143845729</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.006319326153701838</v>
+        <v>0.005484108577280735</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.001837339459082224</v>
+        <v>0.001656756984178261</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.003387516440630776</v>
+        <v>0.00283939845425357</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.002578229918987473</v>
+        <v>0.00230970966859013</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.00205222004504854</v>
+        <v>0.001891434863208145</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.002063183033515611</v>
+        <v>0.001884621642129616</v>
       </c>
     </row>
     <row r="31">
@@ -4905,83 +4907,83 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.004287506028341307</v>
+        <v>0.003787700960958932</v>
       </c>
       <c r="D31" t="n">
-        <v>0.003315391138380453</v>
+        <v>0.002998306139875338</v>
       </c>
       <c r="E31" t="n">
-        <v>0.008479420196646742</v>
+        <v>0.006886618465442316</v>
       </c>
       <c r="F31" t="n">
-        <v>0.020690112203011</v>
+        <v>0.01898211656844476</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01361656701850183</v>
+        <v>0.01141333488514132</v>
       </c>
       <c r="H31" t="n">
-        <v>0.01803358361275847</v>
+        <v>0.01510778442807761</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0001480336414448426</v>
+        <v>0.000136491568756006</v>
       </c>
       <c r="J31" t="n">
-        <v>0.00222432827107731</v>
+        <v>0.002064995248138934</v>
       </c>
       <c r="K31" t="n">
-        <v>0.003193498020639611</v>
+        <v>0.002987442190544018</v>
       </c>
       <c r="L31" t="n">
-        <v>0.003033937430711781</v>
+        <v>0.002799876200551609</v>
       </c>
       <c r="M31" t="n">
-        <v>0.001509761838261474</v>
+        <v>0.001416162777278397</v>
       </c>
       <c r="N31" t="n">
-        <v>0.001979185381212687</v>
+        <v>0.001839256372819751</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002265103354398882</v>
+        <v>0.002125519204061471</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0003061255535327946</v>
+        <v>0.0002740618518560775</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="n">
-        <v>0.0002418512688538527</v>
+        <v>0.0002162609890030044</v>
       </c>
       <c r="U31" t="n">
-        <v>0.0004060601702756264</v>
+        <v>0.0003834141716735754</v>
       </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
-        <v>0.0001026531935846796</v>
+        <v>9.214201838487358e-05</v>
       </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.0003391165244612421</v>
+        <v>0.0003219187517671087</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.0002418512688538527</v>
+        <v>0.0002162609890030044</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.000302066702912331</v>
+        <v>0.0002658584414968912</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.000221757732237482</v>
+        <v>0.000184903061330465</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="n">
-        <v>0.0005926466882938354</v>
+        <v>0.0003918307064144813</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.0004787127970774565</v>
+        <v>0.0001413849892886071</v>
       </c>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
@@ -4989,28 +4991,28 @@
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="n">
-        <v>0.0003061255535327946</v>
+        <v>0.0002740618518560775</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.0003302266620226474</v>
+        <v>0.0002869541290761258</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.0003305132817932393</v>
+        <v>0.0002868297472707136</v>
       </c>
       <c r="AR31" t="n">
-        <v>9.836919187050454e-05</v>
+        <v>8.870099907441025e-05</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.01361656819291568</v>
+        <v>0.01141333580421055</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.01225102063603328</v>
+        <v>0.01097508822031507</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.01128522845093537</v>
+        <v>0.01040106521855104</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.008761508999074479</v>
+        <v>0.008003230546750333</v>
       </c>
     </row>
     <row r="32">
@@ -5023,136 +5025,136 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.002692016556875516</v>
+        <v>0.002378201600649284</v>
       </c>
       <c r="D32" t="n">
-        <v>0.002821569473455688</v>
+        <v>0.002551713726447261</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001435461198424586</v>
+        <v>0.00116581952141091</v>
       </c>
       <c r="F32" t="n">
-        <v>0.005687690633760874</v>
+        <v>0.005218164384801573</v>
       </c>
       <c r="G32" t="n">
-        <v>0.01149261724251874</v>
+        <v>0.009633051349682096</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0005787492252992636</v>
+        <v>0.0004848519696080942</v>
       </c>
       <c r="I32" t="n">
-        <v>0.002520260570731282</v>
+        <v>0.002323757732469157</v>
       </c>
       <c r="J32" t="n">
-        <v>0.003433983759471724</v>
+        <v>0.003188000727096327</v>
       </c>
       <c r="K32" t="n">
-        <v>0.003536321899036007</v>
+        <v>0.003308145855186404</v>
       </c>
       <c r="L32" t="n">
-        <v>0.004651767343674635</v>
+        <v>0.004292894291166113</v>
       </c>
       <c r="M32" t="n">
-        <v>0.003416530128236043</v>
+        <v>0.003204719229510769</v>
       </c>
       <c r="N32" t="n">
-        <v>0.003884604749403328</v>
+        <v>0.003609962012173003</v>
       </c>
       <c r="O32" t="n">
-        <v>0.00295338226447849</v>
+        <v>0.002771383790453797</v>
       </c>
       <c r="P32" t="n">
-        <v>0.001547652389761693</v>
+        <v>0.00138555071627542</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.00142750379965896</v>
+        <v>0.001379799200283799</v>
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>0.0007613639078949815</v>
+        <v>0.0007212621273470386</v>
       </c>
       <c r="T32" t="n">
-        <v>0.001291381961652204</v>
+        <v>0.001154740851809663</v>
       </c>
       <c r="U32" t="n">
-        <v>0.003624636413720394</v>
+        <v>0.003422490236462137</v>
       </c>
       <c r="V32" t="n">
-        <v>0.00296951045385942</v>
+        <v>0.002651718758379553</v>
       </c>
       <c r="W32" t="n">
-        <v>0.0006568525938716853</v>
+        <v>0.0004112647226107843</v>
       </c>
       <c r="X32" t="n">
-        <v>0.001741420117995233</v>
+        <v>0.00137548372472387</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.001560777995841161</v>
+        <v>0.001400962111021607</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.00142750379965896</v>
+        <v>0.001379799200283799</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.001777050453204755</v>
+        <v>0.001697951933714438</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.001223740565159283</v>
+        <v>0.001169801169862111</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.001483050554789873</v>
+        <v>0.0014078399280718</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.001291381961652204</v>
+        <v>0.001154740851809663</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.001616696224857448</v>
+        <v>0.001422905386692864</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.001395782426112727</v>
+        <v>0.001163812602769234</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.001741420117995233</v>
+        <v>0.00137548372472387</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.0009072405907400051</v>
+        <v>0.0005998257116410266</v>
       </c>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="n">
-        <v>0.0006568525938716853</v>
+        <v>0.0004112647226107843</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.001271099118578691</v>
+        <v>0.0009302743091110482</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.0005964322924421182</v>
+        <v>0.0004731989157857834</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.0006571142605139734</v>
+        <v>0.0004619882496269282</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.001547652389761693</v>
+        <v>0.00138555071627542</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.001422485567985072</v>
+        <v>0.001236084647994051</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.001526485416580459</v>
+        <v>0.001324731713880428</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.001490456383748481</v>
+        <v>0.001343967229997787</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.01149261711363581</v>
+        <v>0.009633051186523354</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.006556843772216498</v>
+        <v>0.005873954585893163</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.004245440603251712</v>
+        <v>0.003912823279376835</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.003563655466532728</v>
+        <v>0.003255233349741616</v>
       </c>
     </row>
     <row r="33">
@@ -5165,142 +5167,142 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.003220832569141768</v>
+        <v>0.003810436959235086</v>
       </c>
       <c r="D33" t="n">
-        <v>0.003622752476124174</v>
+        <v>0.004535008497846325</v>
       </c>
       <c r="E33" t="n">
-        <v>0.004959621665446824</v>
+        <v>0.004027990281267198</v>
       </c>
       <c r="F33" t="n">
-        <v>0.003710592728359128</v>
+        <v>0.004510979670839396</v>
       </c>
       <c r="G33" t="n">
-        <v>0.001151429191186632</v>
+        <v>0.001633580037328826</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0008645643113164018</v>
+        <v>0.001339564321232461</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0002146161077532347</v>
+        <v>0.0008549796700278936</v>
       </c>
       <c r="J33" t="n">
-        <v>0.006377380495120279</v>
+        <v>0.007167109008473765</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002566118745681628</v>
+        <v>0.004829726898603165</v>
       </c>
       <c r="L33" t="n">
-        <v>0.002063375153471784</v>
+        <v>0.003574385785009558</v>
       </c>
       <c r="M33" t="n">
-        <v>0.003661715310244511</v>
+        <v>0.004993667520051371</v>
       </c>
       <c r="N33" t="n">
-        <v>0.00473918968524331</v>
+        <v>0.007124928686941638</v>
       </c>
       <c r="O33" t="n">
-        <v>0.004922938495349607</v>
+        <v>0.006621770165574545</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00356009547663663</v>
+        <v>0.003187209783213854</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.00232997643221761</v>
+        <v>0.004222723056051566</v>
       </c>
       <c r="R33" t="n">
-        <v>0.00529532308275928</v>
+        <v>0.002405350141309952</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002860271302038125</v>
+        <v>0.002709618019327313</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002540203732085541</v>
+        <v>0.002271424805721837</v>
       </c>
       <c r="U33" t="n">
-        <v>0.002795310460776918</v>
+        <v>0.005542669987268121</v>
       </c>
       <c r="V33" t="n">
-        <v>0.002427497931022443</v>
+        <v>0.002167711445923236</v>
       </c>
       <c r="W33" t="n">
-        <v>0.003402562494501182</v>
+        <v>0.002130392623128238</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002911972245963127</v>
+        <v>0.002300059813125956</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.003462615586519785</v>
+        <v>0.003108061014873995</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.00232997643221761</v>
+        <v>0.004222723056051566</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002520643393541501</v>
+        <v>0.004143436381012128</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.002363729780874976</v>
+        <v>0.005140270371048707</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.002222460037614729</v>
+        <v>0.004178094768821443</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.002540203732085541</v>
+        <v>0.002271424805721837</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.002893340194604109</v>
+        <v>0.002546520048192837</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.002406526871641084</v>
+        <v>0.002006577995052445</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.002911972245963127</v>
+        <v>0.002300059813125956</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.003106107296250492</v>
+        <v>0.002053615147319577</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.005179944453871105</v>
+        <v>0.001529865914588551</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.004760455242017052</v>
+        <v>0.001930585194740239</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.003402562494501182</v>
+        <v>0.002130392623128238</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.002135379652076349</v>
+        <v>0.001562811901519021</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.002240660677490787</v>
+        <v>0.001777700866750731</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.001976593910797844</v>
+        <v>0.001389656587818523</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.00356009547663663</v>
+        <v>0.003187209783213854</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.004437327842859784</v>
+        <v>0.003855865358581337</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.003800674276442112</v>
+        <v>0.003298343825263159</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.003314135308164792</v>
+        <v>0.002988406301934253</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.001151429306076785</v>
+        <v>0.001633580238326383</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.0004689976198256698</v>
+        <v>0.001526672641212657</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.0003571489817069244</v>
+        <v>0.001135575560333092</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.0003307203830417196</v>
+        <v>0.001136261453884044</v>
       </c>
     </row>
     <row r="34">
@@ -5313,140 +5315,140 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.007894503585155355</v>
+        <v>0.006974221987824185</v>
       </c>
       <c r="D34" t="n">
-        <v>0.006089307637229875</v>
+        <v>0.00550692443643764</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001269028046897928</v>
+        <v>0.001030649711685181</v>
       </c>
       <c r="F34" t="n">
-        <v>0.008976057872208591</v>
+        <v>0.00823507263680155</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01141875828758503</v>
+        <v>0.009571143161973729</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0125760875057741</v>
+        <v>0.01053572174370577</v>
       </c>
       <c r="I34" t="n">
-        <v>0.02711775277264654</v>
+        <v>0.02500340180076688</v>
       </c>
       <c r="J34" t="n">
-        <v>0.00576087574477251</v>
+        <v>0.005348212848237726</v>
       </c>
       <c r="K34" t="n">
-        <v>0.004078704486060264</v>
+        <v>0.003815531992087201</v>
       </c>
       <c r="L34" t="n">
-        <v>0.006622362823477038</v>
+        <v>0.006111462904006261</v>
       </c>
       <c r="M34" t="n">
-        <v>0.009014567134161914</v>
+        <v>0.0084557008298592</v>
       </c>
       <c r="N34" t="n">
-        <v>0.01660101845317217</v>
+        <v>0.01542732139956829</v>
       </c>
       <c r="O34" t="n">
-        <v>0.008180256159118469</v>
+        <v>0.007676158143769431</v>
       </c>
       <c r="P34" t="n">
-        <v>0.004450447516007763</v>
+        <v>0.003984306026562082</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.005953095955573108</v>
+        <v>0.005754154238100723</v>
       </c>
       <c r="R34" t="n">
-        <v>0.001668892577709673</v>
+        <v>0.0007580785789435423</v>
       </c>
       <c r="S34" t="n">
-        <v>0.003229632448573397</v>
+        <v>0.003059524553570486</v>
       </c>
       <c r="T34" t="n">
-        <v>0.00405304385347087</v>
+        <v>0.003624191332044754</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
-        <v>0.002485711469346878</v>
+        <v>0.002219695075536637</v>
       </c>
       <c r="W34" t="n">
-        <v>0.001815998916890231</v>
+        <v>0.001137022671120398</v>
       </c>
       <c r="X34" t="n">
-        <v>0.002048872380150059</v>
+        <v>0.001618328962557891</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.002883289860976372</v>
+        <v>0.002588055355139527</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.005953095955573108</v>
+        <v>0.005754154238100723</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.00500698402786219</v>
+        <v>0.004784117522861541</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.004917808042137293</v>
+        <v>0.004701043476564582</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.003023990733250801</v>
+        <v>0.002870633696632679</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.00405304385347087</v>
+        <v>0.003624191332044754</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.005392822346578727</v>
+        <v>0.004746393198945666</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.002837955314360811</v>
+        <v>0.002366305879167366</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.002048872380150059</v>
+        <v>0.001618328962557891</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.002840607054588453</v>
+        <v>0.001878078610461257</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.002410976437725109</v>
+        <v>0.000712067611110247</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.002069844713070746</v>
+        <v>0.0008394179454090592</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.001815998916890231</v>
+        <v>0.001137022671120398</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.002132865821528643</v>
+        <v>0.001560972114250028</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.003028105585859635</v>
+        <v>0.002402445840493641</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.002666741595673265</v>
+        <v>0.001874869190981763</v>
       </c>
       <c r="AO34" t="n">
-        <v>0.004450447516007763</v>
+        <v>0.003984306026562082</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.003802929509646271</v>
+        <v>0.003304597874364256</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.003887123196466271</v>
+        <v>0.003373366897703156</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.002759377589100192</v>
+        <v>0.002488172814298724</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.01141875944862086</v>
+        <v>0.009571144080372398</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.008520542965138933</v>
+        <v>0.007633136332522186</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.0187312091591569</v>
+        <v>0.017263676046413</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.01570365318160295</v>
+        <v>0.01434455604072928</v>
       </c>
     </row>
     <row r="35">
@@ -5459,142 +5461,142 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.005134995135439902</v>
+        <v>0.00453639618940656</v>
       </c>
       <c r="D35" t="n">
-        <v>0.005642751168064798</v>
+        <v>0.00510307676133263</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0002012339667899199</v>
+        <v>0.0001634335272260364</v>
       </c>
       <c r="F35" t="n">
-        <v>0.004147444063797785</v>
+        <v>0.003805067169652987</v>
       </c>
       <c r="G35" t="n">
-        <v>0.006307912813749752</v>
+        <v>0.005287259356324982</v>
       </c>
       <c r="H35" t="n">
-        <v>0.003305812627385483</v>
+        <v>0.002769471981088801</v>
       </c>
       <c r="I35" t="n">
-        <v>0.008894208003304758</v>
+        <v>0.008200733234449423</v>
       </c>
       <c r="J35" t="n">
-        <v>0.006240100397611135</v>
+        <v>0.005793109693622647</v>
       </c>
       <c r="K35" t="n">
-        <v>0.007164041181627062</v>
+        <v>0.006701791810254814</v>
       </c>
       <c r="L35" t="n">
-        <v>0.007021200744090352</v>
+        <v>0.006479531404858872</v>
       </c>
       <c r="M35" t="n">
-        <v>0.006465357758365926</v>
+        <v>0.006064532012366445</v>
       </c>
       <c r="N35" t="n">
-        <v>0.004706401709837683</v>
+        <v>0.004373657677566745</v>
       </c>
       <c r="O35" t="n">
-        <v>0.006879228728519655</v>
+        <v>0.006455304895118264</v>
       </c>
       <c r="P35" t="n">
-        <v>0.005205106130108913</v>
+        <v>0.00465992142329356</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.002721531887738264</v>
+        <v>0.002630583206255035</v>
       </c>
       <c r="R35" t="n">
-        <v>0.004040519718341369</v>
+        <v>0.001835367648693829</v>
       </c>
       <c r="S35" t="n">
-        <v>0.003026229794149783</v>
+        <v>0.002866835315590682</v>
       </c>
       <c r="T35" t="n">
-        <v>0.004901181248678333</v>
+        <v>0.004382587319658265</v>
       </c>
       <c r="U35" t="n">
-        <v>0.004160724906275512</v>
+        <v>0.003928681043546803</v>
       </c>
       <c r="V35" t="n">
-        <v>0.004633687372413249</v>
+        <v>0.004137798440791872</v>
       </c>
       <c r="W35" t="n">
-        <v>0.002268496082772963</v>
+        <v>0.001420337562688417</v>
       </c>
       <c r="X35" t="n">
-        <v>0.003594627428517348</v>
+        <v>0.002839264042765104</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.005229681716824377</v>
+        <v>0.004694188383931448</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.002721531887738264</v>
+        <v>0.002630583206255035</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.003715732209237969</v>
+        <v>0.003550340778711521</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.003231957398865911</v>
+        <v>0.003089500874432273</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.002258551313630607</v>
+        <v>0.002144012359294589</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.004901181248678333</v>
+        <v>0.004382587319658265</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.005336868791110697</v>
+        <v>0.004697146708321183</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.003571833872022732</v>
+        <v>0.002978218666096289</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.003594627428517348</v>
+        <v>0.002839264042765104</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.004928854756771578</v>
+        <v>0.003258731853745977</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.003888266747176439</v>
+        <v>0.001148376554286764</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.003694111395587143</v>
+        <v>0.001498133351847234</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.002268496082772963</v>
+        <v>0.001420337562688417</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.003152065532747954</v>
+        <v>0.00230688979552488</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002740773742181288</v>
+        <v>0.002174481797261494</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.002069199005919164</v>
+        <v>0.001454763173343194</v>
       </c>
       <c r="AO35" t="n">
-        <v>0.005205106130108913</v>
+        <v>0.00465992142329356</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.005036456801853661</v>
+        <v>0.004376485127982582</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.006882862487176326</v>
+        <v>0.005973163005687849</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.005009523658355956</v>
+        <v>0.004517163808441366</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.006307913138521757</v>
+        <v>0.005287259598288293</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.005135728703649915</v>
+        <v>0.004600847331232022</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.003276377557392118</v>
+        <v>0.003019683367792863</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.003371987571254639</v>
+        <v>0.003080153651200762</v>
       </c>
     </row>
   </sheetData>

--- a/data/proteomics/membrane_size_ratio_across_compartment_cell_system_2018.xlsx
+++ b/data/proteomics/membrane_size_ratio_across_compartment_cell_system_2018.xlsx
@@ -678,139 +678,139 @@
         <v>0.02511520181973679</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03000341216649309</v>
+        <v>0.03000341216649305</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003702045292069249</v>
+        <v>0.003702045292069244</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03488844041365578</v>
+        <v>0.03488844041365579</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01951517110992164</v>
+        <v>0.01951517110992167</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001187598375903376</v>
+        <v>0.001187598375903375</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007340441237873826</v>
+        <v>0.007340441237873822</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02610709374497482</v>
+        <v>0.02610709374497475</v>
       </c>
       <c r="K2" t="n">
         <v>0.02356839435911318</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01815014422997259</v>
+        <v>0.01815014422997261</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02426062249443635</v>
+        <v>0.02426062249443638</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02100155371957382</v>
+        <v>0.02100155371957383</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03070505397151046</v>
+        <v>0.03070505397151051</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02104595317801336</v>
+        <v>0.02104595317801337</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03522607155688043</v>
+        <v>0.03522607155688048</v>
       </c>
       <c r="R2" t="n">
-        <v>0.008767265452101422</v>
+        <v>0.008767265452101427</v>
       </c>
       <c r="S2" t="n">
         <v>0.02223068738853374</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01881819639134931</v>
+        <v>0.0188181963913493</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02119583773454431</v>
+        <v>0.02119583773454433</v>
       </c>
       <c r="V2" t="n">
         <v>0.01978001408311683</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0127032635462696</v>
+        <v>0.01270326354626959</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01621921711936075</v>
+        <v>0.01621921711936078</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01977910637750847</v>
+        <v>0.01977910637750849</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03522607155688043</v>
+        <v>0.03522607155688048</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.02799072126915804</v>
+        <v>0.02799072126915803</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.03228872619884952</v>
+        <v>0.03228872619884954</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.02990535559142441</v>
+        <v>0.02990535559142445</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.01881819639134931</v>
+        <v>0.0188181963913493</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.02067864439237451</v>
+        <v>0.02067864439237452</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.01468996123749254</v>
+        <v>0.01468996123749255</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.01621921711936075</v>
+        <v>0.01621921711936078</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.01488343238678852</v>
+        <v>0.0148834323867885</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.008110975656194624</v>
+        <v>0.008110975656194621</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.01163966883120805</v>
+        <v>0.01163966883120804</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0127032635462696</v>
+        <v>0.01270326354626959</v>
       </c>
       <c r="AL2" t="n">
         <v>0.01418868743908389</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.01648013733760059</v>
+        <v>0.01648013733760061</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.01300676237568732</v>
+        <v>0.01300676237568731</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.02104595317801336</v>
+        <v>0.02104595317801337</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.02023825679949192</v>
+        <v>0.02023825679949191</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.023294325515702</v>
+        <v>0.02329432551570202</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.01899681388009873</v>
+        <v>0.0189968138800987</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.01951517190430115</v>
+        <v>0.01951517190430113</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.01210963592228034</v>
+        <v>0.01210963592228032</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.008252827282967385</v>
+        <v>0.008252827282967383</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.008015482318599259</v>
+        <v>0.008015482318599257</v>
       </c>
     </row>
     <row r="3">
@@ -826,46 +826,46 @@
         <v>0.07887370759644524</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08800443629922101</v>
+        <v>0.08800443629922089</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1004949900392503</v>
+        <v>0.1004949900392502</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07218749048890638</v>
+        <v>0.07218749048890641</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09034791271500815</v>
+        <v>0.09034791271500835</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09246644247569383</v>
+        <v>0.09246644247569377</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05521850289894695</v>
+        <v>0.05521850289894691</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09322016018048279</v>
+        <v>0.09322016018048253</v>
       </c>
       <c r="K3" t="n">
         <v>0.106087134022874</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08918774356158633</v>
+        <v>0.08918774356158642</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0817604740153481</v>
+        <v>0.08176047401534826</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09251393922095685</v>
+        <v>0.0925139392209569</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09572447059740836</v>
+        <v>0.09572447059740852</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08418582309307256</v>
+        <v>0.08418582309307265</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09742050381254624</v>
+        <v>0.09742050381254637</v>
       </c>
       <c r="R3" t="n">
         <v>0.06589787560166725</v>
@@ -874,85 +874,85 @@
         <v>0.1762291280800927</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08806999810962311</v>
+        <v>0.08806999810962302</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0878137900256617</v>
+        <v>0.08781379002566178</v>
       </c>
       <c r="V3" t="n">
-        <v>0.08235968986724085</v>
+        <v>0.08235968986724082</v>
       </c>
       <c r="W3" t="n">
-        <v>0.05902405409660568</v>
+        <v>0.05902405409660569</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1069938715621271</v>
+        <v>0.1069938715621273</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08288188216441197</v>
+        <v>0.08288188216441207</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.09742050381254624</v>
+        <v>0.09742050381254637</v>
       </c>
       <c r="AA3" t="n">
         <v>0.1063186737611517</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.09490791201928499</v>
+        <v>0.09490791201928503</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1025806033273688</v>
+        <v>0.1025806033273689</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.08806999810962311</v>
+        <v>0.08806999810962302</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.07538907809898207</v>
+        <v>0.07538907809898206</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.07067868667820262</v>
+        <v>0.07067868667820268</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.1069938715621271</v>
+        <v>0.1069938715621273</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0948166720497145</v>
+        <v>0.09481667204971439</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.04053573024885065</v>
+        <v>0.04053573024885063</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.05906859245124633</v>
+        <v>0.05906859245124628</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.05902405409660568</v>
+        <v>0.05902405409660569</v>
       </c>
       <c r="AL3" t="n">
         <v>0.06940004349720799</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.117635504603033</v>
+        <v>0.1176355046030331</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.09005662810555166</v>
+        <v>0.09005662810555158</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.08418582309307256</v>
+        <v>0.08418582309307265</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.093603863986954</v>
+        <v>0.09360386398695396</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.09294610532538071</v>
+        <v>0.09294610532538083</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.07953570127862787</v>
+        <v>0.07953570127862775</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.09034791105351689</v>
+        <v>0.09034791105351681</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1043979188753149</v>
+        <v>0.1043979188753147</v>
       </c>
       <c r="AU3" t="n">
         <v>0.07095021623455798</v>
@@ -971,61 +971,61 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1428287595334072</v>
+        <v>0.1428287595334073</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1309242100286049</v>
+        <v>0.1309242100286047</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06769952480226209</v>
+        <v>0.067699524802262</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1078763763470893</v>
+        <v>0.1078763763470894</v>
       </c>
       <c r="G4" t="n">
-        <v>0.126219053510812</v>
+        <v>0.1262190535108123</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04471409805910471</v>
+        <v>0.04471409805910469</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03807308690502782</v>
+        <v>0.03807308690502778</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1324409375017697</v>
+        <v>0.1324409375017694</v>
       </c>
       <c r="K4" t="n">
         <v>0.1319401743146003</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1344605902944148</v>
+        <v>0.1344605902944149</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1195811711044992</v>
+        <v>0.1195811711044995</v>
       </c>
       <c r="N4" t="n">
         <v>0.1317859415711089</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09198077092205778</v>
+        <v>0.09198077092205799</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1372797919893179</v>
+        <v>0.1372797919893181</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1223853700836404</v>
+        <v>0.1223853700836407</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03554605870343806</v>
+        <v>0.03554605870343808</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1275150821080244</v>
+        <v>0.1275150821080243</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2164993717502487</v>
+        <v>0.2164993717502484</v>
       </c>
       <c r="U4" t="n">
-        <v>0.135691716336592</v>
+        <v>0.1356917163365921</v>
       </c>
       <c r="V4" t="n">
         <v>0.2003540945793355</v>
@@ -1034,40 +1034,40 @@
         <v>0.1200506709682665</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09277893444960385</v>
+        <v>0.09277893444960397</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.267276247624928</v>
+        <v>0.2672762476249282</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1223853700836404</v>
+        <v>0.1223853700836407</v>
       </c>
       <c r="AA4" t="n">
         <v>0.09629825122545309</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1059524690725917</v>
+        <v>0.1059524690725918</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1266294971082676</v>
+        <v>0.1266294971082678</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2164993717502487</v>
+        <v>0.2164993717502484</v>
       </c>
       <c r="AE4" t="n">
         <v>0.1750161691066271</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2400548781222447</v>
+        <v>0.2400548781222449</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.09277893444960385</v>
+        <v>0.09277893444960397</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.06662668587612317</v>
+        <v>0.06662668587612311</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.02292449655641244</v>
+        <v>0.02292449655641243</v>
       </c>
       <c r="AJ4" t="n">
         <v>0.03330607387054785</v>
@@ -1079,31 +1079,31 @@
         <v>0.1364247227163576</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.09193629379111026</v>
+        <v>0.0919362937911104</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.06779348019996712</v>
+        <v>0.06779348019996705</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1372797919893179</v>
+        <v>0.1372797919893181</v>
       </c>
       <c r="AP4" t="n">
         <v>0.1210451810678976</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.1259532444883827</v>
+        <v>0.1259532444883829</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.2561028220149204</v>
+        <v>0.2561028220149201</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.1262190277426657</v>
+        <v>0.1262190277426656</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.06633602233980131</v>
+        <v>0.06633602233980117</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.04382924267972185</v>
+        <v>0.04382924267972183</v>
       </c>
       <c r="AV4" t="n">
         <v>0.04818721370499118</v>
@@ -1119,106 +1119,106 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.06145705818614611</v>
+        <v>0.06145705818614614</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0609586370260697</v>
+        <v>0.06095863702606962</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01487585795423529</v>
+        <v>0.01487585795423527</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1022956510734337</v>
+        <v>0.1022956510734338</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1021142538917223</v>
+        <v>0.1021142538917226</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07644194963655154</v>
+        <v>0.07644194963655149</v>
       </c>
       <c r="I5" t="n">
-        <v>0.13630811796995</v>
+        <v>0.1363081179699499</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07374174149300732</v>
+        <v>0.07374174149300716</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07716974291553412</v>
+        <v>0.07716974291553409</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08040266057000886</v>
+        <v>0.08040266057000896</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07605621063629092</v>
+        <v>0.07605621063629102</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07887844453603042</v>
+        <v>0.0788784445360305</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08456454676751991</v>
+        <v>0.08456454676752007</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0351483673888362</v>
+        <v>0.03514836738883623</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03548378263851888</v>
+        <v>0.03548378263851894</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01616728373555455</v>
+        <v>0.01616728373555456</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04312257026611115</v>
+        <v>0.04312257026611116</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02879388498976778</v>
+        <v>0.02879388498976775</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04343615816141662</v>
+        <v>0.04343615816141665</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03110232056627165</v>
+        <v>0.03110232056627167</v>
       </c>
       <c r="W5" t="n">
         <v>0.03085671220746983</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03831577320777386</v>
+        <v>0.03831577320777393</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05372022582205089</v>
+        <v>0.05372022582205095</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03548378263851888</v>
+        <v>0.03548378263851894</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04148003035171896</v>
+        <v>0.04148003035171895</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04398607313382118</v>
+        <v>0.04398607313382122</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.05101921641512238</v>
+        <v>0.05101921641512246</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.02879388498976778</v>
+        <v>0.02879388498976775</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.03472738365820869</v>
+        <v>0.0347273836582087</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02713725629779178</v>
+        <v>0.0271372562977918</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.03831577320777386</v>
+        <v>0.03831577320777393</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.02743759569607277</v>
+        <v>0.02743759569607274</v>
       </c>
       <c r="AI5" t="n">
         <v>0.01076738430900853</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.01364204623450146</v>
+        <v>0.01364204623450145</v>
       </c>
       <c r="AK5" t="n">
         <v>0.03085671220746983</v>
@@ -1227,31 +1227,31 @@
         <v>0.03561668204931327</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.02905743182946033</v>
+        <v>0.02905743182946036</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.02794904429365182</v>
+        <v>0.02794904429365181</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0351483673888362</v>
+        <v>0.03514836738883623</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.03560703337348028</v>
+        <v>0.03560703337348026</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.03921777024606543</v>
+        <v>0.03921777024606547</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.05160990264043091</v>
+        <v>0.05160990264043084</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.1021142596727985</v>
+        <v>0.1021142596727984</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.135048687656857</v>
+        <v>0.1350486876568567</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1758739954032645</v>
+        <v>0.1758739954032644</v>
       </c>
       <c r="AV5" t="n">
         <v>0.1749171466883628</v>
@@ -1267,136 +1267,136 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01801359554967606</v>
+        <v>0.01801359554967607</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01464362966747239</v>
+        <v>0.01464362966747237</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002489946642631805</v>
+        <v>0.002489946642631802</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03188791916090685</v>
+        <v>0.03188791916090686</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03109085794835961</v>
+        <v>0.03109085794835969</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04085271727140761</v>
+        <v>0.04085271727140759</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06012121573976388</v>
+        <v>0.06012121573976385</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02040653833744675</v>
+        <v>0.0204065383374467</v>
       </c>
       <c r="K6" t="n">
         <v>0.02126371784980564</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02488629204834375</v>
+        <v>0.02488629204834377</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02021554710828952</v>
+        <v>0.02021554710828954</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02131771072446403</v>
+        <v>0.02131771072446404</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02061415117482393</v>
+        <v>0.02061415117482398</v>
       </c>
       <c r="P6" t="n">
-        <v>0.007374824945742531</v>
+        <v>0.007374824945742538</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01107912739060176</v>
+        <v>0.01107912739060177</v>
       </c>
       <c r="R6" t="n">
-        <v>0.004437941888614976</v>
+        <v>0.004437941888614977</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008211961249722345</v>
+        <v>0.008211961249722351</v>
       </c>
       <c r="T6" t="n">
-        <v>0.006560860582429331</v>
+        <v>0.006560860582429323</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001752998485648419</v>
+        <v>0.001752998485648421</v>
       </c>
       <c r="V6" t="n">
-        <v>0.005199068873138043</v>
+        <v>0.005199068873138045</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003948144752094672</v>
+        <v>0.003948144752094671</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003277718212143625</v>
+        <v>0.00327771821214363</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009174250600605883</v>
+        <v>0.009174250600605893</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01107912739060176</v>
+        <v>0.01107912739060177</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009902183145036558</v>
+        <v>0.009902183145036554</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01278259046866457</v>
+        <v>0.01278259046866458</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01228073297527567</v>
+        <v>0.01228073297527569</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.006560860582429331</v>
+        <v>0.006560860582429323</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.009163423426702018</v>
+        <v>0.00916342342670202</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.006797602765881605</v>
+        <v>0.006797602765881611</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.003277718212143625</v>
+        <v>0.00327771821214363</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.005632965400009</v>
+        <v>0.005632965400008996</v>
       </c>
       <c r="AI6" t="n">
         <v>0.002398378715963113</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.003210681518564488</v>
+        <v>0.003210681518564486</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.003948144752094672</v>
+        <v>0.003948144752094671</v>
       </c>
       <c r="AL6" t="n">
         <v>0.005399813460394523</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.005708385939959978</v>
+        <v>0.005708385939959982</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.004918443303803645</v>
+        <v>0.004918443303803643</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.007374824945742531</v>
+        <v>0.007374824945742538</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.008247507311033837</v>
+        <v>0.008247507311033832</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.009698339935624741</v>
+        <v>0.009698339935624752</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.008808949703917983</v>
+        <v>0.008808949703917971</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.03109086374734005</v>
+        <v>0.03109086374734003</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.04762739494461515</v>
+        <v>0.04762739494461507</v>
       </c>
       <c r="AU6" t="n">
         <v>0.1137213043868968</v>
@@ -1418,139 +1418,139 @@
         <v>0.02668527424463491</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03075827077977365</v>
+        <v>0.03075827077977361</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009381091357426374</v>
+        <v>0.009381091357426362</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0351179208764085</v>
+        <v>0.03511792087640852</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01507648437251868</v>
+        <v>0.01507648437251871</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009302391838419285</v>
+        <v>0.000930239183841928</v>
       </c>
       <c r="I7" t="n">
         <v>0.01253649058968454</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02089598813472931</v>
+        <v>0.02089598813472925</v>
       </c>
       <c r="K7" t="n">
         <v>0.01467799322175407</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0146936619102909</v>
+        <v>0.01469366191029091</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02358276012616511</v>
+        <v>0.02358276012616514</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02209674286382302</v>
+        <v>0.02209674286382303</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02907387286035907</v>
+        <v>0.02907387286035912</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02068299264242732</v>
+        <v>0.02068299264242733</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02442613305290647</v>
+        <v>0.0244261330529065</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00877284021932073</v>
+        <v>0.008772840219320732</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03102773278730939</v>
+        <v>0.0310277327873094</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0167489939011201</v>
+        <v>0.01674899390112008</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0322948415743296</v>
+        <v>0.03229484157432963</v>
       </c>
       <c r="V7" t="n">
         <v>0.02183372663894574</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02264902952875893</v>
+        <v>0.02264902952875892</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0158492443101448</v>
+        <v>0.01584924431014483</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01255374885159436</v>
+        <v>0.01255374885159437</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.02442613305290647</v>
+        <v>0.0244261330529065</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02256819066836272</v>
+        <v>0.0225681906683627</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02180022149301409</v>
+        <v>0.0218002214930141</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03511587357980316</v>
+        <v>0.03511587357980322</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0167489939011201</v>
+        <v>0.01674899390112008</v>
       </c>
       <c r="AE7" t="n">
         <v>0.02019856944319753</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01391667058416713</v>
+        <v>0.01391667058416714</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0158492443101448</v>
+        <v>0.01584924431014483</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.02143347578061445</v>
+        <v>0.02143347578061443</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.006105094438475357</v>
+        <v>0.006105094438475355</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.008242919014147691</v>
+        <v>0.008242919014147686</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.02264902952875893</v>
+        <v>0.02264902952875892</v>
       </c>
       <c r="AL7" t="n">
         <v>0.01391902209668056</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.02154323789378704</v>
+        <v>0.02154323789378707</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.01914557976305303</v>
+        <v>0.01914557976305302</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.02068299264242732</v>
+        <v>0.02068299264242733</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.02125532333248263</v>
+        <v>0.02125532333248262</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.02139883216793191</v>
+        <v>0.02139883216793194</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.01205444123263639</v>
+        <v>0.01205444123263637</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0150764840087126</v>
+        <v>0.01507648400871258</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.01339055543123284</v>
+        <v>0.01339055543123282</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.008281746651451266</v>
+        <v>0.008281746651451264</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.008135751663499334</v>
+        <v>0.008135751663499335</v>
       </c>
     </row>
     <row r="8">
@@ -1566,139 +1566,139 @@
         <v>0.01610562731002609</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01995641059801948</v>
+        <v>0.01995641059801945</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006702813478767194</v>
+        <v>0.006702813478767185</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01661440359082067</v>
+        <v>0.01661440359082068</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01207595891798584</v>
+        <v>0.01207595891798587</v>
       </c>
       <c r="H8" t="n">
         <v>0.001013837204492321</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01022930078921933</v>
+        <v>0.01022930078921932</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0289803416961788</v>
+        <v>0.02898034169617873</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02188029255717675</v>
+        <v>0.02188029255717674</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02482609268714449</v>
+        <v>0.02482609268714451</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02544511299167182</v>
+        <v>0.02544511299167186</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02539153791519958</v>
+        <v>0.0253915379151996</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02723883043933851</v>
+        <v>0.02723883043933857</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01085045245244728</v>
+        <v>0.01085045245244729</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003791458831838833</v>
+        <v>0.003791458831838838</v>
       </c>
       <c r="R8" t="n">
-        <v>0.005397840475560894</v>
+        <v>0.005397840475560895</v>
       </c>
       <c r="S8" t="n">
         <v>0.01420143144934516</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01172004636591742</v>
+        <v>0.0117200463659174</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01883374592421826</v>
+        <v>0.01883374592421827</v>
       </c>
       <c r="V8" t="n">
         <v>0.009687868111955151</v>
       </c>
       <c r="W8" t="n">
-        <v>0.009873188679726844</v>
+        <v>0.009873188679726846</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01554498286099823</v>
+        <v>0.01554498286099825</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.006543507055078391</v>
+        <v>0.006543507055078401</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003791458831838833</v>
+        <v>0.003791458831838838</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01241187945286332</v>
+        <v>0.01241187945286331</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01069919198640815</v>
+        <v>0.01069919198640816</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.009512175640705925</v>
+        <v>0.009512175640705943</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.01172004636591742</v>
+        <v>0.0117200463659174</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0133943346191838</v>
+        <v>0.01339433461918381</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.009321032930323729</v>
+        <v>0.009321032930323736</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.01554498286099823</v>
+        <v>0.01554498286099825</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.01660885438179522</v>
+        <v>0.01660885438179521</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.00348025726088047</v>
+        <v>0.003480257260880471</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.003597492302077701</v>
+        <v>0.003597492302077699</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.009873188679726844</v>
+        <v>0.009873188679726846</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0119963389318053</v>
+        <v>0.01199633893180529</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.009600946070610614</v>
+        <v>0.009600946070610626</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.007289064389602124</v>
+        <v>0.007289064389602118</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.01085045245244728</v>
+        <v>0.01085045245244729</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.01302273476179075</v>
+        <v>0.01302273476179074</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0130103109344143</v>
+        <v>0.01301031093441432</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.006281900852482534</v>
+        <v>0.006281900852482526</v>
       </c>
       <c r="AS8" t="n">
         <v>0.01207595891433864</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.01266723381126817</v>
+        <v>0.01266723381126815</v>
       </c>
       <c r="AU8" t="n">
         <v>0.009642679759006935</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.008578843999649277</v>
+        <v>0.008578843999649279</v>
       </c>
     </row>
     <row r="9">
@@ -1711,19 +1711,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03003793062602001</v>
+        <v>0.03003793062602002</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02448974842775269</v>
+        <v>0.02448974842775266</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1977280736447042</v>
+        <v>0.197728073644704</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03814924040728879</v>
+        <v>0.03814924040728882</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0921271350072243</v>
+        <v>0.09212713500722448</v>
       </c>
       <c r="H9" t="n">
         <v>0.1085555456749797</v>
@@ -1732,28 +1732,28 @@
         <v>0.07068581154779126</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01802128033207422</v>
+        <v>0.01802128033207417</v>
       </c>
       <c r="K9" t="n">
         <v>0.01777531556201309</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0255419826277275</v>
+        <v>0.02554198262772753</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0136330085996364</v>
+        <v>0.01363300859963642</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02504537757058188</v>
+        <v>0.02504537757058189</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01342732600002916</v>
+        <v>0.01342732600002918</v>
       </c>
       <c r="P9" t="n">
-        <v>0.04840270976099847</v>
+        <v>0.04840270976099852</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05766980976054693</v>
+        <v>0.05766980976054704</v>
       </c>
       <c r="R9" t="n">
         <v>0.03458601774723295</v>
@@ -1762,10 +1762,10 @@
         <v>0.002382734480211703</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03422483278660506</v>
+        <v>0.03422483278660502</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002173060159329834</v>
+        <v>0.002173060159329835</v>
       </c>
       <c r="V9" t="n">
         <v>0.02056764192090162</v>
@@ -1774,79 +1774,79 @@
         <v>0.02350804493584362</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0184349093473433</v>
+        <v>0.01843490934734333</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01328953921604462</v>
+        <v>0.01328953921604463</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05766980976054693</v>
+        <v>0.05766980976054704</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.06951387151789437</v>
+        <v>0.06951387151789434</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.07878632984494488</v>
+        <v>0.07878632984494494</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.06839415505351558</v>
+        <v>0.06839415505351569</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.03422483278660506</v>
+        <v>0.03422483278660502</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.04579188012603737</v>
+        <v>0.04579188012603739</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.02527031487483591</v>
+        <v>0.02527031487483593</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0184349093473433</v>
+        <v>0.01843490934734333</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.01530152981107327</v>
+        <v>0.01530152981107325</v>
       </c>
       <c r="AI9" t="n">
         <v>0.01951902599527494</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.03357615119734306</v>
+        <v>0.03357615119734303</v>
       </c>
       <c r="AK9" t="n">
         <v>0.02350804493584362</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.03602165606595216</v>
+        <v>0.03602165606595217</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.05213475857027509</v>
+        <v>0.05213475857027515</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.08684078563854546</v>
+        <v>0.0868407856385454</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.04840270976099847</v>
+        <v>0.04840270976099852</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.04584597760603448</v>
+        <v>0.04584597760603446</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.04042721563830712</v>
+        <v>0.04042721563830717</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01276214549301327</v>
+        <v>0.01276214549301325</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.09212713390676122</v>
+        <v>0.09212713390676114</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.1248986806312365</v>
+        <v>0.1248986806312363</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.0618775148502824</v>
+        <v>0.06187751485028239</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0730238978738882</v>
+        <v>0.07302389787388817</v>
       </c>
     </row>
     <row r="10">
@@ -1859,136 +1859,136 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.007969434704446287</v>
+        <v>0.007969434704446289</v>
       </c>
       <c r="D10" t="n">
-        <v>0.009239208665947459</v>
+        <v>0.009239208665947449</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002013035458505036</v>
+        <v>0.0002013035458505034</v>
       </c>
       <c r="F10" t="n">
         <v>0.01176057563019389</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01027787720518142</v>
+        <v>0.01027787720518144</v>
       </c>
       <c r="H10" t="n">
-        <v>0.005016279495085693</v>
+        <v>0.00501627949508569</v>
       </c>
       <c r="I10" t="n">
-        <v>0.008890983149246176</v>
+        <v>0.008890983149246173</v>
       </c>
       <c r="J10" t="n">
-        <v>0.009706689689829774</v>
+        <v>0.00970668968982975</v>
       </c>
       <c r="K10" t="n">
-        <v>0.009492118960861369</v>
+        <v>0.009492118960861367</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009192083277655571</v>
+        <v>0.009192083277655579</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01074217129145727</v>
+        <v>0.01074217129145729</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01023429899730572</v>
+        <v>0.01023429899730573</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01226923837963137</v>
+        <v>0.01226923837963139</v>
       </c>
       <c r="P10" t="n">
-        <v>0.008077276215818295</v>
+        <v>0.008077276215818304</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.00553769005121799</v>
+        <v>0.005537690051217998</v>
       </c>
       <c r="R10" t="n">
         <v>0.002915777867061234</v>
       </c>
       <c r="S10" t="n">
-        <v>0.008878277550642038</v>
+        <v>0.008878277550642041</v>
       </c>
       <c r="T10" t="n">
-        <v>0.006950562374544822</v>
+        <v>0.006950562374544814</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01255706421352544</v>
+        <v>0.01255706421352545</v>
       </c>
       <c r="V10" t="n">
-        <v>0.008956724108616938</v>
+        <v>0.008956724108616941</v>
       </c>
       <c r="W10" t="n">
         <v>0.004869167673243544</v>
       </c>
       <c r="X10" t="n">
-        <v>0.005352589908753981</v>
+        <v>0.005352589908753989</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.008502193448769979</v>
+        <v>0.008502193448769988</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.00553769005121799</v>
+        <v>0.005537690051217998</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.005148197578419759</v>
+        <v>0.005148197578419757</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.006065205120427381</v>
+        <v>0.006065205120427385</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.004959576865429432</v>
+        <v>0.004959576865429439</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.006950562374544822</v>
+        <v>0.006950562374544814</v>
       </c>
       <c r="AE10" t="n">
         <v>0.00819773033977741</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.006936871966657036</v>
+        <v>0.006936871966657041</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.005352589908753981</v>
+        <v>0.005352589908753989</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.003794744197172357</v>
+        <v>0.003794744197172351</v>
       </c>
       <c r="AI10" t="n">
         <v>0.002236584036336501</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.003099166627137024</v>
+        <v>0.003099166627137022</v>
       </c>
       <c r="AK10" t="n">
         <v>0.004869167673243544</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.005352719985944503</v>
+        <v>0.005352719985944504</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.005824777361403945</v>
+        <v>0.005824777361403951</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.00452812907164381</v>
+        <v>0.004528129071643809</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.008077276215818295</v>
+        <v>0.008077276215818304</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.007077797108227351</v>
+        <v>0.007077797108227347</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.008129118707340703</v>
+        <v>0.008129118707340711</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.008167634098301112</v>
+        <v>0.0081676340983011</v>
       </c>
       <c r="AS10" t="n">
         <v>0.01027787816684388</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.01178691468394762</v>
+        <v>0.0117869146839476</v>
       </c>
       <c r="AU10" t="n">
         <v>0.00983255290885931</v>
@@ -2007,106 +2007,106 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01968754195640482</v>
+        <v>0.01968754195640483</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02365674501504237</v>
+        <v>0.02365674501504234</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00805637059982031</v>
+        <v>0.0080563705998203</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02293732150021104</v>
+        <v>0.02293732150021105</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02247905409275673</v>
+        <v>0.02247905409275677</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01210039068541793</v>
+        <v>0.01210039068541792</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01852813752794519</v>
+        <v>0.01852813752794518</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02344451259480272</v>
+        <v>0.02344451259480266</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02486154362018679</v>
+        <v>0.02486154362018678</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02081462141012928</v>
+        <v>0.0208146214101293</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02369205848109996</v>
+        <v>0.0236920584811</v>
       </c>
       <c r="N11" t="n">
-        <v>0.03190531666395741</v>
+        <v>0.03190531666395743</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02370778317401489</v>
+        <v>0.02370778317401492</v>
       </c>
       <c r="P11" t="n">
-        <v>0.02443382033985947</v>
+        <v>0.0244338203398595</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.02536440341133436</v>
+        <v>0.0253644034113344</v>
       </c>
       <c r="R11" t="n">
         <v>0.00601505494098595</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01941523123549633</v>
+        <v>0.01941523123549635</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02257216348506468</v>
+        <v>0.02257216348506465</v>
       </c>
       <c r="U11" t="n">
-        <v>0.03009557530377538</v>
+        <v>0.03009557530377541</v>
       </c>
       <c r="V11" t="n">
-        <v>0.02596848040089728</v>
+        <v>0.02596848040089729</v>
       </c>
       <c r="W11" t="n">
         <v>0.01138379119431268</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01685684530593229</v>
+        <v>0.01685684530593231</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01892461614805494</v>
+        <v>0.01892461614805497</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.02536440341133436</v>
+        <v>0.0253644034113344</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02767738535235642</v>
+        <v>0.0276773853523564</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.02717828285213625</v>
+        <v>0.02717828285213626</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01973022902692345</v>
+        <v>0.01973022902692349</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.02257216348506468</v>
+        <v>0.02257216348506465</v>
       </c>
       <c r="AE11" t="n">
         <v>0.02278511910493659</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01682966312263528</v>
+        <v>0.01682966312263529</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01685684530593229</v>
+        <v>0.01685684530593231</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.01227423151617284</v>
+        <v>0.01227423151617283</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.004139415792601293</v>
+        <v>0.004139415792601292</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.005744216237033705</v>
+        <v>0.005744216237033703</v>
       </c>
       <c r="AK11" t="n">
         <v>0.01138379119431268</v>
@@ -2115,28 +2115,28 @@
         <v>0.02038675560310028</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.01302500399523154</v>
+        <v>0.01302500399523155</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.01146587843474748</v>
+        <v>0.01146587843474747</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.02443382033985947</v>
+        <v>0.0244338203398595</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.02253861886786043</v>
+        <v>0.02253861886786042</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.02675688031598984</v>
+        <v>0.02675688031598986</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.01818878764704873</v>
+        <v>0.0181887876470487</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.02247905405140705</v>
+        <v>0.02247905405140704</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.02038965566678309</v>
+        <v>0.02038965566678305</v>
       </c>
       <c r="AU11" t="n">
         <v>0.01395605757738667</v>
@@ -2155,139 +2155,139 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04691379258160368</v>
+        <v>0.04691379258160369</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05466256102704491</v>
+        <v>0.05466256102704484</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01766790902346699</v>
+        <v>0.01766790902346697</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03990105651278403</v>
+        <v>0.03990105651278406</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04653702964286559</v>
+        <v>0.04653702964286565</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05568330248439931</v>
+        <v>0.05568330248439927</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0386596456737775</v>
+        <v>0.03865964567377748</v>
       </c>
       <c r="J12" t="n">
-        <v>0.06858640218335094</v>
+        <v>0.06858640218335074</v>
       </c>
       <c r="K12" t="n">
         <v>0.07758907794922799</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07663078687403616</v>
+        <v>0.0766307868740362</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0840862297629682</v>
+        <v>0.08408622976296834</v>
       </c>
       <c r="N12" t="n">
-        <v>0.03585899911597592</v>
+        <v>0.03585899911597594</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06141159864781777</v>
+        <v>0.06141159864781785</v>
       </c>
       <c r="P12" t="n">
-        <v>0.06013653618475307</v>
+        <v>0.06013653618475311</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07503954015194099</v>
+        <v>0.07503954015194111</v>
       </c>
       <c r="R12" t="n">
-        <v>0.03363501680715925</v>
+        <v>0.03363501680715926</v>
       </c>
       <c r="S12" t="n">
-        <v>0.08464884698811617</v>
+        <v>0.08464884698811619</v>
       </c>
       <c r="T12" t="n">
-        <v>0.05974803293173584</v>
+        <v>0.05974803293173576</v>
       </c>
       <c r="U12" t="n">
-        <v>0.05711576109952931</v>
+        <v>0.05711576109952936</v>
       </c>
       <c r="V12" t="n">
         <v>0.06314269970779542</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0414515089311858</v>
+        <v>0.04145150893118578</v>
       </c>
       <c r="X12" t="n">
-        <v>0.05038968431745432</v>
+        <v>0.05038968431745439</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.03275713395598297</v>
+        <v>0.032757133955983</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.07503954015194099</v>
+        <v>0.07503954015194111</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.04903409033500532</v>
+        <v>0.04903409033500528</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.06179395308923904</v>
+        <v>0.0617939530892391</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.04961395724639781</v>
+        <v>0.04961395724639788</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.05974803293173584</v>
+        <v>0.05974803293173576</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.05742920638873461</v>
+        <v>0.05742920638873463</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.04828504806656626</v>
+        <v>0.04828504806656629</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.05038968431745432</v>
+        <v>0.05038968431745439</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.03422128470828135</v>
+        <v>0.03422128470828133</v>
       </c>
       <c r="AI12" t="n">
         <v>0.02110343991837881</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.02312270576923989</v>
+        <v>0.02312270576923988</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0414515089311858</v>
+        <v>0.04145150893118578</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.04324281998544241</v>
+        <v>0.04324281998544242</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0571979783832897</v>
+        <v>0.05719797838328975</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.04028442295428192</v>
+        <v>0.0402844229542819</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.06013653618475307</v>
+        <v>0.06013653618475311</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.05298398301507968</v>
+        <v>0.05298398301507965</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.04905505629585478</v>
+        <v>0.04905505629585485</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.03145975735853711</v>
+        <v>0.03145975735853709</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.04653703148210696</v>
+        <v>0.04653703148210694</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.04945701786459859</v>
+        <v>0.04945701786459851</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.04012501481677797</v>
+        <v>0.04012501481677795</v>
       </c>
       <c r="AV12" t="n">
         <v>0.03705809203835898</v>
@@ -2306,139 +2306,139 @@
         <v>0.02570992287882265</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02719358321283881</v>
+        <v>0.02719358321283879</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0246356353999158</v>
+        <v>0.02463563539991577</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02923693689190343</v>
+        <v>0.02923693689190344</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0203639419076603</v>
+        <v>0.02036394190766034</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05038850334572796</v>
+        <v>0.05038850334572793</v>
       </c>
       <c r="I13" t="n">
         <v>0.01876494815562671</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0305529728653654</v>
+        <v>0.03055297286536532</v>
       </c>
       <c r="K13" t="n">
         <v>0.01908445918193271</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02290778993064254</v>
+        <v>0.02290778993064257</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03226998995953589</v>
+        <v>0.03226998995953591</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03053214900630186</v>
+        <v>0.03053214900630187</v>
       </c>
       <c r="O13" t="n">
-        <v>0.03703927566148601</v>
+        <v>0.03703927566148608</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01488870276642116</v>
+        <v>0.01488870276642117</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02107913177304386</v>
+        <v>0.0210791317730439</v>
       </c>
       <c r="R13" t="n">
         <v>0.004137897217856486</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01427805925298415</v>
+        <v>0.01427805925298416</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01529941270743615</v>
+        <v>0.01529941270743613</v>
       </c>
       <c r="U13" t="n">
-        <v>0.00146236920721918</v>
+        <v>0.001462369207219181</v>
       </c>
       <c r="V13" t="n">
-        <v>0.007349998808094112</v>
+        <v>0.007349998808094114</v>
       </c>
       <c r="W13" t="n">
-        <v>0.005897687597166973</v>
+        <v>0.005897687597166972</v>
       </c>
       <c r="X13" t="n">
-        <v>0.00655699497657856</v>
+        <v>0.00655699497657857</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.02020044683729252</v>
+        <v>0.02020044683729254</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.02107913177304386</v>
+        <v>0.0210791317730439</v>
       </c>
       <c r="AA13" t="n">
         <v>0.02057866705160773</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.02053811598726998</v>
+        <v>0.02053811598727</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.02270655688619336</v>
+        <v>0.02270655688619339</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01529941270743615</v>
+        <v>0.01529941270743613</v>
       </c>
       <c r="AE13" t="n">
         <v>0.01962561298042148</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01208275830140549</v>
+        <v>0.0120827583014055</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.00655699497657856</v>
+        <v>0.00655699497657857</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01239671849327435</v>
+        <v>0.01239671849327434</v>
       </c>
       <c r="AI13" t="n">
         <v>0.003377132477110651</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.004645828329695755</v>
+        <v>0.004645828329695754</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.005897687597166973</v>
+        <v>0.005897687597166972</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.007494999719542261</v>
+        <v>0.007494999719542263</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.01007447776191187</v>
+        <v>0.01007447776191188</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.00831202929939317</v>
+        <v>0.008312029299393167</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.01488870276642116</v>
+        <v>0.01488870276642117</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.01643788977977261</v>
+        <v>0.0164378897797726</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.01525357383160482</v>
+        <v>0.01525357383160483</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.01939250079906193</v>
+        <v>0.0193925007990619</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.02036394205183918</v>
+        <v>0.02036394205183916</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.02999318860597689</v>
+        <v>0.02999318860597684</v>
       </c>
       <c r="AU13" t="n">
         <v>0.04792237824059509</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.04513694512674223</v>
+        <v>0.04513694512674226</v>
       </c>
     </row>
     <row r="14">
@@ -2454,136 +2454,136 @@
         <v>0.01596740251737053</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01899487939553832</v>
+        <v>0.0189948793955383</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01167350811792752</v>
+        <v>0.0116735081179275</v>
       </c>
       <c r="F14" t="n">
         <v>0.01860180547733113</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01163738268700695</v>
+        <v>0.01163738268700698</v>
       </c>
       <c r="H14" t="n">
-        <v>0.003486768567887808</v>
+        <v>0.003486768567887806</v>
       </c>
       <c r="I14" t="n">
-        <v>0.005466535004870198</v>
+        <v>0.005466535004870197</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02770434591344084</v>
+        <v>0.02770434591344077</v>
       </c>
       <c r="K14" t="n">
         <v>0.01911657037372011</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02265595633446633</v>
+        <v>0.02265595633446636</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02551903024389265</v>
+        <v>0.0255190302438927</v>
       </c>
       <c r="N14" t="n">
-        <v>0.02948546477629293</v>
+        <v>0.02948546477629294</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0240489914323811</v>
+        <v>0.02404899143238115</v>
       </c>
       <c r="P14" t="n">
-        <v>0.01337083331440406</v>
+        <v>0.01337083331440407</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01584074372882486</v>
+        <v>0.01584074372882489</v>
       </c>
       <c r="R14" t="n">
-        <v>0.008243495387122535</v>
+        <v>0.008243495387122537</v>
       </c>
       <c r="S14" t="n">
-        <v>0.009580073131429513</v>
+        <v>0.009580073131429516</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01228949868310249</v>
+        <v>0.01228949868310248</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01705416319667236</v>
+        <v>0.01705416319667238</v>
       </c>
       <c r="V14" t="n">
-        <v>0.006737548111218034</v>
+        <v>0.006737548111218036</v>
       </c>
       <c r="W14" t="n">
-        <v>0.008380715697925836</v>
+        <v>0.008380715697925837</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01162255551985849</v>
+        <v>0.01162255551985852</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.01002657957110216</v>
+        <v>0.01002657957110217</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.01584074372882486</v>
+        <v>0.01584074372882489</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01733421718434069</v>
+        <v>0.01733421718434068</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.02001253595189928</v>
+        <v>0.02001253595189929</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.01459227131093671</v>
+        <v>0.01459227131093673</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.01228949868310249</v>
+        <v>0.01228949868310248</v>
       </c>
       <c r="AE14" t="n">
         <v>0.01328052963155595</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.005803059268781564</v>
+        <v>0.005803059268781568</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.01162255551985849</v>
+        <v>0.01162255551985852</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.008447073466946408</v>
+        <v>0.008447073466946399</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.005232411165766437</v>
+        <v>0.005232411165766436</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.007465772163223231</v>
+        <v>0.007465772163223227</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.008380715697925836</v>
+        <v>0.008380715697925837</v>
       </c>
       <c r="AL14" t="n">
         <v>0.009623984706580671</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.007528493149464917</v>
+        <v>0.007528493149464925</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.006186006024662376</v>
+        <v>0.006186006024662374</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.01337083331440406</v>
+        <v>0.01337083331440407</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.01288662432190082</v>
+        <v>0.01288662432190081</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.01446137624893113</v>
+        <v>0.01446137624893115</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.009625926052572285</v>
+        <v>0.009625926052572275</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.01163738420548913</v>
+        <v>0.01163738420548912</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.009381443922646136</v>
+        <v>0.009381443922646122</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.006755180260962427</v>
+        <v>0.006755180260962426</v>
       </c>
       <c r="AV14" t="n">
         <v>0.006732321300935751</v>
@@ -2599,61 +2599,61 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.04565277944774081</v>
+        <v>0.04565277944774082</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03646708357934478</v>
+        <v>0.03646708357934474</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02246147949753732</v>
+        <v>0.02246147949753729</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03260879870050237</v>
+        <v>0.03260879870050239</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06985931359635199</v>
+        <v>0.06985931359635215</v>
       </c>
       <c r="H15" t="n">
-        <v>0.04265590006749601</v>
+        <v>0.04265590006749599</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0153438973173323</v>
+        <v>0.01534389731733229</v>
       </c>
       <c r="J15" t="n">
-        <v>0.04375174033753283</v>
+        <v>0.04375174033753272</v>
       </c>
       <c r="K15" t="n">
-        <v>0.05843838623097117</v>
+        <v>0.05843838623097116</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05082469998474639</v>
+        <v>0.05082469998474645</v>
       </c>
       <c r="M15" t="n">
-        <v>0.03395284860874122</v>
+        <v>0.03395284860874127</v>
       </c>
       <c r="N15" t="n">
-        <v>0.04249735772100271</v>
+        <v>0.04249735772100274</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02775113368832104</v>
+        <v>0.02775113368832109</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0367370662983726</v>
+        <v>0.03673706629837264</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.03545005568136742</v>
+        <v>0.03545005568136748</v>
       </c>
       <c r="R15" t="n">
-        <v>0.02722753182061511</v>
+        <v>0.02722753182061512</v>
       </c>
       <c r="S15" t="n">
-        <v>0.05354623499454857</v>
+        <v>0.05354623499454859</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03842910954322114</v>
+        <v>0.0384291095432211</v>
       </c>
       <c r="U15" t="n">
-        <v>0.02498925673336978</v>
+        <v>0.02498925673336981</v>
       </c>
       <c r="V15" t="n">
         <v>0.06939257058617772</v>
@@ -2662,73 +2662,73 @@
         <v>0.02925553694067734</v>
       </c>
       <c r="X15" t="n">
-        <v>0.04485258117447827</v>
+        <v>0.04485258117447834</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2210394840839337</v>
+        <v>0.221039484083934</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.03545005568136742</v>
+        <v>0.03545005568136748</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.03512542272689704</v>
+        <v>0.03512542272689702</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.03773398664127424</v>
+        <v>0.03773398664127425</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.05432210267699323</v>
+        <v>0.05432210267699331</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.03842910954322114</v>
+        <v>0.0384291095432211</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.04755797548032309</v>
+        <v>0.0475579754803231</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.02553465840510527</v>
+        <v>0.02553465840510529</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.04485258117447827</v>
+        <v>0.04485258117447834</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0274620058672935</v>
+        <v>0.02746200586729347</v>
       </c>
       <c r="AI15" t="n">
         <v>0.01661101092049267</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.02518282945169372</v>
+        <v>0.02518282945169371</v>
       </c>
       <c r="AK15" t="n">
         <v>0.02925553694067734</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.04280224839820403</v>
+        <v>0.04280224839820402</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.03806041341973873</v>
+        <v>0.03806041341973877</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.03370343585037058</v>
+        <v>0.03370343585037056</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0367370662983726</v>
+        <v>0.03673706629837264</v>
       </c>
       <c r="AP15" t="n">
         <v>0.04336736478662775</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.04336552274514158</v>
+        <v>0.04336552274514164</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.2116038032717424</v>
+        <v>0.2116038032717421</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.06985929798355527</v>
+        <v>0.06985929798355522</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.04892337225944093</v>
+        <v>0.04892337225944084</v>
       </c>
       <c r="AU15" t="n">
         <v>0.02863331861553277</v>
@@ -2750,56 +2750,56 @@
         <v>0.002648188816115491</v>
       </c>
       <c r="D16" t="n">
-        <v>0.003149964416983359</v>
+        <v>0.003149964416983355</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0007441501380025561</v>
+        <v>0.0007441501380025551</v>
       </c>
       <c r="F16" t="n">
-        <v>0.002397922847592523</v>
+        <v>0.002397922847592524</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0007518229663189841</v>
+        <v>0.0007518229663189857</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0003878368055433996</v>
+        <v>0.0003878368055433994</v>
       </c>
       <c r="I16" t="n">
-        <v>2.733084860419375e-05</v>
+        <v>2.733084860419373e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001639830104667513</v>
+        <v>0.001639830104667509</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0007243519153011242</v>
+        <v>0.000724351915301124</v>
       </c>
       <c r="L16" t="n">
-        <v>0.002409187220942709</v>
+        <v>0.00240918722094271</v>
       </c>
       <c r="M16" t="n">
-        <v>0.001009858695007763</v>
+        <v>0.001009858695007765</v>
       </c>
       <c r="N16" t="n">
-        <v>0.002415551832007998</v>
+        <v>0.002415551832008</v>
       </c>
       <c r="O16" t="n">
-        <v>0.001197492560267215</v>
+        <v>0.001197492560267217</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0006997509331795862</v>
+        <v>0.0006997509331795868</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.001686322372213509</v>
+        <v>0.001686322372213512</v>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>0.000473108692632095</v>
+        <v>0.0004731086926320952</v>
       </c>
       <c r="T16" t="n">
-        <v>0.001675335280008557</v>
+        <v>0.001675335280008555</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0009023992587609453</v>
+        <v>0.0009023992587609462</v>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
@@ -2807,35 +2807,35 @@
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>0.0006794595211248414</v>
+        <v>0.0006794595211248421</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.001686322372213509</v>
+        <v>0.001686322372213512</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.002115616729237587</v>
+        <v>0.002115616729237586</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.001911137345477046</v>
+        <v>0.001911137345477047</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.002622729467348767</v>
+        <v>0.002622729467348771</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.001675335280008557</v>
+        <v>0.001675335280008555</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.002128330171982691</v>
+        <v>0.002128330171982692</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0005431513901832597</v>
+        <v>0.0005431513901832601</v>
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>0.001884806261206804</v>
+        <v>0.001884806261206802</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0003914478778935616</v>
+        <v>0.0003914478778935615</v>
       </c>
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="n">
@@ -2845,28 +2845,28 @@
         <v>0.0006952458709269487</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.0006388733128033177</v>
+        <v>0.0006388733128033184</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.0001768145187214988</v>
+        <v>0.0001768145187214987</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.0006997509331795862</v>
+        <v>0.0006997509331795868</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.001045804630192497</v>
+        <v>0.001045804630192496</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.001001649000965316</v>
+        <v>0.001001649000965317</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.000652535325892692</v>
+        <v>0.0006525353258926911</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0007518229250073262</v>
+        <v>0.0007518229250073255</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.001933648018400699</v>
+        <v>0.001933648018400696</v>
       </c>
       <c r="AU16" t="n">
         <v>0.001239434162267051</v>
@@ -2888,106 +2888,106 @@
         <v>0.01508911210854986</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01814463829228772</v>
+        <v>0.0181446382922877</v>
       </c>
       <c r="E17" t="n">
-        <v>0.009896680188257229</v>
+        <v>0.009896680188257217</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02035400181476603</v>
+        <v>0.02035400181476604</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02055270219555751</v>
+        <v>0.02055270219555755</v>
       </c>
       <c r="H17" t="n">
-        <v>0.005371670701066077</v>
+        <v>0.005371670701066074</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01000677286278153</v>
+        <v>0.01000677286278152</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02832663192976222</v>
+        <v>0.02832663192976215</v>
       </c>
       <c r="K17" t="n">
         <v>0.02024837671477004</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02019423421924793</v>
+        <v>0.02019423421924794</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02540904546457602</v>
+        <v>0.02540904546457605</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01535002023601476</v>
+        <v>0.01535002023601477</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0262475788369064</v>
+        <v>0.02624757883690644</v>
       </c>
       <c r="P17" t="n">
-        <v>0.01675924355014466</v>
+        <v>0.01675924355014467</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01192771703232495</v>
+        <v>0.01192771703232497</v>
       </c>
       <c r="R17" t="n">
-        <v>0.00599398126776697</v>
+        <v>0.005993981267766969</v>
       </c>
       <c r="S17" t="n">
         <v>0.0171013489030094</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01391163118366296</v>
+        <v>0.01391163118366294</v>
       </c>
       <c r="U17" t="n">
-        <v>0.02066443348086046</v>
+        <v>0.02066443348086049</v>
       </c>
       <c r="V17" t="n">
         <v>0.01431448096356618</v>
       </c>
       <c r="W17" t="n">
-        <v>0.008870169144319963</v>
+        <v>0.008870169144319961</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01330738287825786</v>
+        <v>0.01330738287825787</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.01590270038605066</v>
+        <v>0.01590270038605068</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.01192771703232495</v>
+        <v>0.01192771703232497</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.01381047602426165</v>
+        <v>0.01381047602426164</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.01497815386540063</v>
+        <v>0.01497815386540064</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.01028883320716912</v>
+        <v>0.01028883320716914</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.01391163118366296</v>
+        <v>0.01391163118366294</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.01459525459965522</v>
+        <v>0.01459525459965523</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.009875140109358926</v>
+        <v>0.009875140109358936</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.01330738287825786</v>
+        <v>0.01330738287825787</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.01499525906872153</v>
+        <v>0.01499525906872152</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.004732434027086429</v>
+        <v>0.004732434027086428</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.006670874625803288</v>
+        <v>0.006670874625803285</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.008870169144319963</v>
+        <v>0.008870169144319961</v>
       </c>
       <c r="AL17" t="n">
         <v>0.01277346479681219</v>
@@ -2996,25 +2996,25 @@
         <v>0.01121969316362675</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.009421799784815577</v>
+        <v>0.009421799784815572</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.01675924355014466</v>
+        <v>0.01675924355014467</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.01626126272074382</v>
+        <v>0.01626126272074381</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.01638144132178146</v>
+        <v>0.01638144132178148</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.0152702890012064</v>
+        <v>0.01527028900120638</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.02055270308534596</v>
+        <v>0.02055270308534594</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.01517623648384747</v>
+        <v>0.01517623648384744</v>
       </c>
       <c r="AU17" t="n">
         <v>0.01066420968396497</v>
@@ -3036,52 +3036,52 @@
         <v>0.001888703513920666</v>
       </c>
       <c r="D18" t="n">
-        <v>0.002321971778228869</v>
+        <v>0.002321971778228865</v>
       </c>
       <c r="E18" t="n">
-        <v>0.004113405213802103</v>
+        <v>0.004113405213802098</v>
       </c>
       <c r="F18" t="n">
-        <v>0.002424223251022408</v>
+        <v>0.002424223251022409</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0006196681882826364</v>
+        <v>0.0006196681882826379</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>0.003333887986000897</v>
+        <v>0.003333887986000888</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0009676892158089861</v>
+        <v>0.0009676892158089859</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0005568553401404404</v>
+        <v>0.0005568553401404409</v>
       </c>
       <c r="M18" t="n">
-        <v>0.002930099709995847</v>
+        <v>0.002930099709995851</v>
       </c>
       <c r="N18" t="n">
-        <v>0.003501935575141041</v>
+        <v>0.003501935575141044</v>
       </c>
       <c r="O18" t="n">
-        <v>0.001730666194990889</v>
+        <v>0.001730666194990892</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0006747035821673959</v>
+        <v>0.0006747035821673967</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.001724130265521345</v>
+        <v>0.001724130265521348</v>
       </c>
       <c r="R18" t="n">
-        <v>0.000532356034254441</v>
+        <v>0.0005323560342544411</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="n">
-        <v>0.001026469510663689</v>
+        <v>0.001026469510663688</v>
       </c>
       <c r="U18" t="n">
-        <v>0.001065993130988806</v>
+        <v>0.001065993130988807</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
@@ -3089,34 +3089,34 @@
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="n">
-        <v>0.0004165818083892711</v>
+        <v>0.0004165818083892716</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.001724130265521345</v>
+        <v>0.001724130265521348</v>
       </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="n">
-        <v>0.002626502945186442</v>
+        <v>0.002626502945186444</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.0019803047954102</v>
+        <v>0.001980304795410202</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.001026469510663689</v>
+        <v>0.001026469510663688</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0005578298140274535</v>
+        <v>0.0005578298140274537</v>
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="n">
-        <v>0.000745206949275753</v>
+        <v>0.0007452069492757524</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.0007508993974528795</v>
+        <v>0.0007508993974528794</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.001547261108610941</v>
+        <v>0.00154726110861094</v>
       </c>
       <c r="AK18" t="n">
         <v>0.0003960737048540662</v>
@@ -3126,25 +3126,25 @@
       </c>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="n">
-        <v>0.0006691410585460338</v>
+        <v>0.0006691410585460335</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.0006747035821673959</v>
+        <v>0.0006747035821673967</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.000727386285875777</v>
+        <v>0.0007273862858757767</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.001341950654180133</v>
+        <v>0.001341950654180135</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.0004000554319556307</v>
+        <v>0.0004000554319556301</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.0006196682113742896</v>
+        <v>0.000619668211374289</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.0005930841110288237</v>
+        <v>0.0005930841110288228</v>
       </c>
       <c r="AU18" t="n">
         <v>0.0004504674033636771</v>
@@ -3163,102 +3163,102 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.003427172203748919</v>
+        <v>0.003427172203748921</v>
       </c>
       <c r="D19" t="n">
-        <v>0.003325867650737401</v>
+        <v>0.003325867650737397</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0.00400508574229583</v>
+        <v>0.004005085742295833</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001656440443452466</v>
+        <v>0.001656440443452469</v>
       </c>
       <c r="H19" t="n">
-        <v>0.002177850417633975</v>
+        <v>0.002177850417633974</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>0.002910754032875178</v>
+        <v>0.00291075403287517</v>
       </c>
       <c r="K19" t="n">
         <v>0.001930493447867452</v>
       </c>
       <c r="L19" t="n">
-        <v>0.003135297439814007</v>
+        <v>0.003135297439814009</v>
       </c>
       <c r="M19" t="n">
-        <v>0.003008102218773029</v>
+        <v>0.003008102218773033</v>
       </c>
       <c r="N19" t="n">
-        <v>0.003153617723996679</v>
+        <v>0.003153617723996681</v>
       </c>
       <c r="O19" t="n">
-        <v>0.001515360696168917</v>
+        <v>0.00151536069616892</v>
       </c>
       <c r="P19" t="n">
-        <v>0.006609697058738297</v>
+        <v>0.006609697058738303</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.006132152828809847</v>
+        <v>0.006132152828809857</v>
       </c>
       <c r="R19" t="n">
-        <v>0.001394469185541929</v>
+        <v>0.00139446918554193</v>
       </c>
       <c r="S19" t="n">
         <v>0.01017327419834081</v>
       </c>
       <c r="T19" t="n">
-        <v>0.003802435832079264</v>
+        <v>0.003802435832079259</v>
       </c>
       <c r="U19" t="n">
-        <v>0.009654051011266809</v>
+        <v>0.009654051011266818</v>
       </c>
       <c r="V19" t="n">
-        <v>0.005736592125913028</v>
+        <v>0.00573659212591303</v>
       </c>
       <c r="W19" t="n">
         <v>0.009854202301420737</v>
       </c>
       <c r="X19" t="n">
-        <v>0.004137711175457683</v>
+        <v>0.00413771117545769</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.0001665016801793567</v>
+        <v>0.0001665016801793569</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.006132152828809847</v>
+        <v>0.006132152828809857</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.008692642421748137</v>
+        <v>0.008692642421748133</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.007880953130576688</v>
+        <v>0.007880953130576693</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.01572550621664425</v>
+        <v>0.01572550621664428</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.003802435832079264</v>
+        <v>0.003802435832079259</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.005451876967777461</v>
+        <v>0.005451876967777463</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.00585066652692093</v>
+        <v>0.005850666526920934</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.004137711175457683</v>
+        <v>0.00413771117545769</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.008878117393244822</v>
+        <v>0.008878117393244813</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.0008244624207949783</v>
+        <v>0.0008244624207949782</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.001719363618773933</v>
+        <v>0.001719363618773932</v>
       </c>
       <c r="AK19" t="n">
         <v>0.009854202301420737</v>
@@ -3267,31 +3267,31 @@
         <v>0.001567230107631244</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.006674386659331813</v>
+        <v>0.00667438665933182</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.007785976952505757</v>
+        <v>0.007785976952505752</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.006609697058738297</v>
+        <v>0.006609697058738303</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.006431572998238645</v>
+        <v>0.006431572998238642</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.005160251781366997</v>
+        <v>0.005160251781367003</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.0001600825814551733</v>
+        <v>0.0001600825814551731</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.001656440540751577</v>
+        <v>0.001656440540751576</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.001363135310381943</v>
+        <v>0.001363135310381941</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.0008715860530628554</v>
+        <v>0.0008715860530628553</v>
       </c>
       <c r="AV19" t="n">
         <v>0.001122340732986495</v>
@@ -3307,98 +3307,98 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.007117196037025438</v>
+        <v>0.00711719603702544</v>
       </c>
       <c r="D20" t="n">
-        <v>0.007564016944911361</v>
+        <v>0.007564016944911353</v>
       </c>
       <c r="E20" t="n">
-        <v>0.005236144563730797</v>
+        <v>0.00523614456373079</v>
       </c>
       <c r="F20" t="n">
-        <v>0.002751587269614753</v>
+        <v>0.002751587269614754</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003214815723860707</v>
+        <v>0.003214815723860713</v>
       </c>
       <c r="H20" t="n">
         <v>0.01141962863643517</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01060255439498923</v>
+        <v>0.01060255439498922</v>
       </c>
       <c r="J20" t="n">
-        <v>0.004479590539263454</v>
+        <v>0.004479590539263442</v>
       </c>
       <c r="K20" t="n">
-        <v>0.002891210590843884</v>
+        <v>0.002891210590843883</v>
       </c>
       <c r="L20" t="n">
-        <v>0.008110601354382808</v>
+        <v>0.008110601354382815</v>
       </c>
       <c r="M20" t="n">
-        <v>0.006001676625700885</v>
+        <v>0.006001676625700895</v>
       </c>
       <c r="N20" t="n">
-        <v>0.004914879031991477</v>
+        <v>0.00491487903199148</v>
       </c>
       <c r="O20" t="n">
-        <v>0.004105255004105041</v>
+        <v>0.004105255004105047</v>
       </c>
       <c r="P20" t="n">
-        <v>0.008485224622020402</v>
+        <v>0.00848522462202041</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.002634526775646649</v>
+        <v>0.002634526775646653</v>
       </c>
       <c r="R20" t="n">
-        <v>0.001318405632612097</v>
+        <v>0.001318405632612098</v>
       </c>
       <c r="S20" t="n">
-        <v>0.006223125408572706</v>
+        <v>0.006223125408572707</v>
       </c>
       <c r="T20" t="n">
-        <v>0.01223414957309873</v>
+        <v>0.01223414957309872</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.009990287373709241</v>
+        <v>0.009990287373709243</v>
       </c>
       <c r="W20" t="n">
         <v>0.009619159236047548</v>
       </c>
       <c r="X20" t="n">
-        <v>0.003679496861099086</v>
+        <v>0.003679496861099091</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.002562210779130057</v>
+        <v>0.002562210779130059</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.002634526775646649</v>
+        <v>0.002634526775646653</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.002654596949375634</v>
+        <v>0.002654596949375632</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.002531618201662161</v>
+        <v>0.002531618201662163</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.003812779452409425</v>
+        <v>0.003812779452409431</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.01223414957309873</v>
+        <v>0.01223414957309872</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.01129645841232138</v>
+        <v>0.01129645841232139</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.01976422185051175</v>
+        <v>0.01976422185051176</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.003679496861099086</v>
+        <v>0.003679496861099091</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.003117197163796458</v>
+        <v>0.003117197163796455</v>
       </c>
       <c r="AI20" t="n">
         <v>0.0009962981326846697</v>
@@ -3413,31 +3413,31 @@
         <v>0.011464350551323</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.004082809958381031</v>
+        <v>0.004082809958381035</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.005013403772161974</v>
+        <v>0.005013403772161971</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.008485224622020402</v>
+        <v>0.00848522462202041</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.007338571012212878</v>
+        <v>0.007338571012212874</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.007106525388212119</v>
+        <v>0.007106525388212127</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.002461282486214912</v>
+        <v>0.002461282486214909</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.00321481597846164</v>
+        <v>0.003214815978461637</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.005242223237188721</v>
+        <v>0.005242223237188711</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.02125819084378414</v>
+        <v>0.02125819084378413</v>
       </c>
       <c r="AV20" t="n">
         <v>0.02118813288594133</v>
@@ -3453,106 +3453,106 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.009944093122489086</v>
+        <v>0.009944093122489089</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0122430905349501</v>
+        <v>0.01224309053495008</v>
       </c>
       <c r="E21" t="n">
-        <v>0.009600132677067845</v>
+        <v>0.009600132677067833</v>
       </c>
       <c r="F21" t="n">
-        <v>0.008003246515223985</v>
+        <v>0.008003246515223989</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0118922263786514</v>
+        <v>0.01189222637865142</v>
       </c>
       <c r="H21" t="n">
-        <v>0.009521790679859291</v>
+        <v>0.009521790679859282</v>
       </c>
       <c r="I21" t="n">
-        <v>0.009896083393405348</v>
+        <v>0.009896083393405345</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0146945151200945</v>
+        <v>0.01469451512009446</v>
       </c>
       <c r="K21" t="n">
         <v>0.02140413199392973</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01795406318491858</v>
+        <v>0.0179540631849186</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01920549008142503</v>
+        <v>0.01920549008142506</v>
       </c>
       <c r="N21" t="n">
-        <v>0.007712452415307077</v>
+        <v>0.007712452415307082</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01131926524766272</v>
+        <v>0.01131926524766274</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0125305513627588</v>
+        <v>0.01253055136275882</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.01548658707775759</v>
+        <v>0.01548658707775762</v>
       </c>
       <c r="R21" t="n">
         <v>0.01020050140239543</v>
       </c>
       <c r="S21" t="n">
-        <v>0.03343726021333207</v>
+        <v>0.03343726021333208</v>
       </c>
       <c r="T21" t="n">
-        <v>0.01430803663819668</v>
+        <v>0.01430803663819666</v>
       </c>
       <c r="U21" t="n">
-        <v>0.01123236539173616</v>
+        <v>0.01123236539173617</v>
       </c>
       <c r="V21" t="n">
-        <v>0.01598354820068666</v>
+        <v>0.01598354820068667</v>
       </c>
       <c r="W21" t="n">
         <v>0.009890653740333785</v>
       </c>
       <c r="X21" t="n">
-        <v>0.01696158180128777</v>
+        <v>0.01696158180128779</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.0006631998247969375</v>
+        <v>0.0006631998247969383</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.01548658707775759</v>
+        <v>0.01548658707775762</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.01245261080099493</v>
+        <v>0.01245261080099492</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.002700919514295396</v>
+        <v>0.002700919514295398</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.007236996649184875</v>
+        <v>0.007236996649184885</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.01430803663819668</v>
+        <v>0.01430803663819666</v>
       </c>
       <c r="AE21" t="n">
         <v>0.01230069073490908</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.009586146677205953</v>
+        <v>0.009586146677205958</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.01696158180128777</v>
+        <v>0.01696158180128779</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.01143014158647154</v>
+        <v>0.01143014158647153</v>
       </c>
       <c r="AI21" t="n">
         <v>0.006046584873729402</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.006903297497864835</v>
+        <v>0.006903297497864831</v>
       </c>
       <c r="AK21" t="n">
         <v>0.009890653740333785</v>
@@ -3561,34 +3561,34 @@
         <v>0.01025200318510243</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.02193720518501976</v>
+        <v>0.02193720518501979</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.0150528867761288</v>
+        <v>0.01505288677612879</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.0125305513627588</v>
+        <v>0.01253055136275882</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.01162511156931564</v>
+        <v>0.01162511156931563</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.01140593306169787</v>
+        <v>0.01140593306169788</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.0006373553768122537</v>
+        <v>0.0006373553768122529</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.0118922273636129</v>
+        <v>0.01189222736361289</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.01659067516656193</v>
+        <v>0.0165906751665619</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.01195796442712615</v>
+        <v>0.01195796442712616</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.009816628113679929</v>
+        <v>0.009816628113679933</v>
       </c>
     </row>
     <row r="22">
@@ -3604,44 +3604,44 @@
         <v>0.001221843976643471</v>
       </c>
       <c r="D22" t="n">
-        <v>0.001658516623002498</v>
+        <v>0.001658516623002496</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.001445643722235353</v>
+        <v>0.001445643722235354</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0004819097648255641</v>
+        <v>0.000481909764825565</v>
       </c>
       <c r="H22" t="n">
-        <v>7.558020936972019e-05</v>
+        <v>7.558020936972015e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>0.001094037493690462</v>
+        <v>0.001094037493690461</v>
       </c>
       <c r="J22" t="n">
-        <v>0.001619882792146431</v>
+        <v>0.001619882792146427</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0007794360383832566</v>
+        <v>0.0007794360383832564</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0005010294847054898</v>
+        <v>0.0005010294847054902</v>
       </c>
       <c r="M22" t="n">
-        <v>0.001359774514165229</v>
+        <v>0.00135977451416523</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0006206270361239028</v>
+        <v>0.0006206270361239032</v>
       </c>
       <c r="O22" t="n">
-        <v>0.001907331965071007</v>
+        <v>0.00190733196507101</v>
       </c>
       <c r="P22" t="n">
-        <v>0.001725033846986429</v>
+        <v>0.001725033846986431</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.002301049165517837</v>
+        <v>0.002301049165517841</v>
       </c>
       <c r="R22" t="n">
         <v>0.001548599122205448</v>
@@ -3650,55 +3650,55 @@
         <v>0.001162757851478784</v>
       </c>
       <c r="T22" t="n">
-        <v>0.002110014926724083</v>
+        <v>0.002110014926724081</v>
       </c>
       <c r="U22" t="n">
-        <v>0.002940517043387342</v>
+        <v>0.002940517043387345</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0006955830551549938</v>
+        <v>0.000695583055154994</v>
       </c>
       <c r="W22" t="n">
         <v>0.001251018516390445</v>
       </c>
       <c r="X22" t="n">
-        <v>0.001522823531475058</v>
+        <v>0.001522823531475061</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.0008998855953901335</v>
+        <v>0.0008998855953901346</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.002301049165517837</v>
+        <v>0.002301049165517841</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.002023771278280159</v>
+        <v>0.002023771278280158</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.002475516435743855</v>
+        <v>0.002475516435743856</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.002853931924023541</v>
+        <v>0.002853931924023546</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.002110014926724083</v>
+        <v>0.002110014926724081</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.002669708563860698</v>
+        <v>0.002669708563860699</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.001670054735380762</v>
+        <v>0.001670054735380763</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.001522823531475058</v>
+        <v>0.001522823531475061</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.001826124578724754</v>
+        <v>0.001826124578724752</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.000955521385104598</v>
+        <v>0.0009555213851045979</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.001229428094523409</v>
+        <v>0.001229428094523408</v>
       </c>
       <c r="AK22" t="n">
         <v>0.001251018516390445</v>
@@ -3707,28 +3707,28 @@
         <v>0.001656151602029605</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.0009548532739717959</v>
+        <v>0.0009548532739717968</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.0007186395616616819</v>
+        <v>0.0007186395616616813</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.001725033846986429</v>
+        <v>0.001725033846986431</v>
       </c>
       <c r="AP22" t="n">
         <v>0.002234674972706947</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.0024288169135638</v>
+        <v>0.002428816913563803</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.0008637435482175386</v>
+        <v>0.0008637435482175374</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.0004819097535182122</v>
+        <v>0.0004819097535182118</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.0005156680369076729</v>
+        <v>0.000515668036907672</v>
       </c>
       <c r="AU22" t="n">
         <v>0.0003513750427094952</v>
@@ -3750,103 +3750,103 @@
         <v>0.01067497274085898</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01200548920254552</v>
+        <v>0.0120054892025455</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02322318204386806</v>
+        <v>0.02322318204386803</v>
       </c>
       <c r="F23" t="n">
         <v>0.01075769273372761</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01241231284836333</v>
+        <v>0.01241231284836336</v>
       </c>
       <c r="H23" t="n">
-        <v>0.02710723059280148</v>
+        <v>0.02710723059280146</v>
       </c>
       <c r="I23" t="n">
-        <v>0.006853841003095725</v>
+        <v>0.006853841003095722</v>
       </c>
       <c r="J23" t="n">
-        <v>0.01682246792784011</v>
+        <v>0.01682246792784007</v>
       </c>
       <c r="K23" t="n">
-        <v>0.01595668799190649</v>
+        <v>0.01595668799190648</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01773473410770577</v>
+        <v>0.01773473410770578</v>
       </c>
       <c r="M23" t="n">
-        <v>0.01672406116952879</v>
+        <v>0.01672406116952882</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0235283996302639</v>
+        <v>0.02352839963026392</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01559591582624298</v>
+        <v>0.015595915826243</v>
       </c>
       <c r="P23" t="n">
-        <v>0.01032077375336816</v>
+        <v>0.01032077375336817</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.01283094429899817</v>
+        <v>0.01283094429899819</v>
       </c>
       <c r="R23" t="n">
-        <v>0.003574644930110901</v>
+        <v>0.003574644930110902</v>
       </c>
       <c r="S23" t="n">
-        <v>0.01276505974893639</v>
+        <v>0.0127650597489364</v>
       </c>
       <c r="T23" t="n">
-        <v>0.01068635105181155</v>
+        <v>0.01068635105181153</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01235276711578797</v>
+        <v>0.01235276711578798</v>
       </c>
       <c r="V23" t="n">
-        <v>0.007115302850536963</v>
+        <v>0.007115302850536965</v>
       </c>
       <c r="W23" t="n">
         <v>0.007226671336383297</v>
       </c>
       <c r="X23" t="n">
-        <v>0.01524567936650126</v>
+        <v>0.01524567936650129</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.01541190675972721</v>
+        <v>0.01541190675972723</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.01283094429899817</v>
+        <v>0.01283094429899819</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.009855383137236761</v>
+        <v>0.009855383137236755</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.0124755644919876</v>
+        <v>0.01247556449198761</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.01562852939796065</v>
+        <v>0.01562852939796067</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.01068635105181155</v>
+        <v>0.01068635105181153</v>
       </c>
       <c r="AE23" t="n">
         <v>0.01292813607579789</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.004587564787511936</v>
+        <v>0.00458756478751194</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.01524567936650126</v>
+        <v>0.01524567936650129</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.01176637539473503</v>
+        <v>0.01176637539473502</v>
       </c>
       <c r="AI23" t="n">
         <v>0.001819357607846976</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.004503332732109336</v>
+        <v>0.004503332732109335</v>
       </c>
       <c r="AK23" t="n">
         <v>0.007226671336383297</v>
@@ -3855,31 +3855,31 @@
         <v>0.0068032055773382</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.008686715329552694</v>
+        <v>0.008686715329552702</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.006794781784865777</v>
+        <v>0.006794781784865774</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.01032077375336816</v>
+        <v>0.01032077375336817</v>
       </c>
       <c r="AP23" t="n">
         <v>0.01236087191544419</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.01300285202906658</v>
+        <v>0.0130028520290666</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.01474904964029645</v>
+        <v>0.01474904964029643</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.01241231297301506</v>
+        <v>0.01241231297301505</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.01835709917735838</v>
+        <v>0.01835709917735836</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.01151921107218452</v>
+        <v>0.01151921107218451</v>
       </c>
       <c r="AV23" t="n">
         <v>0.01052038817563444</v>
@@ -3895,142 +3895,142 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01642618763456791</v>
+        <v>0.01642618763456792</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01006620471430887</v>
+        <v>0.01006620471430886</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008254603102664819</v>
+        <v>0.008254603102664806</v>
       </c>
       <c r="F24" t="n">
-        <v>0.005178995195684236</v>
+        <v>0.005178995195684238</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001804841800994962</v>
+        <v>0.001804841800994966</v>
       </c>
       <c r="H24" t="n">
-        <v>0.001500051932714347</v>
+        <v>0.001500051932714346</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0002775805134323624</v>
+        <v>0.0002775805134323623</v>
       </c>
       <c r="J24" t="n">
-        <v>0.006343726052781313</v>
+        <v>0.006343726052781298</v>
       </c>
       <c r="K24" t="n">
         <v>0.007179491000503233</v>
       </c>
       <c r="L24" t="n">
-        <v>0.002586320747179591</v>
+        <v>0.002586320747179593</v>
       </c>
       <c r="M24" t="n">
-        <v>0.007243896768665496</v>
+        <v>0.007243896768665504</v>
       </c>
       <c r="N24" t="n">
-        <v>0.001773941675796374</v>
+        <v>0.001773941675796375</v>
       </c>
       <c r="O24" t="n">
-        <v>0.00445986991120505</v>
+        <v>0.004459869911205057</v>
       </c>
       <c r="P24" t="n">
-        <v>0.010017575043014</v>
+        <v>0.01001757504301402</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.03177019378849272</v>
+        <v>0.03177019378849277</v>
       </c>
       <c r="R24" t="n">
         <v>0.001175175343531013</v>
       </c>
       <c r="S24" t="n">
-        <v>0.009844596363033186</v>
+        <v>0.009844596363033187</v>
       </c>
       <c r="T24" t="n">
-        <v>0.03363196294543695</v>
+        <v>0.0336319629454369</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03786776650241763</v>
+        <v>0.03786776650241766</v>
       </c>
       <c r="V24" t="n">
-        <v>0.007748058686113975</v>
+        <v>0.007748058686113977</v>
       </c>
       <c r="W24" t="n">
         <v>0.013202437158261</v>
       </c>
       <c r="X24" t="n">
-        <v>0.007177610660352347</v>
+        <v>0.007177610660352358</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.04185077758758901</v>
+        <v>0.04185077758758907</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.03177019378849272</v>
+        <v>0.03177019378849277</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.03617340905894013</v>
+        <v>0.03617340905894011</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.01033869930253722</v>
+        <v>0.01033869930253723</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.006680929715028769</v>
+        <v>0.00668092971502878</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.03363196294543695</v>
+        <v>0.0336319629454369</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.008749409948990757</v>
+        <v>0.008749409948990759</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.07664084586515475</v>
+        <v>0.07664084586515481</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.007177610660352347</v>
+        <v>0.007177610660352358</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.007205707427217404</v>
+        <v>0.007205707427217397</v>
       </c>
       <c r="AI24" t="n">
         <v>0.001426198640043327</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.001244024753065791</v>
+        <v>0.00124402475306579</v>
       </c>
       <c r="AK24" t="n">
         <v>0.013202437158261</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.005494187451312373</v>
+        <v>0.005494187451312372</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.006458750776878846</v>
+        <v>0.006458750776878852</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.003775737145762187</v>
+        <v>0.003775737145762186</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.010017575043014</v>
+        <v>0.01001757504301402</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.008264132590748399</v>
+        <v>0.008264132590748397</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.008102892782289754</v>
+        <v>0.008102892782289765</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.04016161653596278</v>
+        <v>0.04016161653596271</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.001804841809198685</v>
+        <v>0.001804841809198683</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.003047145367306289</v>
+        <v>0.003047145367306285</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.0007422015515836844</v>
+        <v>0.0007422015515836842</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.0007461077282497543</v>
+        <v>0.0007461077282497542</v>
       </c>
     </row>
     <row r="25">
@@ -4046,49 +4046,49 @@
         <v>0.001659147952615484</v>
       </c>
       <c r="D25" t="n">
-        <v>0.002081256547546465</v>
+        <v>0.002081256547546462</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0002003270910728917</v>
+        <v>0.0002003270910728915</v>
       </c>
       <c r="F25" t="n">
-        <v>0.001809067314966652</v>
+        <v>0.001809067314966653</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0002097229080177917</v>
+        <v>0.0002097229080177921</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>0.0009123928647359485</v>
+        <v>0.0009123928647359462</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0003520307441241863</v>
+        <v>0.0003520307441241862</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001395716464562062</v>
+        <v>0.001395716464562063</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0007371221537001842</v>
+        <v>0.0007371221537001853</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>0.001978892196066998</v>
+        <v>0.001978892196067001</v>
       </c>
       <c r="P25" t="n">
-        <v>0.00172172844309177</v>
+        <v>0.001721728443091771</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.001101087722969745</v>
+        <v>0.001101087722969747</v>
       </c>
       <c r="R25" t="n">
-        <v>0.001127823334526934</v>
+        <v>0.001127823334526935</v>
       </c>
       <c r="S25" t="n">
         <v>0.001899672512954344</v>
       </c>
       <c r="T25" t="n">
-        <v>0.001743295694244287</v>
+        <v>0.001743295694244285</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
@@ -4098,25 +4098,25 @@
         <v>0.0007120593584453229</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001377787270062914</v>
+        <v>0.001377787270062916</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.0006293237890395893</v>
+        <v>0.0006293237890395901</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.001101087722969745</v>
+        <v>0.001101087722969747</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.0004635958213814985</v>
+        <v>0.0004635958213814982</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.0008766643686706524</v>
+        <v>0.0008766643686706529</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.001152349139645291</v>
+        <v>0.001152349139645293</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.001743295694244287</v>
+        <v>0.001743295694244285</v>
       </c>
       <c r="AE25" t="n">
         <v>0.001990138740914014</v>
@@ -4125,16 +4125,16 @@
         <v>0.001004715736084065</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.001377787270062914</v>
+        <v>0.001377787270062916</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.0004710708298558637</v>
+        <v>0.0004710708298558633</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.0006550360952300511</v>
+        <v>0.000655036095230051</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.0009037161606777459</v>
+        <v>0.0009037161606777455</v>
       </c>
       <c r="AK25" t="n">
         <v>0.0007120593584453229</v>
@@ -4143,31 +4143,31 @@
         <v>0.0007360729497717406</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.001246319388464897</v>
+        <v>0.001246319388464899</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.0009363314812219269</v>
+        <v>0.0009363314812219263</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.00172172844309177</v>
+        <v>0.001721728443091771</v>
       </c>
       <c r="AP25" t="n">
         <v>0.001327299914377372</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.002091949738266443</v>
+        <v>0.002091949738266446</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.0006040895123983674</v>
+        <v>0.0006040895123983665</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.0002097229119458932</v>
+        <v>0.0002097229119458931</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.0005690108809129674</v>
+        <v>0.0005690108809129664</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.0003155170107018599</v>
+        <v>0.0003155170107018598</v>
       </c>
       <c r="AV25" t="n">
         <v>0.0003387260805088019</v>
@@ -4186,97 +4186,97 @@
         <v>0.001832036413276914</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00209043774491334</v>
+        <v>0.002090437744913337</v>
       </c>
       <c r="E26" t="n">
-        <v>0.003944194378932308</v>
+        <v>0.003944194378932303</v>
       </c>
       <c r="F26" t="n">
-        <v>0.002101891787895876</v>
+        <v>0.002101891787895877</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0005448739422391516</v>
+        <v>0.0005448739422391528</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>6.443738829901789e-05</v>
+        <v>6.443738829901786e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.001350702545236476</v>
+        <v>0.001350702545236473</v>
       </c>
       <c r="K26" t="n">
         <v>0.001959231732017848</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0009504125673924405</v>
+        <v>0.0009504125673924413</v>
       </c>
       <c r="M26" t="n">
-        <v>0.001040209059151588</v>
+        <v>0.001040209059151589</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>0.001580019244203939</v>
+        <v>0.001580019244203942</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0004024596594489294</v>
+        <v>0.0004024596594489297</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.001772800073312411</v>
+        <v>0.001772800073312414</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0004370248361826283</v>
+        <v>0.0004370248361826284</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0003450678217624855</v>
+        <v>0.0003450678217624856</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0006637929168881569</v>
+        <v>0.0006637929168881562</v>
       </c>
       <c r="U26" t="n">
-        <v>0.003783129162680775</v>
+        <v>0.003783129162680778</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
         <v>0.0004264995141620274</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001076568551685</v>
+        <v>0.001076568551685001</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.0009137896730463245</v>
+        <v>0.0009137896730463255</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.001772800073312411</v>
+        <v>0.001772800073312414</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.001033736133735541</v>
+        <v>0.00103373613373554</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.001094792412553799</v>
+        <v>0.0010947924125538</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.001440722902914554</v>
+        <v>0.001440722902914556</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.0006637929168881569</v>
+        <v>0.0006637929168881562</v>
       </c>
       <c r="AE26" t="n">
         <v>0.00117166332158646</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.000331598389479245</v>
+        <v>0.0003315983894792452</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.001076568551685</v>
+        <v>0.001076568551685001</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.0015041218003492</v>
+        <v>0.001504121800349199</v>
       </c>
       <c r="AI26" t="n">
         <v>0.0002794860982405052</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.0006676517182327729</v>
+        <v>0.0006676517182327725</v>
       </c>
       <c r="AK26" t="n">
         <v>0.0004264995141620274</v>
@@ -4285,28 +4285,28 @@
         <v>0.0002399016828175478</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.0004904236493948065</v>
+        <v>0.0004904236493948071</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.0002999732046516773</v>
+        <v>0.0002999732046516771</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.0004024596594489294</v>
+        <v>0.0004024596594489297</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.0004183061711768778</v>
+        <v>0.0004183061711768776</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.0004255333948829594</v>
+        <v>0.0004255333948829599</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.0008777278033019429</v>
+        <v>0.0008777278033019418</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.0005448739640703615</v>
+        <v>0.0005448739640703611</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.0003009929628747897</v>
+        <v>0.0003009929628747892</v>
       </c>
       <c r="AU26" t="n">
         <v>0.0002871850070993702</v>
@@ -4328,58 +4328,58 @@
         <v>0.004055898526163918</v>
       </c>
       <c r="D27" t="n">
-        <v>0.004480087135708896</v>
+        <v>0.00448008713570889</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001544912556482825</v>
+        <v>0.001544912556482823</v>
       </c>
       <c r="F27" t="n">
-        <v>0.008258379295735082</v>
+        <v>0.008258379295735087</v>
       </c>
       <c r="G27" t="n">
-        <v>0.003794682145137206</v>
+        <v>0.003794682145137214</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0003026505741331506</v>
+        <v>0.0003026505741331504</v>
       </c>
       <c r="I27" t="n">
         <v>0.001200955902888359</v>
       </c>
       <c r="J27" t="n">
-        <v>0.005510627554440097</v>
+        <v>0.005510627554440083</v>
       </c>
       <c r="K27" t="n">
-        <v>0.004311190321813565</v>
+        <v>0.004311190321813564</v>
       </c>
       <c r="L27" t="n">
-        <v>0.005795690581662129</v>
+        <v>0.005795690581662133</v>
       </c>
       <c r="M27" t="n">
-        <v>0.004859770986686503</v>
+        <v>0.004859770986686511</v>
       </c>
       <c r="N27" t="n">
-        <v>0.00446617560990897</v>
+        <v>0.004466175609908973</v>
       </c>
       <c r="O27" t="n">
-        <v>0.004675595336520992</v>
+        <v>0.004675595336521</v>
       </c>
       <c r="P27" t="n">
-        <v>0.003474464606784904</v>
+        <v>0.003474464606784908</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.003361521371866789</v>
+        <v>0.003361521371866794</v>
       </c>
       <c r="R27" t="n">
-        <v>0.000784726055187557</v>
+        <v>0.0007847260551875571</v>
       </c>
       <c r="S27" t="n">
         <v>0.004722076555749979</v>
       </c>
       <c r="T27" t="n">
-        <v>0.003678655094601526</v>
+        <v>0.003678655094601523</v>
       </c>
       <c r="U27" t="n">
-        <v>0.00827450445977972</v>
+        <v>0.008274504459779727</v>
       </c>
       <c r="V27" t="n">
         <v>0.001628514515733823</v>
@@ -4388,43 +4388,43 @@
         <v>0.002035352817690717</v>
       </c>
       <c r="X27" t="n">
-        <v>0.00322177189856353</v>
+        <v>0.003221771898563536</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.004104586847203949</v>
+        <v>0.004104586847203954</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.003361521371866789</v>
+        <v>0.003361521371866794</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.002933113376166471</v>
+        <v>0.00293311337616647</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.004160693151096135</v>
+        <v>0.004160693151096137</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.0037957445731527</v>
+        <v>0.003795744573152706</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.003678655094601526</v>
+        <v>0.003678655094601523</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.004861624815968368</v>
+        <v>0.004861624815968369</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.002998885006726769</v>
+        <v>0.002998885006726771</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.00322177189856353</v>
+        <v>0.003221771898563536</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.00652343589065229</v>
+        <v>0.006523435890652282</v>
       </c>
       <c r="AI27" t="n">
         <v>0.001259724099226425</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.00189934557167364</v>
+        <v>0.001899345571673639</v>
       </c>
       <c r="AK27" t="n">
         <v>0.002035352817690717</v>
@@ -4433,28 +4433,28 @@
         <v>0.003159107426375853</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.003098015855424541</v>
+        <v>0.003098015855424544</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.00202768585855352</v>
+        <v>0.002027685858553518</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.003474464606784904</v>
+        <v>0.003474464606784908</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.004226741430367791</v>
+        <v>0.004226741430367789</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.004371322610924969</v>
+        <v>0.004371322610924974</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.003941994773293977</v>
+        <v>0.003941994773293971</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.003794682164342853</v>
+        <v>0.003794682164342849</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.00262834900781964</v>
+        <v>0.002628349007819636</v>
       </c>
       <c r="AU27" t="n">
         <v>0.003852471154072289</v>
@@ -4476,81 +4476,81 @@
         <v>0.001367655221625854</v>
       </c>
       <c r="D28" t="n">
-        <v>0.001642092374792672</v>
+        <v>0.001642092374792671</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0002072682633068175</v>
+        <v>0.0002072682633068172</v>
       </c>
       <c r="F28" t="n">
-        <v>0.001154745598617408</v>
+        <v>0.001154745598617409</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0003069024356958097</v>
+        <v>0.0003069024356958103</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0007207691406123045</v>
+        <v>0.000720769140612304</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0006749942308516616</v>
+        <v>0.0006749942308516613</v>
       </c>
       <c r="J28" t="n">
-        <v>0.001168838603671218</v>
+        <v>0.001168838603671215</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0008060405732881811</v>
+        <v>0.0008060405732881809</v>
       </c>
       <c r="L28" t="n">
-        <v>0.001764191358556924</v>
+        <v>0.001764191358556926</v>
       </c>
       <c r="M28" t="n">
-        <v>0.001691660196876108</v>
+        <v>0.00169166019687611</v>
       </c>
       <c r="N28" t="n">
-        <v>0.002621771760581059</v>
+        <v>0.002621771760581061</v>
       </c>
       <c r="O28" t="n">
-        <v>0.001741202619136571</v>
+        <v>0.001741202619136574</v>
       </c>
       <c r="P28" t="n">
-        <v>0.001092671961233934</v>
+        <v>0.001092671961233935</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.002086457201046715</v>
+        <v>0.002086457201046719</v>
       </c>
       <c r="R28" t="n">
-        <v>0.000891512980329377</v>
+        <v>0.0008915129803293773</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0008998180012842094</v>
+        <v>0.0008998180012842098</v>
       </c>
       <c r="T28" t="n">
-        <v>0.001392372015621054</v>
+        <v>0.001392372015621052</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.0006970455596331104</v>
+        <v>0.0006970455596331106</v>
       </c>
       <c r="W28" t="n">
         <v>0.001074375907557814</v>
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="n">
-        <v>0.001847895644025193</v>
+        <v>0.001847895644025195</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.002086457201046715</v>
+        <v>0.002086457201046719</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.001835206463035577</v>
+        <v>0.001835206463035576</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.002405311776790713</v>
+        <v>0.002405311776790714</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.002572089160167976</v>
+        <v>0.00257208916016798</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.001392372015621054</v>
+        <v>0.001392372015621052</v>
       </c>
       <c r="AE28" t="n">
         <v>0.001241357875040245</v>
@@ -4560,13 +4560,13 @@
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="n">
-        <v>0.001251279836225593</v>
+        <v>0.001251279836225591</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.0005936973173906881</v>
+        <v>0.000593697317390688</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.001173294729952545</v>
+        <v>0.001173294729952544</v>
       </c>
       <c r="AK28" t="n">
         <v>0.001074375907557814</v>
@@ -4575,28 +4575,28 @@
         <v>0.001887649914513307</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.000590344184822762</v>
+        <v>0.0005903441848227626</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.0003312709200538975</v>
+        <v>0.0003312709200538973</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.001092671961233934</v>
+        <v>0.001092671961233935</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.001123919746369046</v>
+        <v>0.001123919746369045</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.001058896411342175</v>
+        <v>0.001058896411342177</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.001778320207060209</v>
+        <v>0.001778320207060206</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.0003069024485311992</v>
+        <v>0.0003069024485311988</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.001212148774300586</v>
+        <v>0.001212148774300584</v>
       </c>
       <c r="AU28" t="n">
         <v>0.001415449010148696</v>
@@ -4615,101 +4615,101 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.004861113707205682</v>
+        <v>0.004861113707205685</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005503385220107498</v>
+        <v>0.005503385220107491</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000916760937842648</v>
+        <v>0.0009167609378426469</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00629596045192414</v>
+        <v>0.006295960451924144</v>
       </c>
       <c r="G29" t="n">
-        <v>0.003786945691580009</v>
+        <v>0.003786945691580017</v>
       </c>
       <c r="H29" t="n">
-        <v>0.004480129728469084</v>
+        <v>0.004480129728469081</v>
       </c>
       <c r="I29" t="n">
         <v>0.001192282047707311</v>
       </c>
       <c r="J29" t="n">
-        <v>0.006116239167559843</v>
+        <v>0.006116239167559827</v>
       </c>
       <c r="K29" t="n">
-        <v>0.002767837529566237</v>
+        <v>0.002767837529566235</v>
       </c>
       <c r="L29" t="n">
-        <v>0.00539112969614614</v>
+        <v>0.005391129696146144</v>
       </c>
       <c r="M29" t="n">
-        <v>0.006820243941034816</v>
+        <v>0.006820243941034825</v>
       </c>
       <c r="N29" t="n">
-        <v>0.009180835690904094</v>
+        <v>0.009180835690904098</v>
       </c>
       <c r="O29" t="n">
-        <v>0.00704180561046823</v>
+        <v>0.007041805610468244</v>
       </c>
       <c r="P29" t="n">
-        <v>0.003482699176979855</v>
+        <v>0.003482699176979859</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.00720360273316952</v>
+        <v>0.007203602733169531</v>
       </c>
       <c r="R29" t="n">
-        <v>0.002580254311219297</v>
+        <v>0.002580254311219298</v>
       </c>
       <c r="S29" t="n">
-        <v>0.00229412511726805</v>
+        <v>0.002294125117268051</v>
       </c>
       <c r="T29" t="n">
-        <v>0.003452200180966378</v>
+        <v>0.003452200180966374</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0.002491672890522881</v>
+        <v>0.002491672890522882</v>
       </c>
       <c r="W29" t="n">
         <v>0.003181417080538184</v>
       </c>
       <c r="X29" t="n">
-        <v>0.002708652203009795</v>
+        <v>0.0027086522030098</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.006972530425668463</v>
+        <v>0.006972530425668472</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.00720360273316952</v>
+        <v>0.007203602733169531</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.006942296505430568</v>
+        <v>0.006942296505430563</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.0101027107598573</v>
+        <v>0.01010271075985731</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.006370977120601684</v>
+        <v>0.006370977120601693</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.003452200180966378</v>
+        <v>0.003452200180966374</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.004411962999625055</v>
+        <v>0.004411962999625056</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.002944014905937172</v>
+        <v>0.002944014905937174</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.002708652203009795</v>
+        <v>0.0027086522030098</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.005144237532996126</v>
+        <v>0.005144237532996121</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.00163287375849071</v>
+        <v>0.001632873758490709</v>
       </c>
       <c r="AJ29" t="n">
         <v>0.003527760762117678</v>
@@ -4721,28 +4721,28 @@
         <v>0.003614170192613698</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.002079407119429909</v>
+        <v>0.002079407119429911</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.002344367947209282</v>
+        <v>0.002344367947209281</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.003482699176979855</v>
+        <v>0.003482699176979859</v>
       </c>
       <c r="AP29" t="n">
         <v>0.00351313829925361</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.007451811998012941</v>
+        <v>0.007451811998012951</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.006697664512208416</v>
+        <v>0.006697664512208405</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.003786945912389</v>
+        <v>0.003786945912388997</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.003538612345112291</v>
+        <v>0.003538612345112286</v>
       </c>
       <c r="AU29" t="n">
         <v>0.002352411563767358</v>
@@ -4764,101 +4764,101 @@
         <v>0.003759988450008111</v>
       </c>
       <c r="D30" t="n">
-        <v>0.004401299796392985</v>
+        <v>0.00440129979639298</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>0.006276067505875211</v>
+        <v>0.006276067505875215</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002839398522755481</v>
+        <v>0.002839398522755486</v>
       </c>
       <c r="H30" t="n">
-        <v>0.007812672490361272</v>
+        <v>0.007812672490361267</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0006518024354573913</v>
+        <v>0.000651802435457391</v>
       </c>
       <c r="J30" t="n">
-        <v>0.006071763890270493</v>
+        <v>0.006071763890270478</v>
       </c>
       <c r="K30" t="n">
-        <v>0.004696440113798386</v>
+        <v>0.004696440113798384</v>
       </c>
       <c r="L30" t="n">
-        <v>0.00426913518094707</v>
+        <v>0.004269135180947074</v>
       </c>
       <c r="M30" t="n">
-        <v>0.006509735899701032</v>
+        <v>0.006509735899701042</v>
       </c>
       <c r="N30" t="n">
-        <v>0.004244038114355963</v>
+        <v>0.004244038114355965</v>
       </c>
       <c r="O30" t="n">
-        <v>0.007438988852880839</v>
+        <v>0.007438988852880849</v>
       </c>
       <c r="P30" t="n">
-        <v>0.004715815698701806</v>
+        <v>0.004715815698701812</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.006105588371388039</v>
+        <v>0.006105588371388049</v>
       </c>
       <c r="R30" t="n">
-        <v>0.00297407907370213</v>
+        <v>0.002974079073702131</v>
       </c>
       <c r="S30" t="n">
         <v>0.00372906733502286</v>
       </c>
       <c r="T30" t="n">
-        <v>0.004282320656125064</v>
+        <v>0.00428232065612506</v>
       </c>
       <c r="U30" t="n">
-        <v>0.003233209090851814</v>
+        <v>0.003233209090851817</v>
       </c>
       <c r="V30" t="n">
-        <v>0.002450245841418495</v>
+        <v>0.002450245841418496</v>
       </c>
       <c r="W30" t="n">
         <v>0.002851103430107696</v>
       </c>
       <c r="X30" t="n">
-        <v>0.003582071392860713</v>
+        <v>0.003582071392860717</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.001725164900462456</v>
+        <v>0.001725164900462458</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.006105588371388039</v>
+        <v>0.006105588371388049</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.007240433993581838</v>
+        <v>0.007240433993581834</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.00672377412706591</v>
+        <v>0.006723774127065913</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.005598072859304389</v>
+        <v>0.005598072859304397</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.004282320656125064</v>
+        <v>0.00428232065612506</v>
       </c>
       <c r="AE30" t="n">
         <v>0.005048238901984435</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.004631932117977976</v>
+        <v>0.00463193211797798</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.003582071392860713</v>
+        <v>0.003582071392860717</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.004585628150163124</v>
+        <v>0.00458562815016312</v>
       </c>
       <c r="AI30" t="n">
         <v>0.001943880675951361</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.003049221225319712</v>
+        <v>0.00304922122531971</v>
       </c>
       <c r="AK30" t="n">
         <v>0.002851103430107696</v>
@@ -4867,31 +4867,31 @@
         <v>0.003946600089032796</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.002446531646290028</v>
+        <v>0.002446531646290031</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.002224115634167524</v>
+        <v>0.002224115634167523</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.004715815698701806</v>
+        <v>0.004715815698701812</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.005159418143845729</v>
+        <v>0.005159418143845728</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.005484108577280735</v>
+        <v>0.005484108577280741</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.001656756984178261</v>
+        <v>0.001656756984178258</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.00283939845425357</v>
+        <v>0.002839398454253568</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.00230970966859013</v>
+        <v>0.002309709668590126</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.001891434863208145</v>
+        <v>0.001891434863208144</v>
       </c>
       <c r="AV30" t="n">
         <v>0.001884621642129616</v>
@@ -4907,80 +4907,80 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.003787700960958932</v>
+        <v>0.003787700960958933</v>
       </c>
       <c r="D31" t="n">
-        <v>0.002998306139875338</v>
+        <v>0.002998306139875334</v>
       </c>
       <c r="E31" t="n">
-        <v>0.006886618465442316</v>
+        <v>0.006886618465442308</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01898211656844476</v>
+        <v>0.01898211656844477</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01141333488514132</v>
+        <v>0.01141333488514134</v>
       </c>
       <c r="H31" t="n">
-        <v>0.01510778442807761</v>
+        <v>0.0151077844280776</v>
       </c>
       <c r="I31" t="n">
-        <v>0.000136491568756006</v>
+        <v>0.0001364915687560059</v>
       </c>
       <c r="J31" t="n">
-        <v>0.002064995248138934</v>
+        <v>0.002064995248138929</v>
       </c>
       <c r="K31" t="n">
         <v>0.002987442190544018</v>
       </c>
       <c r="L31" t="n">
-        <v>0.002799876200551609</v>
+        <v>0.002799876200551612</v>
       </c>
       <c r="M31" t="n">
-        <v>0.001416162777278397</v>
+        <v>0.001416162777278399</v>
       </c>
       <c r="N31" t="n">
-        <v>0.001839256372819751</v>
+        <v>0.001839256372819753</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002125519204061471</v>
+        <v>0.002125519204061475</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0002740618518560775</v>
+        <v>0.0002740618518560777</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="n">
-        <v>0.0002162609890030044</v>
+        <v>0.0002162609890030041</v>
       </c>
       <c r="U31" t="n">
-        <v>0.0003834141716735754</v>
+        <v>0.0003834141716735757</v>
       </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
-        <v>9.214201838487358e-05</v>
+        <v>9.214201838487369e-05</v>
       </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.0003219187517671087</v>
+        <v>0.0003219187517671092</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.0002162609890030044</v>
+        <v>0.0002162609890030041</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.0002658584414968912</v>
+        <v>0.0002658584414968913</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.000184903061330465</v>
+        <v>0.0001849030613304652</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="n">
-        <v>0.0003918307064144813</v>
+        <v>0.0003918307064144809</v>
       </c>
       <c r="AI31" t="n">
         <v>0.0001413849892886071</v>
@@ -4991,22 +4991,22 @@
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="n">
-        <v>0.0002740618518560775</v>
+        <v>0.0002740618518560777</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.0002869541290761258</v>
+        <v>0.0002869541290761257</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.0002868297472707136</v>
+        <v>0.0002868297472707139</v>
       </c>
       <c r="AR31" t="n">
-        <v>8.870099907441025e-05</v>
+        <v>8.870099907441012e-05</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.01141333580421055</v>
+        <v>0.01141333580421054</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.01097508822031507</v>
+        <v>0.01097508822031505</v>
       </c>
       <c r="AU31" t="n">
         <v>0.01040106521855104</v>
@@ -5025,59 +5025,59 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.002378201600649284</v>
+        <v>0.002378201600649285</v>
       </c>
       <c r="D32" t="n">
-        <v>0.002551713726447261</v>
+        <v>0.002551713726447258</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00116581952141091</v>
+        <v>0.001165819521410909</v>
       </c>
       <c r="F32" t="n">
-        <v>0.005218164384801573</v>
+        <v>0.005218164384801575</v>
       </c>
       <c r="G32" t="n">
-        <v>0.009633051349682096</v>
+        <v>0.009633051349682115</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0004848519696080942</v>
+        <v>0.0004848519696080939</v>
       </c>
       <c r="I32" t="n">
-        <v>0.002323757732469157</v>
+        <v>0.002323757732469156</v>
       </c>
       <c r="J32" t="n">
-        <v>0.003188000727096327</v>
+        <v>0.003188000727096319</v>
       </c>
       <c r="K32" t="n">
-        <v>0.003308145855186404</v>
+        <v>0.003308145855186403</v>
       </c>
       <c r="L32" t="n">
-        <v>0.004292894291166113</v>
+        <v>0.004292894291166117</v>
       </c>
       <c r="M32" t="n">
-        <v>0.003204719229510769</v>
+        <v>0.003204719229510774</v>
       </c>
       <c r="N32" t="n">
-        <v>0.003609962012173003</v>
+        <v>0.003609962012173006</v>
       </c>
       <c r="O32" t="n">
-        <v>0.002771383790453797</v>
+        <v>0.002771383790453802</v>
       </c>
       <c r="P32" t="n">
-        <v>0.00138555071627542</v>
+        <v>0.001385550716275422</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.001379799200283799</v>
+        <v>0.001379799200283801</v>
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>0.0007212621273470386</v>
+        <v>0.0007212621273470389</v>
       </c>
       <c r="T32" t="n">
-        <v>0.001154740851809663</v>
+        <v>0.001154740851809661</v>
       </c>
       <c r="U32" t="n">
-        <v>0.003422490236462137</v>
+        <v>0.00342249023646214</v>
       </c>
       <c r="V32" t="n">
         <v>0.002651718758379553</v>
@@ -5086,37 +5086,37 @@
         <v>0.0004112647226107843</v>
       </c>
       <c r="X32" t="n">
-        <v>0.00137548372472387</v>
+        <v>0.001375483724723873</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.001400962111021607</v>
+        <v>0.001400962111021609</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.001379799200283799</v>
+        <v>0.001379799200283801</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.001697951933714438</v>
+        <v>0.001697951933714437</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.001169801169862111</v>
+        <v>0.001169801169862112</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.0014078399280718</v>
+        <v>0.001407839928071802</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.001154740851809663</v>
+        <v>0.001154740851809661</v>
       </c>
       <c r="AE32" t="n">
         <v>0.001422905386692864</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.001163812602769234</v>
+        <v>0.001163812602769235</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.00137548372472387</v>
+        <v>0.001375483724723873</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.0005998257116410266</v>
+        <v>0.0005998257116410261</v>
       </c>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
@@ -5127,34 +5127,34 @@
         <v>0.0009302743091110482</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.0004731989157857834</v>
+        <v>0.0004731989157857839</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.0004619882496269282</v>
+        <v>0.0004619882496269279</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.00138555071627542</v>
+        <v>0.001385550716275422</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.001236084647994051</v>
+        <v>0.00123608464799405</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.001324731713880428</v>
+        <v>0.00132473171388043</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.001343967229997787</v>
+        <v>0.001343967229997785</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.009633051186523354</v>
+        <v>0.009633051186523344</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.005873954585893163</v>
+        <v>0.005873954585893153</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.003912823279376835</v>
+        <v>0.003912823279376834</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.003255233349741616</v>
+        <v>0.003255233349741615</v>
       </c>
     </row>
     <row r="33">
@@ -5170,58 +5170,58 @@
         <v>0.003810436959235086</v>
       </c>
       <c r="D33" t="n">
-        <v>0.004535008497846325</v>
+        <v>0.00453500849784632</v>
       </c>
       <c r="E33" t="n">
-        <v>0.004027990281267198</v>
+        <v>0.004027990281267193</v>
       </c>
       <c r="F33" t="n">
-        <v>0.004510979670839396</v>
+        <v>0.004510979670839399</v>
       </c>
       <c r="G33" t="n">
-        <v>0.001633580037328826</v>
+        <v>0.001633580037328829</v>
       </c>
       <c r="H33" t="n">
-        <v>0.001339564321232461</v>
+        <v>0.00133956432123246</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0008549796700278936</v>
+        <v>0.0008549796700278932</v>
       </c>
       <c r="J33" t="n">
-        <v>0.007167109008473765</v>
+        <v>0.007167109008473745</v>
       </c>
       <c r="K33" t="n">
-        <v>0.004829726898603165</v>
+        <v>0.004829726898603164</v>
       </c>
       <c r="L33" t="n">
-        <v>0.003574385785009558</v>
+        <v>0.003574385785009561</v>
       </c>
       <c r="M33" t="n">
-        <v>0.004993667520051371</v>
+        <v>0.004993667520051378</v>
       </c>
       <c r="N33" t="n">
-        <v>0.007124928686941638</v>
+        <v>0.007124928686941642</v>
       </c>
       <c r="O33" t="n">
-        <v>0.006621770165574545</v>
+        <v>0.006621770165574557</v>
       </c>
       <c r="P33" t="n">
-        <v>0.003187209783213854</v>
+        <v>0.003187209783213857</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.004222723056051566</v>
+        <v>0.004222723056051573</v>
       </c>
       <c r="R33" t="n">
-        <v>0.002405350141309952</v>
+        <v>0.002405350141309953</v>
       </c>
       <c r="S33" t="n">
-        <v>0.002709618019327313</v>
+        <v>0.002709618019327314</v>
       </c>
       <c r="T33" t="n">
-        <v>0.002271424805721837</v>
+        <v>0.002271424805721834</v>
       </c>
       <c r="U33" t="n">
-        <v>0.005542669987268121</v>
+        <v>0.005542669987268126</v>
       </c>
       <c r="V33" t="n">
         <v>0.002167711445923236</v>
@@ -5230,43 +5230,43 @@
         <v>0.002130392623128238</v>
       </c>
       <c r="X33" t="n">
-        <v>0.002300059813125956</v>
+        <v>0.00230005981312596</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.003108061014873995</v>
+        <v>0.003108061014873999</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.004222723056051566</v>
+        <v>0.004222723056051573</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.004143436381012128</v>
+        <v>0.004143436381012125</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.005140270371048707</v>
+        <v>0.005140270371048711</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.004178094768821443</v>
+        <v>0.00417809476882145</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.002271424805721837</v>
+        <v>0.002271424805721834</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.002546520048192837</v>
+        <v>0.002546520048192838</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.002006577995052445</v>
+        <v>0.002006577995052447</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.002300059813125956</v>
+        <v>0.00230005981312596</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.002053615147319577</v>
+        <v>0.002053615147319576</v>
       </c>
       <c r="AI33" t="n">
         <v>0.001529865914588551</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.001930585194740239</v>
+        <v>0.001930585194740238</v>
       </c>
       <c r="AK33" t="n">
         <v>0.002130392623128238</v>
@@ -5275,28 +5275,28 @@
         <v>0.001562811901519021</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.001777700866750731</v>
+        <v>0.001777700866750733</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.001389656587818523</v>
+        <v>0.001389656587818522</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.003187209783213854</v>
+        <v>0.003187209783213857</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.003855865358581337</v>
+        <v>0.003855865358581336</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.003298343825263159</v>
+        <v>0.003298343825263163</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.002988406301934253</v>
+        <v>0.002988406301934249</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.001633580238326383</v>
+        <v>0.001633580238326381</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.001526672641212657</v>
+        <v>0.001526672641212654</v>
       </c>
       <c r="AU33" t="n">
         <v>0.001135575560333092</v>
@@ -5315,58 +5315,58 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.006974221987824185</v>
+        <v>0.006974221987824187</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00550692443643764</v>
+        <v>0.005506924436437635</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001030649711685181</v>
+        <v>0.00103064971168518</v>
       </c>
       <c r="F34" t="n">
-        <v>0.00823507263680155</v>
+        <v>0.008235072636801555</v>
       </c>
       <c r="G34" t="n">
-        <v>0.009571143161973729</v>
+        <v>0.009571143161973749</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01053572174370577</v>
+        <v>0.01053572174370576</v>
       </c>
       <c r="I34" t="n">
-        <v>0.02500340180076688</v>
+        <v>0.02500340180076687</v>
       </c>
       <c r="J34" t="n">
-        <v>0.005348212848237726</v>
+        <v>0.005348212848237712</v>
       </c>
       <c r="K34" t="n">
         <v>0.003815531992087201</v>
       </c>
       <c r="L34" t="n">
-        <v>0.006111462904006261</v>
+        <v>0.006111462904006267</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0084557008298592</v>
+        <v>0.008455700829859213</v>
       </c>
       <c r="N34" t="n">
         <v>0.01542732139956829</v>
       </c>
       <c r="O34" t="n">
-        <v>0.007676158143769431</v>
+        <v>0.007676158143769445</v>
       </c>
       <c r="P34" t="n">
-        <v>0.003984306026562082</v>
+        <v>0.003984306026562087</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.005754154238100723</v>
+        <v>0.005754154238100732</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0007580785789435423</v>
+        <v>0.0007580785789435425</v>
       </c>
       <c r="S34" t="n">
-        <v>0.003059524553570486</v>
+        <v>0.003059524553570487</v>
       </c>
       <c r="T34" t="n">
-        <v>0.003624191332044754</v>
+        <v>0.003624191332044749</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
@@ -5376,43 +5376,43 @@
         <v>0.001137022671120398</v>
       </c>
       <c r="X34" t="n">
-        <v>0.001618328962557891</v>
+        <v>0.001618328962557893</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.002588055355139527</v>
+        <v>0.00258805535513953</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.005754154238100723</v>
+        <v>0.005754154238100732</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.004784117522861541</v>
+        <v>0.004784117522861539</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.004701043476564582</v>
+        <v>0.004701043476564586</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.002870633696632679</v>
+        <v>0.002870633696632684</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.003624191332044754</v>
+        <v>0.003624191332044749</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.004746393198945666</v>
+        <v>0.004746393198945667</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.002366305879167366</v>
+        <v>0.002366305879167368</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.001618328962557891</v>
+        <v>0.001618328962557893</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.001878078610461257</v>
+        <v>0.001878078610461256</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.000712067611110247</v>
+        <v>0.0007120676111102469</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.0008394179454090592</v>
+        <v>0.0008394179454090587</v>
       </c>
       <c r="AK34" t="n">
         <v>0.001137022671120398</v>
@@ -5421,31 +5421,31 @@
         <v>0.001560972114250028</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.002402445840493641</v>
+        <v>0.002402445840493644</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.001874869190981763</v>
+        <v>0.001874869190981762</v>
       </c>
       <c r="AO34" t="n">
-        <v>0.003984306026562082</v>
+        <v>0.003984306026562087</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.003304597874364256</v>
+        <v>0.003304597874364254</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.003373366897703156</v>
+        <v>0.00337336689770316</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.002488172814298724</v>
+        <v>0.002488172814298721</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.009571144080372398</v>
+        <v>0.009571144080372389</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.007633136332522186</v>
+        <v>0.007633136332522172</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.017263676046413</v>
+        <v>0.01726367604641299</v>
       </c>
       <c r="AV34" t="n">
         <v>0.01434455604072928</v>
@@ -5461,142 +5461,142 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.00453639618940656</v>
+        <v>0.004536396189406561</v>
       </c>
       <c r="D35" t="n">
-        <v>0.00510307676133263</v>
+        <v>0.005103076761332623</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0001634335272260364</v>
+        <v>0.0001634335272260362</v>
       </c>
       <c r="F35" t="n">
-        <v>0.003805067169652987</v>
+        <v>0.00380506716965299</v>
       </c>
       <c r="G35" t="n">
-        <v>0.005287259356324982</v>
+        <v>0.005287259356324994</v>
       </c>
       <c r="H35" t="n">
-        <v>0.002769471981088801</v>
+        <v>0.0027694719810888</v>
       </c>
       <c r="I35" t="n">
-        <v>0.008200733234449423</v>
+        <v>0.00820073323444942</v>
       </c>
       <c r="J35" t="n">
-        <v>0.005793109693622647</v>
+        <v>0.005793109693622631</v>
       </c>
       <c r="K35" t="n">
-        <v>0.006701791810254814</v>
+        <v>0.006701791810254812</v>
       </c>
       <c r="L35" t="n">
-        <v>0.006479531404858872</v>
+        <v>0.006479531404858878</v>
       </c>
       <c r="M35" t="n">
-        <v>0.006064532012366445</v>
+        <v>0.006064532012366455</v>
       </c>
       <c r="N35" t="n">
-        <v>0.004373657677566745</v>
+        <v>0.004373657677566748</v>
       </c>
       <c r="O35" t="n">
-        <v>0.006455304895118264</v>
+        <v>0.006455304895118276</v>
       </c>
       <c r="P35" t="n">
-        <v>0.00465992142329356</v>
+        <v>0.004659921423293564</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.002630583206255035</v>
+        <v>0.00263058320625504</v>
       </c>
       <c r="R35" t="n">
-        <v>0.001835367648693829</v>
+        <v>0.00183536764869383</v>
       </c>
       <c r="S35" t="n">
-        <v>0.002866835315590682</v>
+        <v>0.002866835315590683</v>
       </c>
       <c r="T35" t="n">
-        <v>0.004382587319658265</v>
+        <v>0.004382587319658258</v>
       </c>
       <c r="U35" t="n">
-        <v>0.003928681043546803</v>
+        <v>0.003928681043546807</v>
       </c>
       <c r="V35" t="n">
         <v>0.004137798440791872</v>
       </c>
       <c r="W35" t="n">
-        <v>0.001420337562688417</v>
+        <v>0.001420337562688416</v>
       </c>
       <c r="X35" t="n">
-        <v>0.002839264042765104</v>
+        <v>0.002839264042765108</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.004694188383931448</v>
+        <v>0.004694188383931454</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.002630583206255035</v>
+        <v>0.00263058320625504</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.003550340778711521</v>
+        <v>0.003550340778711518</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.003089500874432273</v>
+        <v>0.003089500874432275</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.002144012359294589</v>
+        <v>0.002144012359294592</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.004382587319658265</v>
+        <v>0.004382587319658258</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.004697146708321183</v>
+        <v>0.004697146708321185</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.002978218666096289</v>
+        <v>0.002978218666096291</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.002839264042765104</v>
+        <v>0.002839264042765108</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.003258731853745977</v>
+        <v>0.003258731853745974</v>
       </c>
       <c r="AI35" t="n">
         <v>0.001148376554286764</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.001498133351847234</v>
+        <v>0.001498133351847233</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.001420337562688417</v>
+        <v>0.001420337562688416</v>
       </c>
       <c r="AL35" t="n">
         <v>0.00230688979552488</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002174481797261494</v>
+        <v>0.002174481797261496</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.001454763173343194</v>
+        <v>0.001454763173343193</v>
       </c>
       <c r="AO35" t="n">
-        <v>0.00465992142329356</v>
+        <v>0.004659921423293564</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.004376485127982582</v>
+        <v>0.004376485127982581</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.005973163005687849</v>
+        <v>0.005973163005687857</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.004517163808441366</v>
+        <v>0.004517163808441359</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.005287259598288293</v>
+        <v>0.005287259598288287</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.004600847331232022</v>
+        <v>0.004600847331232014</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.003019683367792863</v>
+        <v>0.003019683367792864</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.003080153651200762</v>
+        <v>0.003080153651200761</v>
       </c>
     </row>
   </sheetData>
